--- a/CrCraft收支与赞助鸣谢单.xlsx
+++ b/CrCraft收支与赞助鸣谢单.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet name="收支与赞助鸣谢" sheetId="1" r:id="rId1"/>
-    <sheet name="服主的投资和欠条" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="78">
   <si>
     <t>服务器收入与支出</t>
   </si>
@@ -72,124 +71,127 @@
     <t>Celi2357</t>
   </si>
   <si>
-    <t>↑1</t>
-  </si>
-  <si>
     <t>MoFangYa_</t>
   </si>
   <si>
     <t>AL_1S_2</t>
   </si>
   <si>
+    <t>BYyihan</t>
+  </si>
+  <si>
+    <t>KIRINIT</t>
+  </si>
+  <si>
+    <t>Mtve</t>
+  </si>
+  <si>
+    <t>qmzp_</t>
+  </si>
+  <si>
+    <t>zkiftie</t>
+  </si>
+  <si>
+    <t>Disha_UUU2</t>
+  </si>
+  <si>
+    <t>_LoveSelf_</t>
+  </si>
+  <si>
+    <t>dog</t>
+  </si>
+  <si>
+    <t>NGZI</t>
+  </si>
+  <si>
+    <t>Guramchik</t>
+  </si>
+  <si>
+    <t>Press_on</t>
+  </si>
+  <si>
+    <t>用于购买内存条</t>
+  </si>
+  <si>
+    <t>partyking1145</t>
+  </si>
+  <si>
+    <t>购买内存条</t>
+  </si>
+  <si>
+    <t>xiaoshenjin233</t>
+  </si>
+  <si>
+    <t>主板、硬盘、机箱</t>
+  </si>
+  <si>
+    <t>rocksuger</t>
+  </si>
+  <si>
+    <t>电费</t>
+  </si>
+  <si>
+    <t>SNHGY</t>
+  </si>
+  <si>
+    <t>Sz05</t>
+  </si>
+  <si>
+    <t>woshixiaoliu_ovo</t>
+  </si>
+  <si>
+    <t>10天群管理员</t>
+  </si>
+  <si>
+    <t>Y37MzZ_TrusT</t>
+  </si>
+  <si>
+    <t>luolizuiniubi</t>
+  </si>
+  <si>
+    <t>↑34</t>
+  </si>
+  <si>
+    <t>匿名玩家</t>
+  </si>
+  <si>
+    <t>cgh</t>
+  </si>
+  <si>
     <t>↓1</t>
   </si>
   <si>
-    <t>BYyihan</t>
-  </si>
-  <si>
-    <t>KIRINIT</t>
-  </si>
-  <si>
-    <t>Mtve</t>
-  </si>
-  <si>
-    <t>qmzp_</t>
-  </si>
-  <si>
-    <t>zkiftie</t>
-  </si>
-  <si>
-    <t>Disha_UUU2</t>
-  </si>
-  <si>
-    <t>_LoveSelf_</t>
-  </si>
-  <si>
-    <t>dog</t>
-  </si>
-  <si>
-    <t>NGZI</t>
-  </si>
-  <si>
-    <t>Guramchik</t>
-  </si>
-  <si>
-    <t>Press_on</t>
-  </si>
-  <si>
-    <t>用于购买内存条</t>
-  </si>
-  <si>
-    <t>partyking1145</t>
-  </si>
-  <si>
-    <t>购买内存条</t>
-  </si>
-  <si>
-    <t>xiaoshenjin233</t>
-  </si>
-  <si>
-    <t>主板、硬盘、机箱</t>
-  </si>
-  <si>
-    <t>rocksuger</t>
-  </si>
-  <si>
-    <t>电费</t>
-  </si>
-  <si>
-    <t>SNHGY</t>
-  </si>
-  <si>
-    <t>Sz05</t>
-  </si>
-  <si>
-    <t>woshixiaoliu_ovo</t>
-  </si>
-  <si>
-    <t>10天群管理员</t>
-  </si>
-  <si>
-    <t>Y37MzZ_TrusT</t>
-  </si>
-  <si>
-    <t>cgh</t>
-  </si>
-  <si>
-    <t>匿名玩家</t>
-  </si>
-  <si>
     <t>srdownb</t>
   </si>
   <si>
+    <t>Alhion_WWW</t>
+  </si>
+  <si>
     <t>Xs1st_</t>
   </si>
   <si>
-    <t>Alhion_WWW</t>
+    <t>darkmoon114514</t>
   </si>
   <si>
     <t>chunfeng</t>
   </si>
   <si>
-    <t>darkmoon114514</t>
-  </si>
-  <si>
     <t>KAMI</t>
   </si>
   <si>
     <t>91kk</t>
   </si>
   <si>
+    <t>捐樱花映射VIP</t>
+  </si>
+  <si>
     <t>faxi</t>
   </si>
   <si>
-    <t>捐樱花映射VIP</t>
+    <t>樱花映射VIP</t>
   </si>
   <si>
     <t>wybhh51811</t>
-  </si>
-  <si>
-    <t>樱花映射VIP</t>
   </si>
   <si>
     <t>red_chipi</t>
@@ -1105,7 +1107,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1178,21 +1180,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="31" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="7" xfId="22" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="31" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="7" xfId="22" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="31" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1215,18 +1217,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="31" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="31" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="31" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="7" xfId="22" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="31" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1">
@@ -1565,7 +1555,7 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:K164"/>
+  <dimension ref="A1:K165"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="15.625" customWidth="1"/>
@@ -1658,14 +1648,11 @@
       <c r="J3" s="3">
         <v>46219</v>
       </c>
-      <c r="K3" t="s">
-        <v>14</v>
-      </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="12"/>
       <c r="B4" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C4" s="13">
         <v>0.55</v>
@@ -1676,7 +1663,7 @@
         <v>2</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I4" s="16">
         <f>SUM(C44,C49,C51:C51,C53,C58:C58,C60:C60,C63,C66:C66,C68:C68,C70,C72:C72,C77,C91,C95,C125,C127,C136,C138,C141,C148,C150,C152,C154,C156,C159)</f>
@@ -1685,14 +1672,11 @@
       <c r="J4" s="3">
         <v>46204</v>
       </c>
-      <c r="K4" t="s">
-        <v>17</v>
-      </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="12"/>
       <c r="B5" s="8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C5" s="13">
         <v>2</v>
@@ -1703,7 +1687,7 @@
         <v>3</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I5" s="2">
         <f>SUM(C110:C110,C113,C116,C118,C129,C134,C142,C151,C153,C158)</f>
@@ -1716,7 +1700,7 @@
     <row r="6" spans="1:11">
       <c r="A6" s="12"/>
       <c r="B6" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C6" s="13">
         <v>3</v>
@@ -1727,7 +1711,7 @@
         <v>4</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I6" s="16">
         <f>SUM(C28:C28,C32:C32,C34:C34,C37,C39,C42:C42,C54,C57,C59,C61,C67,C69,C71,C76)</f>
@@ -1740,7 +1724,7 @@
     <row r="7" spans="1:11">
       <c r="A7" s="12"/>
       <c r="B7" s="8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C7" s="13">
         <v>1.28</v>
@@ -1751,7 +1735,7 @@
         <v>5</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I7" s="16">
         <f>SUM(C11,C16,C29,C25,C62,C81:C81)</f>
@@ -1766,7 +1750,7 @@
         <v>44164</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C8" s="13">
         <v>9</v>
@@ -1780,7 +1764,7 @@
         <v>6</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I8" s="2">
         <f>SUM(C121,C123,C126,C128,C131,C161)</f>
@@ -1795,7 +1779,7 @@
         <v>44213</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C9" s="13">
         <v>0.1</v>
@@ -1809,7 +1793,7 @@
         <v>7</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="I9" s="16">
         <f>SUM(C52,C65)</f>
@@ -1838,7 +1822,7 @@
         <v>8</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I10" s="2">
         <f>SUM(C133,C143,C147,C155,C160)</f>
@@ -1853,7 +1837,7 @@
         <v>44781</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C11" s="13">
         <v>130</v>
@@ -1863,13 +1847,13 @@
         <v>193.93</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G11" s="15">
         <v>9</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I11" s="2">
         <f>SUM(C86,C101,C105,C107,C112,C119,C124)</f>
@@ -1892,13 +1876,13 @@
         <v>-5.06999999999999</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G12" s="15">
         <v>10</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I12" s="16">
         <f>SUM(C8:C8,C47,C45,C50:C50)</f>
@@ -1913,7 +1897,7 @@
         <v>44787</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C13" s="13">
         <v>5.02</v>
@@ -1950,13 +1934,13 @@
         <v>-780.05</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G14" s="15">
         <v>12</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I14" s="16">
         <f>SUM(C56,C46,C74)</f>
@@ -1981,13 +1965,13 @@
         <v>-660.05</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G15" s="15">
         <v>13</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I15" s="2">
         <f>SUM(C99,C109,C130,C137,C144)</f>
@@ -2002,7 +1986,7 @@
         <v>44946</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C16" s="13">
         <v>13</v>
@@ -2016,7 +2000,7 @@
         <v>14</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I16" s="2">
         <f>SUM(C85:C85,C89,C96:C98,C117,C120,C122)</f>
@@ -2026,12 +2010,12 @@
         <v>46039</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:11">
       <c r="A17" s="17">
         <v>44953</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C17" s="13">
         <v>10</v>
@@ -2041,13 +2025,13 @@
         <v>-637.05</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G17" s="15">
         <v>15</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I17" s="2">
         <v>15</v>
@@ -2056,7 +2040,7 @@
         <v>45930</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:11">
       <c r="A18" s="17">
         <v>44958</v>
       </c>
@@ -2075,21 +2059,23 @@
       <c r="G18" s="15">
         <v>16</v>
       </c>
-      <c r="H18" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="I18" s="16">
-        <f>SUM(C40,C64)</f>
-        <v>11</v>
+      <c r="H18" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I18" s="2">
+        <v>12</v>
       </c>
       <c r="J18" s="3">
-        <v>45555</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
+        <v>46302</v>
+      </c>
+      <c r="K18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
       <c r="A19" s="17"/>
       <c r="B19" s="22" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C19" s="13">
         <v>1.32</v>
@@ -2099,18 +2085,21 @@
       <c r="G19" s="15">
         <v>17</v>
       </c>
-      <c r="H19" s="1" t="s">
+      <c r="H19" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="I19" s="16">
+        <f>SUM(C40,C64)</f>
+        <v>11</v>
+      </c>
+      <c r="J19" s="3">
+        <v>45555</v>
+      </c>
+      <c r="K19" t="s">
         <v>43</v>
       </c>
-      <c r="I19" s="2">
-        <f>SUM(C135,C139,C146)</f>
-        <v>10.5</v>
-      </c>
-      <c r="J19" s="3">
-        <v>46145</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
+    </row>
+    <row r="20" spans="1:11">
       <c r="A20" s="17">
         <v>44961</v>
       </c>
@@ -2128,17 +2117,21 @@
       <c r="G20" s="15">
         <v>18</v>
       </c>
-      <c r="H20" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="I20" s="16">
-        <v>10</v>
+      <c r="H20" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I20" s="2">
+        <f>SUM(C135,C139,C146)</f>
+        <v>10.5</v>
       </c>
       <c r="J20" s="3">
-        <v>44953</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
+        <v>46145</v>
+      </c>
+      <c r="K20" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
       <c r="A21" s="17">
         <v>45138</v>
       </c>
@@ -2158,16 +2151,19 @@
         <v>19</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="I21" s="16">
         <v>10</v>
       </c>
       <c r="J21" s="3">
-        <v>45234</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
+        <v>44953</v>
+      </c>
+      <c r="K21" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
       <c r="A22" s="17">
         <v>45140</v>
       </c>
@@ -2192,10 +2188,13 @@
         <v>10</v>
       </c>
       <c r="J22" s="3">
-        <v>45325</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
+        <v>45234</v>
+      </c>
+      <c r="K22" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
       <c r="A23" s="17">
         <v>45141</v>
       </c>
@@ -2220,10 +2219,13 @@
         <v>10</v>
       </c>
       <c r="J23" s="3">
-        <v>45649</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
+        <v>45325</v>
+      </c>
+      <c r="K23" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
       <c r="A24" s="17"/>
       <c r="B24" s="8" t="s">
         <v>13</v>
@@ -2236,22 +2238,25 @@
       <c r="G24" s="15">
         <v>22</v>
       </c>
-      <c r="H24" s="1" t="s">
+      <c r="H24" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="I24" s="2">
+      <c r="I24" s="16">
         <v>10</v>
       </c>
       <c r="J24" s="3">
-        <v>46069</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
+        <v>45649</v>
+      </c>
+      <c r="K24" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
       <c r="A25" s="17">
         <v>45160</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C25" s="13">
         <v>3</v>
@@ -2264,22 +2269,25 @@
       <c r="G25" s="15">
         <v>23</v>
       </c>
-      <c r="H25" s="10" t="s">
+      <c r="H25" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="I25" s="16">
+      <c r="I25" s="2">
         <v>10</v>
       </c>
       <c r="J25" s="3">
-        <v>46145</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
+        <v>46069</v>
+      </c>
+      <c r="K25" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
       <c r="A26" s="17">
         <v>45234</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C26" s="13">
         <v>10</v>
@@ -2297,14 +2305,17 @@
       <c r="H26" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="I26" s="2">
-        <v>8</v>
+      <c r="I26" s="16">
+        <v>10</v>
       </c>
       <c r="J26" s="3">
-        <v>45860</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
+        <v>46145</v>
+      </c>
+      <c r="K26" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
       <c r="A27" s="17"/>
       <c r="B27" s="8"/>
       <c r="C27" s="18">
@@ -2324,15 +2335,18 @@
         <v>8</v>
       </c>
       <c r="J27" s="3">
-        <v>46205</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
+        <v>45860</v>
+      </c>
+      <c r="K27" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
       <c r="A28" s="17">
         <v>45249</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C28" s="13">
         <v>15.5</v>
@@ -2349,18 +2363,21 @@
         <v>55</v>
       </c>
       <c r="I28" s="2">
-        <v>7.33</v>
+        <v>8</v>
       </c>
       <c r="J28" s="3">
-        <v>45907</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
+        <v>46205</v>
+      </c>
+      <c r="K28" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
       <c r="A29" s="17">
         <v>45305</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C29" s="13">
         <v>50</v>
@@ -2376,20 +2393,22 @@
       <c r="H29" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="I29" s="16">
-        <f>SUM(C82,C84,C94)</f>
-        <v>6.98</v>
+      <c r="I29" s="2">
+        <v>7.33</v>
       </c>
       <c r="J29" s="3">
-        <v>45861</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10">
+        <v>45907</v>
+      </c>
+      <c r="K29" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
       <c r="A30" s="17">
         <v>45325</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C30" s="13">
         <v>10</v>
@@ -2405,14 +2424,18 @@
       <c r="H30" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="I30" s="2">
-        <v>6</v>
+      <c r="I30" s="16">
+        <f>SUM(C82,C84,C94)</f>
+        <v>6.98</v>
       </c>
       <c r="J30" s="3">
-        <v>45868</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10">
+        <v>45861</v>
+      </c>
+      <c r="K30" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
       <c r="A31" s="17">
         <v>45341</v>
       </c>
@@ -2434,18 +2457,21 @@
         <v>58</v>
       </c>
       <c r="I31" s="2">
-        <v>5.04</v>
+        <v>6</v>
       </c>
       <c r="J31" s="3">
-        <v>46160</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10">
+        <v>45868</v>
+      </c>
+      <c r="K31" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
       <c r="A32" s="17">
         <v>45368</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C32" s="13">
         <v>33.01</v>
@@ -2455,27 +2481,30 @@
         <v>-239.1</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G32">
         <v>30</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="I32" s="16">
-        <v>5.02</v>
+        <v>59</v>
+      </c>
+      <c r="I32" s="2">
+        <v>5.04</v>
       </c>
       <c r="J32" s="3">
-        <v>44787</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10">
+        <v>46160</v>
+      </c>
+      <c r="K32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
       <c r="A33" s="17">
         <v>45387</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C33" s="13">
         <v>1.38</v>
@@ -2489,21 +2518,24 @@
         <v>31</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="I33" s="16">
-        <v>5</v>
+        <v>5.02</v>
       </c>
       <c r="J33" s="3">
-        <v>45634</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10">
+        <v>44787</v>
+      </c>
+      <c r="K33" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
       <c r="A34" s="17">
         <v>45394</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C34" s="13">
         <v>16</v>
@@ -2513,7 +2545,7 @@
         <v>-221.72</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G34">
         <v>32</v>
@@ -2522,18 +2554,21 @@
         <v>61</v>
       </c>
       <c r="I34" s="16">
-        <v>4.15</v>
+        <v>5</v>
       </c>
       <c r="J34" s="3">
-        <v>45707</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10">
+        <v>45634</v>
+      </c>
+      <c r="K34" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11">
       <c r="A35" s="17">
         <v>45396</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C35" s="13">
         <v>0.8</v>
@@ -2549,14 +2584,17 @@
       <c r="H35" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="I35" s="2">
-        <v>4</v>
+      <c r="I35" s="16">
+        <v>4.15</v>
       </c>
       <c r="J35" s="3">
-        <v>45885</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10">
+        <v>45707</v>
+      </c>
+      <c r="K35" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
       <c r="A36" s="17">
         <v>45403</v>
       </c>
@@ -2574,23 +2612,25 @@
       <c r="G36">
         <v>34</v>
       </c>
-      <c r="H36" s="1" t="s">
+      <c r="H36" s="10" t="s">
         <v>63</v>
       </c>
       <c r="I36" s="2">
-        <f>SUM(C100,C108)</f>
         <v>4</v>
       </c>
       <c r="J36" s="3">
-        <v>45934</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10">
+        <v>45885</v>
+      </c>
+      <c r="K36" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11">
       <c r="A37" s="17">
         <v>45403</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C37" s="13">
         <v>5</v>
@@ -2600,22 +2640,26 @@
         <v>-212.72</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G37">
         <v>35</v>
       </c>
-      <c r="H37" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="I37" s="16">
-        <v>3</v>
-      </c>
-      <c r="J37" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10">
+      <c r="H37" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="I37" s="2">
+        <f>SUM(C100,C108)</f>
+        <v>4</v>
+      </c>
+      <c r="J37" s="3">
+        <v>45934</v>
+      </c>
+      <c r="K37" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11">
       <c r="A38" s="17">
         <v>45412</v>
       </c>
@@ -2634,21 +2678,24 @@
         <v>36</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>64</v>
+        <v>18</v>
       </c>
       <c r="I38" s="16">
         <v>3</v>
       </c>
-      <c r="J38" s="3">
-        <v>45500</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10">
+      <c r="J38" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K38" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11">
       <c r="A39" s="17">
         <v>45417</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C39" s="13">
         <v>11</v>
@@ -2664,19 +2711,22 @@
       <c r="H39" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="I39" s="2">
-        <v>2.5</v>
+      <c r="I39" s="16">
+        <v>3</v>
       </c>
       <c r="J39" s="3">
-        <v>45976</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10">
+        <v>45500</v>
+      </c>
+      <c r="K39" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11">
       <c r="A40" s="17">
         <v>45421</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C40" s="13">
         <v>5</v>
@@ -2686,23 +2736,25 @@
         <v>-189.72</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G40" s="15">
         <v>38</v>
       </c>
       <c r="H40" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="I40" s="16">
-        <f>SUM(C35,C33:C33)</f>
-        <v>2.18</v>
+        <v>66</v>
+      </c>
+      <c r="I40" s="2">
+        <v>2.5</v>
       </c>
       <c r="J40" s="3">
-        <v>45396</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10">
+        <v>45976</v>
+      </c>
+      <c r="K40" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11">
       <c r="A41" s="17">
         <v>45478</v>
       </c>
@@ -2716,27 +2768,31 @@
         <v>-1999.72</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G41">
         <v>39</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="I41" s="16">
-        <v>2</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10">
+        <f>SUM(C35,C33:C33)</f>
+        <v>2.18</v>
+      </c>
+      <c r="J41" s="3">
+        <v>45396</v>
+      </c>
+      <c r="K41" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11">
       <c r="A42" s="17">
         <v>45494</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C42" s="13">
         <v>82.45</v>
@@ -2746,22 +2802,25 @@
         <v>-1915.27</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G42" s="15">
         <v>40</v>
       </c>
-      <c r="H42" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="I42" s="2">
+      <c r="H42" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="I42" s="16">
         <v>2</v>
       </c>
-      <c r="J42" s="3">
-        <v>45907</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10">
+      <c r="J42" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K42" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11">
       <c r="A43" s="17"/>
       <c r="B43" s="8" t="s">
         <v>13</v>
@@ -2774,162 +2833,180 @@
       <c r="G43">
         <v>41</v>
       </c>
-      <c r="H43" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="I43" s="16">
-        <v>1.32</v>
+      <c r="H43" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I43" s="2">
+        <v>2</v>
       </c>
       <c r="J43" s="3">
-        <v>44958</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10">
-      <c r="A44" s="25">
+        <v>45907</v>
+      </c>
+      <c r="K43" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11">
+      <c r="A44" s="24">
         <v>45495</v>
       </c>
-      <c r="B44" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C44" s="27">
+      <c r="B44" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C44" s="26">
         <v>8</v>
       </c>
       <c r="D44" s="21">
         <f>SUM(C3:C44)</f>
         <v>-1907.27</v>
       </c>
-      <c r="E44" s="28"/>
+      <c r="E44" s="27"/>
       <c r="G44">
         <v>42</v>
       </c>
-      <c r="H44" s="10" t="s">
+      <c r="H44" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="I44" s="16">
+        <v>1.32</v>
+      </c>
+      <c r="J44" s="3">
+        <v>44958</v>
+      </c>
+      <c r="K44" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11">
+      <c r="A45" s="24">
+        <v>45496</v>
+      </c>
+      <c r="B45" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="I44" s="16">
-        <v>1.28</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10">
-      <c r="A45" s="25">
-        <v>45496</v>
-      </c>
-      <c r="B45" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="C45" s="27">
+      <c r="C45" s="26">
         <v>5</v>
       </c>
       <c r="D45" s="21">
         <f>SUM(C3:C46)</f>
         <v>-1899.27</v>
       </c>
-      <c r="E45" s="28"/>
+      <c r="E45" s="27"/>
       <c r="G45">
         <v>43</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="I45" s="16">
-        <v>1.01</v>
-      </c>
-      <c r="J45" s="3">
-        <v>45141</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10">
+        <v>1.28</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K45" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11">
       <c r="A46" s="29"/>
-      <c r="B46" s="26" t="s">
-        <v>34</v>
-      </c>
-      <c r="C46" s="27">
+      <c r="B46" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C46" s="26">
         <v>3</v>
       </c>
       <c r="D46" s="30"/>
-      <c r="E46" s="28"/>
+      <c r="E46" s="27"/>
       <c r="G46">
         <v>44</v>
       </c>
       <c r="H46" s="10" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="I46" s="16">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="J46" s="3">
-        <v>45794</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10">
+        <v>45141</v>
+      </c>
+      <c r="K46" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11">
       <c r="A47" s="17">
         <v>45497</v>
       </c>
-      <c r="B47" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="C47" s="27">
+      <c r="B47" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="C47" s="26">
         <v>25</v>
       </c>
       <c r="D47" s="21">
         <f>SUM(C3:C47)</f>
         <v>-1874.27</v>
       </c>
-      <c r="E47" s="28"/>
+      <c r="E47" s="27"/>
       <c r="G47">
         <v>45</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>15</v>
+        <v>69</v>
       </c>
       <c r="I47" s="16">
-        <v>0.55</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10">
-      <c r="A48" s="25">
+        <v>1</v>
+      </c>
+      <c r="J47" s="3">
+        <v>45794</v>
+      </c>
+      <c r="K47" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11">
+      <c r="A48" s="24">
         <v>45500</v>
       </c>
-      <c r="B48" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="C48" s="27">
+      <c r="B48" s="25" t="s">
+        <v>65</v>
+      </c>
+      <c r="C48" s="26">
         <v>3</v>
       </c>
       <c r="D48" s="21">
         <f>SUM(C3:C49)</f>
         <v>-1866.27</v>
       </c>
-      <c r="E48" s="28"/>
+      <c r="E48" s="27"/>
       <c r="G48" s="15">
         <v>46</v>
       </c>
       <c r="H48" s="10" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="I48" s="16">
-        <v>0.5</v>
-      </c>
-      <c r="J48" s="3">
-        <v>45697</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10">
+        <v>0.55</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K48" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11">
       <c r="A49" s="31"/>
-      <c r="B49" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C49" s="27">
+      <c r="B49" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C49" s="26">
         <v>5</v>
       </c>
       <c r="D49" s="30"/>
-      <c r="E49" s="28" t="s">
-        <v>35</v>
+      <c r="E49" s="27" t="s">
+        <v>33</v>
       </c>
       <c r="G49">
         <v>47</v>
@@ -2937,120 +3014,144 @@
       <c r="H49" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="I49" s="2">
+      <c r="I49" s="16">
         <v>0.5</v>
       </c>
       <c r="J49" s="3">
-        <v>45885</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10">
-      <c r="A50" s="25">
+        <v>45697</v>
+      </c>
+      <c r="K49" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11">
+      <c r="A50" s="24">
         <v>45505</v>
       </c>
-      <c r="B50" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="C50" s="27">
+      <c r="B50" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="C50" s="26">
         <v>10</v>
       </c>
       <c r="D50" s="21">
         <f>SUM(C3:C50)</f>
         <v>-1856.27</v>
       </c>
-      <c r="E50" s="28" t="s">
-        <v>35</v>
+      <c r="E50" s="27" t="s">
+        <v>33</v>
       </c>
       <c r="G50">
         <v>48</v>
       </c>
       <c r="H50" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="I50" s="16">
-        <v>0.11</v>
+        <v>71</v>
+      </c>
+      <c r="I50" s="2">
+        <v>0.5</v>
       </c>
       <c r="J50" s="3">
-        <v>45140</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10">
-      <c r="A51" s="25">
+        <v>45885</v>
+      </c>
+      <c r="K50" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11">
+      <c r="A51" s="24">
         <v>45507</v>
       </c>
-      <c r="B51" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C51" s="27">
+      <c r="B51" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C51" s="26">
         <v>14</v>
       </c>
       <c r="D51" s="21">
         <f>SUM(C3:C52)</f>
         <v>-1756.27</v>
       </c>
-      <c r="E51" s="28" t="s">
-        <v>35</v>
+      <c r="E51" s="27" t="s">
+        <v>33</v>
       </c>
       <c r="G51">
         <v>49</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="I51" s="16">
+        <v>0.11</v>
+      </c>
+      <c r="J51" s="3">
+        <v>45140</v>
+      </c>
+      <c r="K51" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11">
+      <c r="A52" s="31"/>
+      <c r="B52" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="C52" s="26">
+        <v>86</v>
+      </c>
+      <c r="D52" s="30"/>
+      <c r="E52" s="27" t="s">
+        <v>72</v>
+      </c>
+      <c r="G52">
+        <v>50</v>
+      </c>
+      <c r="H52" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="I52" s="16">
         <v>0.1</v>
       </c>
-      <c r="J51" s="3">
+      <c r="J52" s="3">
         <v>44213</v>
       </c>
-    </row>
-    <row r="52" spans="1:10">
-      <c r="A52" s="31"/>
-      <c r="B52" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="C52" s="27">
-        <v>86</v>
-      </c>
-      <c r="D52" s="30"/>
-      <c r="E52" s="28" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10">
-      <c r="A53" s="25">
+      <c r="K52" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11">
+      <c r="A53" s="24">
         <v>45508</v>
       </c>
-      <c r="B53" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C53" s="27">
+      <c r="B53" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C53" s="26">
         <v>9</v>
       </c>
       <c r="D53" s="21">
         <f>SUM(C3:C54)</f>
         <v>-1737.27</v>
       </c>
-      <c r="E53" s="28" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10">
+      <c r="E53" s="27" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11">
       <c r="A54" s="31"/>
-      <c r="B54" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="C54" s="27">
+      <c r="B54" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="C54" s="26">
         <v>10</v>
       </c>
       <c r="D54" s="30"/>
-      <c r="E54" s="28"/>
-    </row>
-    <row r="55" spans="1:10">
-      <c r="A55" s="25">
+      <c r="E54" s="27"/>
+    </row>
+    <row r="55" spans="1:11">
+      <c r="A55" s="24">
         <v>45509</v>
       </c>
-      <c r="B55" s="26"/>
+      <c r="B55" s="25"/>
       <c r="C55" s="32">
         <v>-10</v>
       </c>
@@ -3058,45 +3159,45 @@
         <f>SUM(C3:C56)</f>
         <v>-1737.27</v>
       </c>
-      <c r="E55" s="28" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10">
+      <c r="E55" s="27" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11">
       <c r="A56" s="31"/>
-      <c r="B56" s="26" t="s">
-        <v>34</v>
-      </c>
-      <c r="C56" s="27">
+      <c r="B56" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C56" s="26">
         <v>10</v>
       </c>
       <c r="D56" s="30"/>
-      <c r="E56" s="28"/>
-    </row>
-    <row r="57" spans="1:10">
-      <c r="A57" s="25">
+      <c r="E56" s="27"/>
+    </row>
+    <row r="57" spans="1:11">
+      <c r="A57" s="24">
         <v>45510</v>
       </c>
-      <c r="B57" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="C57" s="27">
+      <c r="B57" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="C57" s="26">
         <v>40</v>
       </c>
       <c r="D57" s="20">
         <f>SUM(C3:C57)</f>
         <v>-1697.27</v>
       </c>
-      <c r="E57" s="28"/>
-    </row>
-    <row r="58" spans="1:10">
-      <c r="A58" s="25">
+      <c r="E57" s="27"/>
+    </row>
+    <row r="58" spans="1:11">
+      <c r="A58" s="24">
         <v>45525</v>
       </c>
       <c r="B58" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="C58" s="27">
+        <v>15</v>
+      </c>
+      <c r="C58" s="26">
         <f>6+5+5+5+6+5+5+5+30</f>
         <v>72</v>
       </c>
@@ -3104,234 +3205,234 @@
         <f>SUM(C3:C58)</f>
         <v>-1625.27</v>
       </c>
-      <c r="E58" s="28" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10">
-      <c r="A59" s="25">
+      <c r="E58" s="27" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11">
+      <c r="A59" s="24">
         <v>45525</v>
       </c>
       <c r="B59" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="C59" s="27">
+        <v>19</v>
+      </c>
+      <c r="C59" s="26">
         <v>6</v>
       </c>
       <c r="D59" s="21">
         <f>SUM(C3:C59)</f>
         <v>-1619.27</v>
       </c>
-      <c r="E59" s="28"/>
-    </row>
-    <row r="60" spans="1:10">
-      <c r="A60" s="25">
+      <c r="E59" s="27"/>
+    </row>
+    <row r="60" spans="1:11">
+      <c r="A60" s="24">
         <v>45549</v>
       </c>
       <c r="B60" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="C60" s="27">
+        <v>15</v>
+      </c>
+      <c r="C60" s="26">
         <v>30</v>
       </c>
       <c r="D60" s="21">
         <f>SUM(C3:C61)</f>
         <v>-1569.27</v>
       </c>
-      <c r="E60" s="28" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10">
+      <c r="E60" s="27" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11">
       <c r="A61" s="29"/>
       <c r="B61" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="C61" s="27">
+        <v>19</v>
+      </c>
+      <c r="C61" s="26">
         <v>20</v>
       </c>
       <c r="D61" s="30"/>
-      <c r="E61" s="28"/>
-    </row>
-    <row r="62" spans="1:10">
+      <c r="E61" s="27"/>
+    </row>
+    <row r="62" spans="1:11">
       <c r="A62" s="31">
         <v>45551</v>
       </c>
       <c r="B62" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="C62" s="27">
+        <v>21</v>
+      </c>
+      <c r="C62" s="26">
         <v>17</v>
       </c>
       <c r="D62" s="21">
         <f>SUM(C3:C62)</f>
         <v>-1552.27</v>
       </c>
-      <c r="E62" s="28"/>
-    </row>
-    <row r="63" spans="1:10">
-      <c r="A63" s="25">
+      <c r="E62" s="27"/>
+    </row>
+    <row r="63" spans="1:11">
+      <c r="A63" s="24">
         <v>45552</v>
       </c>
       <c r="B63" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="C63" s="27">
+        <v>15</v>
+      </c>
+      <c r="C63" s="26">
         <v>40</v>
       </c>
       <c r="D63" s="21">
         <f>SUM(C3:C63)</f>
         <v>-1512.27</v>
       </c>
-      <c r="E63" s="28"/>
-    </row>
-    <row r="64" spans="1:10">
-      <c r="A64" s="25">
+      <c r="E63" s="27"/>
+    </row>
+    <row r="64" spans="1:11">
+      <c r="A64" s="24">
         <v>45555</v>
       </c>
       <c r="B64" s="33" t="s">
-        <v>41</v>
-      </c>
-      <c r="C64" s="27">
+        <v>42</v>
+      </c>
+      <c r="C64" s="26">
         <v>6</v>
       </c>
       <c r="D64" s="21">
         <f>SUM(C3:C65)</f>
         <v>-1486.27</v>
       </c>
-      <c r="E64" s="28"/>
+      <c r="E64" s="27"/>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="31"/>
       <c r="B65" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="C65" s="27">
+        <v>25</v>
+      </c>
+      <c r="C65" s="26">
         <v>20</v>
       </c>
       <c r="D65" s="30"/>
-      <c r="E65" s="28"/>
+      <c r="E65" s="27"/>
     </row>
     <row r="66" spans="1:5">
-      <c r="A66" s="25">
+      <c r="A66" s="24">
         <v>45584</v>
       </c>
       <c r="B66" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="C66" s="27">
+        <v>15</v>
+      </c>
+      <c r="C66" s="26">
         <v>30</v>
       </c>
       <c r="D66" s="21">
         <f>SUM(C3:C66)</f>
         <v>-1456.27</v>
       </c>
-      <c r="E66" s="28" t="s">
-        <v>35</v>
+      <c r="E66" s="27" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="67" spans="1:5">
-      <c r="A67" s="25">
+      <c r="A67" s="24">
         <v>45584</v>
       </c>
       <c r="B67" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="C67" s="27">
+        <v>19</v>
+      </c>
+      <c r="C67" s="26">
         <v>7</v>
       </c>
       <c r="D67" s="21">
         <f>SUM(C3:C67)</f>
         <v>-1449.27</v>
       </c>
-      <c r="E67" s="28"/>
+      <c r="E67" s="27"/>
     </row>
     <row r="68" spans="1:5">
-      <c r="A68" s="25">
+      <c r="A68" s="24">
         <v>45592</v>
       </c>
       <c r="B68" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="C68" s="27">
+        <v>15</v>
+      </c>
+      <c r="C68" s="26">
         <v>60</v>
       </c>
       <c r="D68" s="21">
         <f>SUM(C3:C68)</f>
         <v>-1389.27</v>
       </c>
-      <c r="E68" s="28" t="s">
-        <v>73</v>
+      <c r="E68" s="27" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="69" spans="1:5">
-      <c r="A69" s="25">
+      <c r="A69" s="24">
         <v>45597</v>
       </c>
       <c r="B69" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="C69" s="27">
+        <v>19</v>
+      </c>
+      <c r="C69" s="26">
         <v>5</v>
       </c>
       <c r="D69" s="21">
         <f>SUM(C3:C69)</f>
         <v>-1384.27</v>
       </c>
-      <c r="E69" s="28" t="s">
-        <v>35</v>
+      <c r="E69" s="27" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="70" spans="1:5">
-      <c r="A70" s="25">
+      <c r="A70" s="24">
         <v>45598</v>
       </c>
       <c r="B70" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="C70" s="27">
+        <v>15</v>
+      </c>
+      <c r="C70" s="26">
         <v>5</v>
       </c>
       <c r="D70" s="21">
         <f>SUM(C3:C70)</f>
         <v>-1379.27</v>
       </c>
-      <c r="E70" s="28" t="s">
-        <v>35</v>
+      <c r="E70" s="27" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="71" spans="1:5">
-      <c r="A71" s="25">
+      <c r="A71" s="24">
         <v>45612</v>
       </c>
       <c r="B71" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="C71" s="27">
+        <v>19</v>
+      </c>
+      <c r="C71" s="26">
         <v>5</v>
       </c>
       <c r="D71" s="21">
         <f>SUM(C3:C71)</f>
         <v>-1374.27</v>
       </c>
-      <c r="E71" s="28"/>
+      <c r="E71" s="27"/>
     </row>
     <row r="72" spans="1:5">
-      <c r="A72" s="25">
+      <c r="A72" s="24">
         <v>45619</v>
       </c>
       <c r="B72" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="C72" s="27">
+        <v>15</v>
+      </c>
+      <c r="C72" s="26">
         <v>15</v>
       </c>
       <c r="D72" s="21">
         <f>SUM(C3:C72)</f>
         <v>-1359.27</v>
       </c>
-      <c r="E72" s="28" t="s">
-        <v>35</v>
+      <c r="E72" s="27" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -3339,282 +3440,282 @@
         <v>45634</v>
       </c>
       <c r="B73" s="33" t="s">
-        <v>60</v>
-      </c>
-      <c r="C73" s="27">
+        <v>61</v>
+      </c>
+      <c r="C73" s="26">
         <v>5</v>
       </c>
       <c r="D73" s="21">
         <f>SUM(C3:C74)</f>
         <v>-1344.27</v>
       </c>
-      <c r="E73" s="28" t="s">
-        <v>35</v>
+      <c r="E73" s="27" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="17"/>
       <c r="B74" s="33" t="s">
-        <v>34</v>
-      </c>
-      <c r="C74" s="27">
+        <v>32</v>
+      </c>
+      <c r="C74" s="26">
         <v>10</v>
       </c>
       <c r="D74" s="30"/>
-      <c r="E74" s="28"/>
+      <c r="E74" s="27"/>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="17">
         <v>45649</v>
       </c>
       <c r="B75" s="33" t="s">
-        <v>48</v>
-      </c>
-      <c r="C75" s="27">
+        <v>49</v>
+      </c>
+      <c r="C75" s="26">
         <v>10</v>
       </c>
       <c r="D75" s="21">
         <f>SUM(C3:C75)</f>
         <v>-1334.27</v>
       </c>
-      <c r="E75" s="28"/>
+      <c r="E75" s="27"/>
     </row>
     <row r="76" spans="1:5">
-      <c r="A76" s="25">
+      <c r="A76" s="24">
         <v>45654</v>
       </c>
       <c r="B76" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="C76" s="27">
+        <v>19</v>
+      </c>
+      <c r="C76" s="26">
         <v>30</v>
       </c>
       <c r="D76" s="21">
         <f>SUM(C3:C76)</f>
         <v>-1304.27</v>
       </c>
-      <c r="E76" s="28"/>
+      <c r="E76" s="27"/>
     </row>
     <row r="77" spans="1:5">
-      <c r="A77" s="25">
+      <c r="A77" s="24">
         <v>45686</v>
       </c>
       <c r="B77" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="C77" s="27">
+        <v>15</v>
+      </c>
+      <c r="C77" s="26">
         <v>9</v>
       </c>
       <c r="D77" s="21">
         <f>SUM(C3:C77)</f>
         <v>-1295.27</v>
       </c>
-      <c r="E77" s="28" t="s">
-        <v>35</v>
+      <c r="E77" s="27" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="78" spans="1:5">
-      <c r="A78" s="25">
+      <c r="A78" s="24">
         <v>45697</v>
       </c>
       <c r="B78" s="33" t="s">
-        <v>69</v>
-      </c>
-      <c r="C78" s="27">
+        <v>70</v>
+      </c>
+      <c r="C78" s="26">
         <v>0.5</v>
       </c>
       <c r="D78" s="21">
         <f>SUM(C3:C78)</f>
         <v>-1294.77</v>
       </c>
-      <c r="E78" s="28"/>
+      <c r="E78" s="27"/>
     </row>
     <row r="79" spans="1:5">
-      <c r="A79" s="25">
+      <c r="A79" s="24">
         <v>45707</v>
       </c>
       <c r="B79" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="C79" s="27">
+        <v>62</v>
+      </c>
+      <c r="C79" s="26">
         <v>4.15</v>
       </c>
       <c r="D79" s="21">
         <f>SUM(C3:C79)</f>
         <v>-1290.62</v>
       </c>
-      <c r="E79" s="28"/>
+      <c r="E79" s="27"/>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="17">
         <v>45794</v>
       </c>
       <c r="B80" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="C80" s="27">
+        <v>69</v>
+      </c>
+      <c r="C80" s="26">
         <v>1</v>
       </c>
       <c r="D80" s="20">
         <f>SUM(C3:C80)</f>
         <v>-1289.62</v>
       </c>
-      <c r="E80" s="28"/>
+      <c r="E80" s="27"/>
     </row>
     <row r="81" spans="1:5">
-      <c r="A81" s="25">
+      <c r="A81" s="24">
         <v>45829</v>
       </c>
       <c r="B81" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="C81" s="27">
+        <v>21</v>
+      </c>
+      <c r="C81" s="26">
         <v>26.66</v>
       </c>
       <c r="D81" s="21">
         <f>SUM(C3:C81)</f>
         <v>-1262.96</v>
       </c>
-      <c r="E81" s="28"/>
+      <c r="E81" s="27"/>
     </row>
     <row r="82" spans="1:5">
-      <c r="A82" s="25">
+      <c r="A82" s="24">
         <v>45844</v>
       </c>
       <c r="B82" s="33" t="s">
-        <v>56</v>
-      </c>
-      <c r="C82" s="27">
+        <v>57</v>
+      </c>
+      <c r="C82" s="26">
         <v>2.48</v>
       </c>
       <c r="D82" s="21">
         <f>SUM(C3:C82)</f>
         <v>-1260.48</v>
       </c>
-      <c r="E82" s="28"/>
+      <c r="E82" s="27"/>
     </row>
     <row r="83" spans="1:5">
-      <c r="A83" s="25">
+      <c r="A83" s="24">
         <v>45860</v>
       </c>
       <c r="B83" s="33" t="s">
-        <v>52</v>
-      </c>
-      <c r="C83" s="27">
+        <v>54</v>
+      </c>
+      <c r="C83" s="26">
         <v>8</v>
       </c>
       <c r="D83" s="21">
         <f>SUM(C3:C83)</f>
         <v>-1252.48</v>
       </c>
-      <c r="E83" s="28"/>
+      <c r="E83" s="27"/>
     </row>
     <row r="84" spans="1:5">
-      <c r="A84" s="25">
+      <c r="A84" s="24">
         <v>45861</v>
       </c>
       <c r="B84" s="33" t="s">
-        <v>56</v>
-      </c>
-      <c r="C84" s="27">
+        <v>57</v>
+      </c>
+      <c r="C84" s="26">
         <v>0.5</v>
       </c>
       <c r="D84" s="21">
         <f>SUM(C3:C84)</f>
         <v>-1251.98</v>
       </c>
-      <c r="E84" s="28"/>
+      <c r="E84" s="27"/>
     </row>
     <row r="85" spans="1:5">
-      <c r="A85" s="25">
+      <c r="A85" s="24">
         <v>45865</v>
       </c>
       <c r="B85" s="33" t="s">
-        <v>37</v>
-      </c>
-      <c r="C85" s="27">
+        <v>35</v>
+      </c>
+      <c r="C85" s="26">
         <v>3</v>
       </c>
       <c r="D85" s="21">
         <f>SUM(C3:C85)</f>
         <v>-1248.98</v>
       </c>
-      <c r="E85" s="28"/>
+      <c r="E85" s="27"/>
     </row>
     <row r="86" spans="1:5">
-      <c r="A86" s="25">
+      <c r="A86" s="24">
         <v>45868</v>
       </c>
       <c r="B86" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="C86" s="27">
+        <v>28</v>
+      </c>
+      <c r="C86" s="26">
         <v>5.01</v>
       </c>
       <c r="D86" s="21">
         <f>SUM(C3:C86)</f>
         <v>-1243.97</v>
       </c>
-      <c r="E86" s="28"/>
+      <c r="E86" s="27"/>
     </row>
     <row r="87" spans="1:5">
-      <c r="A87" s="25">
+      <c r="A87" s="24">
         <v>45868</v>
       </c>
       <c r="B87" s="33" t="s">
-        <v>57</v>
-      </c>
-      <c r="C87" s="27">
+        <v>58</v>
+      </c>
+      <c r="C87" s="26">
         <v>6</v>
       </c>
       <c r="D87" s="21">
         <f>SUM(C3:C87)</f>
         <v>-1237.97</v>
       </c>
-      <c r="E87" s="28"/>
+      <c r="E87" s="27"/>
     </row>
     <row r="88" spans="1:5">
-      <c r="A88" s="25">
+      <c r="A88" s="24">
         <v>45877</v>
       </c>
       <c r="B88" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="C88" s="27">
+      <c r="C88" s="26">
         <v>5</v>
       </c>
       <c r="D88" s="21">
         <f>SUM(C3:C88)</f>
         <v>-1232.97</v>
       </c>
-      <c r="E88" s="28" t="s">
+      <c r="E88" s="27" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89" s="24">
+        <v>45878</v>
+      </c>
+      <c r="B89" s="33" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="89" spans="1:5">
-      <c r="A89" s="25">
-        <v>45878</v>
-      </c>
-      <c r="B89" s="33" t="s">
-        <v>37</v>
-      </c>
-      <c r="C89" s="27">
+      <c r="C89" s="26">
         <v>0.01</v>
       </c>
       <c r="D89" s="21">
         <f>SUM(C3:C89)</f>
         <v>-1232.96</v>
       </c>
-      <c r="E89" s="28"/>
+      <c r="E89" s="27"/>
     </row>
     <row r="90" spans="1:5">
-      <c r="A90" s="25">
+      <c r="A90" s="24">
         <v>45879</v>
       </c>
       <c r="B90" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="C90" s="27">
+      <c r="C90" s="26">
         <v>26</v>
       </c>
       <c r="D90" s="21">
@@ -3624,13 +3725,13 @@
       <c r="E90" s="34"/>
     </row>
     <row r="91" spans="1:5">
-      <c r="A91" s="25">
+      <c r="A91" s="24">
         <v>45881</v>
       </c>
       <c r="B91" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="C91" s="27">
+        <v>15</v>
+      </c>
+      <c r="C91" s="26">
         <v>5</v>
       </c>
       <c r="D91" s="21">
@@ -3638,7 +3739,7 @@
         <v>-1201.96</v>
       </c>
       <c r="E91" s="34" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -3646,9 +3747,9 @@
         <v>45885</v>
       </c>
       <c r="B92" s="33" t="s">
-        <v>70</v>
-      </c>
-      <c r="C92" s="27">
+        <v>71</v>
+      </c>
+      <c r="C92" s="26">
         <v>0.5</v>
       </c>
       <c r="D92" s="21">
@@ -3660,9 +3761,9 @@
     <row r="93" spans="1:5">
       <c r="A93" s="17"/>
       <c r="B93" s="33" t="s">
-        <v>62</v>
-      </c>
-      <c r="C93" s="27">
+        <v>63</v>
+      </c>
+      <c r="C93" s="26">
         <v>6</v>
       </c>
       <c r="D93" s="30"/>
@@ -3671,22 +3772,22 @@
     <row r="94" spans="1:5">
       <c r="A94" s="17"/>
       <c r="B94" s="33" t="s">
-        <v>56</v>
-      </c>
-      <c r="C94" s="27">
+        <v>57</v>
+      </c>
+      <c r="C94" s="26">
         <v>4</v>
       </c>
       <c r="D94" s="30"/>
       <c r="E94" s="34"/>
     </row>
     <row r="95" spans="1:5">
-      <c r="A95" s="25">
+      <c r="A95" s="24">
         <v>45886</v>
       </c>
       <c r="B95" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="C95" s="27">
+        <v>15</v>
+      </c>
+      <c r="C95" s="26">
         <v>5</v>
       </c>
       <c r="D95" s="21">
@@ -3694,17 +3795,17 @@
         <v>-1186.46</v>
       </c>
       <c r="E95" s="34" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
+      <c r="A96" s="24">
+        <v>45894</v>
+      </c>
+      <c r="B96" s="33" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="96" spans="1:5">
-      <c r="A96" s="25">
-        <v>45894</v>
-      </c>
-      <c r="B96" s="33" t="s">
-        <v>37</v>
-      </c>
-      <c r="C96" s="27">
+      <c r="C96" s="26">
         <v>1</v>
       </c>
       <c r="D96" s="21">
@@ -3714,13 +3815,13 @@
       <c r="E96" s="34"/>
     </row>
     <row r="97" spans="1:5">
-      <c r="A97" s="25">
+      <c r="A97" s="24">
         <v>45905</v>
       </c>
       <c r="B97" s="33" t="s">
-        <v>55</v>
-      </c>
-      <c r="C97" s="27">
+        <v>56</v>
+      </c>
+      <c r="C97" s="26">
         <v>7.33</v>
       </c>
       <c r="D97" s="21">
@@ -3730,13 +3831,13 @@
       <c r="E97" s="34"/>
     </row>
     <row r="98" spans="1:5">
-      <c r="A98" s="25">
+      <c r="A98" s="24">
         <v>45907</v>
       </c>
       <c r="B98" s="33" t="s">
-        <v>37</v>
-      </c>
-      <c r="C98" s="27">
+        <v>35</v>
+      </c>
+      <c r="C98" s="26">
         <v>2</v>
       </c>
       <c r="D98" s="21">
@@ -3748,9 +3849,9 @@
     <row r="99" spans="1:5">
       <c r="A99" s="31"/>
       <c r="B99" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="C99" s="27">
+        <v>34</v>
+      </c>
+      <c r="C99" s="26">
         <v>2</v>
       </c>
       <c r="D99" s="30"/>
@@ -3759,9 +3860,9 @@
     <row r="100" spans="1:5">
       <c r="A100" s="31"/>
       <c r="B100" s="33" t="s">
-        <v>63</v>
-      </c>
-      <c r="C100" s="27">
+        <v>64</v>
+      </c>
+      <c r="C100" s="26">
         <v>2</v>
       </c>
       <c r="D100" s="30"/>
@@ -3770,9 +3871,9 @@
     <row r="101" spans="1:5">
       <c r="A101" s="31"/>
       <c r="B101" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="C101" s="27">
+        <v>28</v>
+      </c>
+      <c r="C101" s="26">
         <v>2</v>
       </c>
       <c r="D101" s="30"/>
@@ -3781,16 +3882,16 @@
     <row r="102" spans="1:5">
       <c r="A102" s="31"/>
       <c r="B102" s="33" t="s">
-        <v>67</v>
-      </c>
-      <c r="C102" s="27">
+        <v>68</v>
+      </c>
+      <c r="C102" s="26">
         <v>2</v>
       </c>
       <c r="D102" s="30"/>
       <c r="E102" s="34"/>
     </row>
     <row r="103" spans="1:5">
-      <c r="A103" s="25">
+      <c r="A103" s="24">
         <v>45915</v>
       </c>
       <c r="B103" s="33"/>
@@ -3802,17 +3903,17 @@
         <v>-1298.13</v>
       </c>
       <c r="E103" s="34" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="104" spans="1:5">
-      <c r="A104" s="25">
+      <c r="A104" s="24">
         <v>45916</v>
       </c>
       <c r="B104" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="C104" s="27">
+      <c r="C104" s="26">
         <v>6</v>
       </c>
       <c r="D104" s="21">
@@ -3820,17 +3921,17 @@
         <v>-1292.13</v>
       </c>
       <c r="E104" s="34" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="105" spans="1:5">
-      <c r="A105" s="25">
+      <c r="A105" s="24">
         <v>45925</v>
       </c>
       <c r="B105" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="C105" s="27">
+        <v>28</v>
+      </c>
+      <c r="C105" s="26">
         <v>10</v>
       </c>
       <c r="D105" s="21">
@@ -3840,13 +3941,13 @@
       <c r="E105" s="34"/>
     </row>
     <row r="106" spans="1:5">
-      <c r="A106" s="25">
+      <c r="A106" s="24">
         <v>45930</v>
       </c>
       <c r="B106" s="33" t="s">
-        <v>40</v>
-      </c>
-      <c r="C106" s="27">
+        <v>38</v>
+      </c>
+      <c r="C106" s="26">
         <v>15</v>
       </c>
       <c r="D106" s="21">
@@ -3856,13 +3957,13 @@
       <c r="E106" s="34"/>
     </row>
     <row r="107" spans="1:5">
-      <c r="A107" s="25">
+      <c r="A107" s="24">
         <v>45934</v>
       </c>
       <c r="B107" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="C107" s="27">
+        <v>28</v>
+      </c>
+      <c r="C107" s="26">
         <v>2</v>
       </c>
       <c r="D107" s="21">
@@ -3874,9 +3975,9 @@
     <row r="108" spans="1:5">
       <c r="A108" s="31"/>
       <c r="B108" s="33" t="s">
-        <v>63</v>
-      </c>
-      <c r="C108" s="27">
+        <v>64</v>
+      </c>
+      <c r="C108" s="26">
         <v>2</v>
       </c>
       <c r="D108" s="21">
@@ -3888,9 +3989,9 @@
     <row r="109" spans="1:5">
       <c r="A109" s="31"/>
       <c r="B109" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="C109" s="27">
+        <v>34</v>
+      </c>
+      <c r="C109" s="26">
         <v>0.45</v>
       </c>
       <c r="D109" s="21">
@@ -3900,13 +4001,13 @@
       <c r="E109" s="34"/>
     </row>
     <row r="110" spans="1:5">
-      <c r="A110" s="25">
+      <c r="A110" s="24">
         <v>45965</v>
       </c>
       <c r="B110" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="C110" s="27">
+        <v>17</v>
+      </c>
+      <c r="C110" s="26">
         <v>60</v>
       </c>
       <c r="D110" s="21">
@@ -3916,13 +4017,13 @@
       <c r="E110" s="34"/>
     </row>
     <row r="111" spans="1:5">
-      <c r="A111" s="25">
+      <c r="A111" s="24">
         <v>45968</v>
       </c>
       <c r="B111" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="C111" s="27">
+      <c r="C111" s="26">
         <v>5</v>
       </c>
       <c r="D111" s="21">
@@ -3932,13 +4033,13 @@
       <c r="E111" s="34"/>
     </row>
     <row r="112" spans="1:5">
-      <c r="A112" s="25">
+      <c r="A112" s="24">
         <v>45969</v>
       </c>
       <c r="B112" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="C112" s="27">
+        <v>28</v>
+      </c>
+      <c r="C112" s="26">
         <v>6</v>
       </c>
       <c r="D112" s="21">
@@ -3948,13 +4049,13 @@
       <c r="E112" s="34"/>
     </row>
     <row r="113" spans="1:5">
-      <c r="A113" s="25">
+      <c r="A113" s="24">
         <v>45972</v>
       </c>
       <c r="B113" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="C113" s="27">
+        <v>17</v>
+      </c>
+      <c r="C113" s="26">
         <v>60</v>
       </c>
       <c r="D113" s="21">
@@ -3964,13 +4065,13 @@
       <c r="E113" s="34"/>
     </row>
     <row r="114" spans="1:5">
-      <c r="A114" s="25">
+      <c r="A114" s="24">
         <v>45975</v>
       </c>
       <c r="B114" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="C114" s="27">
+      <c r="C114" s="26">
         <v>37</v>
       </c>
       <c r="D114" s="21">
@@ -3980,13 +4081,13 @@
       <c r="E114" s="34"/>
     </row>
     <row r="115" spans="1:5">
-      <c r="A115" s="25">
+      <c r="A115" s="24">
         <v>45976</v>
       </c>
       <c r="B115" s="33" t="s">
-        <v>65</v>
-      </c>
-      <c r="C115" s="27">
+        <v>66</v>
+      </c>
+      <c r="C115" s="26">
         <v>2.5</v>
       </c>
       <c r="D115" s="21">
@@ -3996,13 +4097,13 @@
       <c r="E115" s="34"/>
     </row>
     <row r="116" spans="1:5">
-      <c r="A116" s="25">
+      <c r="A116" s="24">
         <v>45980</v>
       </c>
       <c r="B116" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="C116" s="27">
+        <v>17</v>
+      </c>
+      <c r="C116" s="26">
         <v>20</v>
       </c>
       <c r="D116" s="21">
@@ -4012,13 +4113,13 @@
       <c r="E116" s="34"/>
     </row>
     <row r="117" spans="1:5">
-      <c r="A117" s="25">
+      <c r="A117" s="24">
         <v>45990</v>
       </c>
       <c r="B117" s="33" t="s">
-        <v>37</v>
-      </c>
-      <c r="C117" s="27">
+        <v>35</v>
+      </c>
+      <c r="C117" s="26">
         <v>1</v>
       </c>
       <c r="D117" s="21">
@@ -4028,13 +4129,13 @@
       <c r="E117" s="34"/>
     </row>
     <row r="118" spans="1:5">
-      <c r="A118" s="25">
+      <c r="A118" s="24">
         <v>46012</v>
       </c>
       <c r="B118" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="C118" s="27">
+        <v>17</v>
+      </c>
+      <c r="C118" s="26">
         <v>10</v>
       </c>
       <c r="D118" s="21">
@@ -4044,13 +4145,13 @@
       <c r="E118" s="34"/>
     </row>
     <row r="119" spans="1:5">
-      <c r="A119" s="25">
+      <c r="A119" s="24">
         <v>46029</v>
       </c>
       <c r="B119" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="C119" s="27">
+        <v>28</v>
+      </c>
+      <c r="C119" s="26">
         <v>16</v>
       </c>
       <c r="D119" s="21">
@@ -4060,13 +4161,13 @@
       <c r="E119" s="34"/>
     </row>
     <row r="120" spans="1:5">
-      <c r="A120" s="25">
+      <c r="A120" s="24">
         <v>46031</v>
       </c>
       <c r="B120" s="33" t="s">
-        <v>37</v>
-      </c>
-      <c r="C120" s="27">
+        <v>35</v>
+      </c>
+      <c r="C120" s="26">
         <v>2</v>
       </c>
       <c r="D120" s="21">
@@ -4076,13 +4177,13 @@
       <c r="E120" s="34"/>
     </row>
     <row r="121" spans="1:5">
-      <c r="A121" s="25">
+      <c r="A121" s="24">
         <v>46038</v>
       </c>
       <c r="B121" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="C121" s="27">
+        <v>23</v>
+      </c>
+      <c r="C121" s="26">
         <v>66</v>
       </c>
       <c r="D121" s="21">
@@ -4092,13 +4193,13 @@
       <c r="E121" s="34"/>
     </row>
     <row r="122" spans="1:5">
-      <c r="A122" s="25">
+      <c r="A122" s="24">
         <v>46039</v>
       </c>
       <c r="B122" s="33" t="s">
-        <v>37</v>
-      </c>
-      <c r="C122" s="27">
+        <v>35</v>
+      </c>
+      <c r="C122" s="26">
         <v>1</v>
       </c>
       <c r="D122" s="21">
@@ -4108,13 +4209,13 @@
       <c r="E122" s="34"/>
     </row>
     <row r="123" spans="1:5">
-      <c r="A123" s="25">
+      <c r="A123" s="24">
         <v>46047</v>
       </c>
       <c r="B123" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="C123" s="27">
+        <v>23</v>
+      </c>
+      <c r="C123" s="26">
         <v>7</v>
       </c>
       <c r="D123" s="21">
@@ -4126,9 +4227,9 @@
     <row r="124" spans="1:5">
       <c r="A124" s="31"/>
       <c r="B124" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="C124" s="27">
+        <v>28</v>
+      </c>
+      <c r="C124" s="26">
         <v>11</v>
       </c>
       <c r="D124" s="21">
@@ -4138,13 +4239,13 @@
       <c r="E124" s="34"/>
     </row>
     <row r="125" spans="1:5">
-      <c r="A125" s="25">
+      <c r="A125" s="24">
         <v>46054</v>
       </c>
       <c r="B125" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="C125" s="27">
+        <v>15</v>
+      </c>
+      <c r="C125" s="26">
         <v>5</v>
       </c>
       <c r="D125" s="21">
@@ -4152,17 +4253,17 @@
         <v>-953.18</v>
       </c>
       <c r="E125" s="34" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="126" spans="1:5">
-      <c r="A126" s="25">
+      <c r="A126" s="24">
         <v>46055</v>
       </c>
       <c r="B126" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="C126" s="27">
+        <v>23</v>
+      </c>
+      <c r="C126" s="26">
         <v>36</v>
       </c>
       <c r="D126" s="21">
@@ -4172,13 +4273,13 @@
       <c r="E126" s="34"/>
     </row>
     <row r="127" spans="1:5">
-      <c r="A127" s="25">
+      <c r="A127" s="24">
         <v>46057</v>
       </c>
       <c r="B127" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="C127" s="27">
+        <v>15</v>
+      </c>
+      <c r="C127" s="26">
         <v>5</v>
       </c>
       <c r="D127" s="21">
@@ -4186,7 +4287,7 @@
         <v>-912.18</v>
       </c>
       <c r="E127" s="34" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="128" spans="1:5">
@@ -4194,9 +4295,9 @@
         <v>46068</v>
       </c>
       <c r="B128" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="C128" s="27">
+        <v>23</v>
+      </c>
+      <c r="C128" s="26">
         <v>78</v>
       </c>
       <c r="D128" s="21">
@@ -4208,9 +4309,9 @@
     <row r="129" spans="1:5">
       <c r="A129" s="36"/>
       <c r="B129" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="C129" s="27">
+        <v>17</v>
+      </c>
+      <c r="C129" s="26">
         <v>30</v>
       </c>
       <c r="D129" s="21">
@@ -4220,13 +4321,13 @@
       <c r="E129" s="34"/>
     </row>
     <row r="130" spans="1:5">
-      <c r="A130" s="25">
+      <c r="A130" s="24">
         <v>46069</v>
       </c>
       <c r="B130" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="C130" s="27">
+        <v>34</v>
+      </c>
+      <c r="C130" s="26">
         <v>5</v>
       </c>
       <c r="D130" s="21">
@@ -4238,9 +4339,9 @@
     <row r="131" spans="1:5">
       <c r="A131" s="31"/>
       <c r="B131" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="C131" s="27">
+        <v>23</v>
+      </c>
+      <c r="C131" s="26">
         <v>8</v>
       </c>
       <c r="D131" s="21">
@@ -4252,9 +4353,9 @@
     <row r="132" spans="1:5">
       <c r="A132" s="31"/>
       <c r="B132" s="33" t="s">
-        <v>49</v>
-      </c>
-      <c r="C132" s="27">
+        <v>50</v>
+      </c>
+      <c r="C132" s="26">
         <v>10</v>
       </c>
       <c r="D132" s="21">
@@ -4264,13 +4365,13 @@
       <c r="E132" s="34"/>
     </row>
     <row r="133" spans="1:5">
-      <c r="A133" s="25">
+      <c r="A133" s="24">
         <v>46070</v>
       </c>
       <c r="B133" s="33" t="s">
-        <v>28</v>
-      </c>
-      <c r="C133" s="27">
+        <v>26</v>
+      </c>
+      <c r="C133" s="26">
         <v>8.32</v>
       </c>
       <c r="D133" s="21">
@@ -4282,9 +4383,9 @@
     <row r="134" spans="1:5">
       <c r="A134" s="31"/>
       <c r="B134" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="C134" s="27">
+        <v>17</v>
+      </c>
+      <c r="C134" s="26">
         <v>10</v>
       </c>
       <c r="D134" s="21">
@@ -4298,9 +4399,9 @@
         <v>46074</v>
       </c>
       <c r="B135" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="C135" s="27">
+        <v>44</v>
+      </c>
+      <c r="C135" s="26">
         <v>1.5</v>
       </c>
       <c r="D135" s="21">
@@ -4310,13 +4411,13 @@
       <c r="E135" s="34"/>
     </row>
     <row r="136" spans="1:5">
-      <c r="A136" s="25">
+      <c r="A136" s="24">
         <v>46079</v>
       </c>
       <c r="B136" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="C136" s="27">
+        <v>15</v>
+      </c>
+      <c r="C136" s="26">
         <v>25</v>
       </c>
       <c r="D136" s="21">
@@ -4324,17 +4425,17 @@
         <v>-736.36</v>
       </c>
       <c r="E136" s="34" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="137" spans="1:5">
-      <c r="A137" s="25">
+      <c r="A137" s="24">
         <v>46085</v>
       </c>
       <c r="B137" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="C137" s="27">
+        <v>34</v>
+      </c>
+      <c r="C137" s="26">
         <v>10</v>
       </c>
       <c r="D137" s="21">
@@ -4344,13 +4445,13 @@
       <c r="E137" s="34"/>
     </row>
     <row r="138" spans="1:5">
-      <c r="A138" s="25">
+      <c r="A138" s="24">
         <v>46123</v>
       </c>
       <c r="B138" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="C138" s="27">
+        <v>15</v>
+      </c>
+      <c r="C138" s="26">
         <v>70</v>
       </c>
       <c r="D138" s="21">
@@ -4358,17 +4459,17 @@
         <v>-656.36</v>
       </c>
       <c r="E138" s="34" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="139" spans="1:5">
-      <c r="A139" s="25">
+      <c r="A139" s="24">
         <v>46130</v>
       </c>
       <c r="B139" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="C139" s="27">
+        <v>44</v>
+      </c>
+      <c r="C139" s="26">
         <v>3</v>
       </c>
       <c r="D139" s="21">
@@ -4378,7 +4479,7 @@
       <c r="E139" s="34"/>
     </row>
     <row r="140" spans="1:5">
-      <c r="A140" s="25">
+      <c r="A140" s="24">
         <v>46135</v>
       </c>
       <c r="B140" s="33"/>
@@ -4390,17 +4491,17 @@
         <v>-3151.15</v>
       </c>
       <c r="E140" s="34" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="141" spans="1:5">
-      <c r="A141" s="25">
+      <c r="A141" s="24">
         <v>46136</v>
       </c>
       <c r="B141" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="C141" s="27">
+        <v>15</v>
+      </c>
+      <c r="C141" s="26">
         <v>15</v>
       </c>
       <c r="D141" s="21">
@@ -4408,17 +4509,17 @@
         <v>-3136.15</v>
       </c>
       <c r="E141" s="34" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="142" spans="1:5">
-      <c r="A142" s="25">
+      <c r="A142" s="24">
         <v>46141</v>
       </c>
       <c r="B142" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="C142" s="27">
+        <v>17</v>
+      </c>
+      <c r="C142" s="26">
         <v>10</v>
       </c>
       <c r="D142" s="21">
@@ -4430,9 +4531,9 @@
     <row r="143" spans="1:5">
       <c r="A143" s="31"/>
       <c r="B143" s="33" t="s">
-        <v>28</v>
-      </c>
-      <c r="C143" s="27">
+        <v>26</v>
+      </c>
+      <c r="C143" s="26">
         <v>10</v>
       </c>
       <c r="D143" s="21">
@@ -4442,13 +4543,13 @@
       <c r="E143" s="34"/>
     </row>
     <row r="144" spans="1:5">
-      <c r="A144" s="25">
+      <c r="A144" s="24">
         <v>46144</v>
       </c>
       <c r="B144" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="C144" s="27">
+        <v>34</v>
+      </c>
+      <c r="C144" s="26">
         <v>1</v>
       </c>
       <c r="D144" s="21">
@@ -4458,13 +4559,13 @@
       <c r="E144" s="34"/>
     </row>
     <row r="145" spans="1:5">
-      <c r="A145" s="25">
+      <c r="A145" s="24">
         <v>46145</v>
       </c>
       <c r="B145" s="33" t="s">
-        <v>50</v>
-      </c>
-      <c r="C145" s="27">
+        <v>52</v>
+      </c>
+      <c r="C145" s="26">
         <v>10</v>
       </c>
       <c r="D145" s="21">
@@ -4476,9 +4577,9 @@
     <row r="146" spans="1:5">
       <c r="A146" s="31"/>
       <c r="B146" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="C146" s="27">
+        <v>44</v>
+      </c>
+      <c r="C146" s="26">
         <v>6</v>
       </c>
       <c r="D146" s="21">
@@ -4488,13 +4589,13 @@
       <c r="E146" s="34"/>
     </row>
     <row r="147" spans="1:5">
-      <c r="A147" s="25">
+      <c r="A147" s="24">
         <v>46146</v>
       </c>
       <c r="B147" s="33" t="s">
-        <v>28</v>
-      </c>
-      <c r="C147" s="27">
+        <v>26</v>
+      </c>
+      <c r="C147" s="26">
         <v>20</v>
       </c>
       <c r="D147" s="21">
@@ -4504,13 +4605,13 @@
       <c r="E147" s="34"/>
     </row>
     <row r="148" spans="1:5">
-      <c r="A148" s="25">
+      <c r="A148" s="24">
         <v>46158</v>
       </c>
       <c r="B148" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="C148" s="27">
+        <v>15</v>
+      </c>
+      <c r="C148" s="26">
         <v>20</v>
       </c>
       <c r="D148" s="21">
@@ -4518,17 +4619,17 @@
         <v>-3059.15</v>
       </c>
       <c r="E148" s="34" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="149" spans="1:5">
-      <c r="A149" s="25">
+      <c r="A149" s="24">
         <v>46160</v>
       </c>
       <c r="B149" s="33" t="s">
-        <v>58</v>
-      </c>
-      <c r="C149" s="27">
+        <v>59</v>
+      </c>
+      <c r="C149" s="26">
         <v>5.04</v>
       </c>
       <c r="D149" s="21">
@@ -4538,13 +4639,13 @@
       <c r="E149" s="34"/>
     </row>
     <row r="150" spans="1:5">
-      <c r="A150" s="25">
+      <c r="A150" s="24">
         <v>46179</v>
       </c>
       <c r="B150" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="C150" s="27">
+        <v>15</v>
+      </c>
+      <c r="C150" s="26">
         <v>30</v>
       </c>
       <c r="D150" s="21">
@@ -4552,17 +4653,17 @@
         <v>-3024.11</v>
       </c>
       <c r="E150" s="34" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="151" spans="1:5">
-      <c r="A151" s="25">
+      <c r="A151" s="24">
         <v>46184</v>
       </c>
       <c r="B151" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="C151" s="27">
+        <v>17</v>
+      </c>
+      <c r="C151" s="26">
         <v>10</v>
       </c>
       <c r="D151" s="21">
@@ -4572,13 +4673,13 @@
       <c r="E151" s="34"/>
     </row>
     <row r="152" spans="1:5">
-      <c r="A152" s="25">
+      <c r="A152" s="24">
         <v>46192</v>
       </c>
       <c r="B152" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="C152" s="27">
+        <v>15</v>
+      </c>
+      <c r="C152" s="26">
         <v>20</v>
       </c>
       <c r="D152" s="21">
@@ -4586,17 +4687,17 @@
         <v>-2994.11</v>
       </c>
       <c r="E152" s="34" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="153" spans="1:5">
-      <c r="A153" s="25">
+      <c r="A153" s="24">
         <v>46193</v>
       </c>
       <c r="B153" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="C153" s="27">
+        <v>17</v>
+      </c>
+      <c r="C153" s="26">
         <v>50</v>
       </c>
       <c r="D153" s="21">
@@ -4608,9 +4709,9 @@
     <row r="154" spans="1:5">
       <c r="A154" s="31"/>
       <c r="B154" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="C154" s="27">
+        <v>15</v>
+      </c>
+      <c r="C154" s="26">
         <v>10</v>
       </c>
       <c r="D154" s="21">
@@ -4618,17 +4719,17 @@
         <v>-2934.11</v>
       </c>
       <c r="E154" s="34" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="155" spans="1:5">
-      <c r="A155" s="25">
+      <c r="A155" s="24">
         <v>46196</v>
       </c>
       <c r="B155" s="33" t="s">
-        <v>28</v>
-      </c>
-      <c r="C155" s="27">
+        <v>26</v>
+      </c>
+      <c r="C155" s="26">
         <v>25</v>
       </c>
       <c r="D155" s="21">
@@ -4638,13 +4739,13 @@
       <c r="E155" s="34"/>
     </row>
     <row r="156" spans="1:5">
-      <c r="A156" s="25">
+      <c r="A156" s="24">
         <v>46204</v>
       </c>
       <c r="B156" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="C156" s="27">
+        <v>15</v>
+      </c>
+      <c r="C156" s="26">
         <v>20</v>
       </c>
       <c r="D156" s="21">
@@ -4652,17 +4753,17 @@
         <v>-2889.11</v>
       </c>
       <c r="E156" s="34" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="157" spans="1:5">
-      <c r="A157" s="25">
+      <c r="A157" s="24">
         <v>46205</v>
       </c>
       <c r="B157" s="33" t="s">
-        <v>54</v>
-      </c>
-      <c r="C157" s="27">
+        <v>55</v>
+      </c>
+      <c r="C157" s="26">
         <v>8</v>
       </c>
       <c r="D157" s="21">
@@ -4674,9 +4775,9 @@
     <row r="158" spans="1:5">
       <c r="A158" s="31"/>
       <c r="B158" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="C158" s="27">
+        <v>17</v>
+      </c>
+      <c r="C158" s="26">
         <v>240</v>
       </c>
       <c r="D158" s="21">
@@ -4688,9 +4789,9 @@
     <row r="159" spans="1:5">
       <c r="A159" s="31"/>
       <c r="B159" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="C159" s="27">
+        <v>15</v>
+      </c>
+      <c r="C159" s="26">
         <v>10</v>
       </c>
       <c r="D159" s="21">
@@ -4698,17 +4799,17 @@
         <v>-2631.11</v>
       </c>
       <c r="E159" s="34" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="160" spans="1:5">
-      <c r="A160" s="25">
+      <c r="A160" s="24">
         <v>46206</v>
       </c>
       <c r="B160" s="33" t="s">
-        <v>28</v>
-      </c>
-      <c r="C160" s="27">
+        <v>26</v>
+      </c>
+      <c r="C160" s="26">
         <v>5</v>
       </c>
       <c r="D160" s="21">
@@ -4716,17 +4817,17 @@
         <v>-2626.11</v>
       </c>
       <c r="E160" s="34" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="161" spans="1:5">
-      <c r="A161" s="25">
+      <c r="A161" s="24">
         <v>46210</v>
       </c>
       <c r="B161" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="C161" s="27">
+        <v>23</v>
+      </c>
+      <c r="C161" s="26">
         <v>33</v>
       </c>
       <c r="D161" s="21">
@@ -4736,42 +4837,58 @@
       <c r="E161" s="34"/>
     </row>
     <row r="162" spans="1:5">
-      <c r="A162" s="37">
+      <c r="A162" s="24">
         <v>46219</v>
       </c>
-      <c r="B162" s="38" t="s">
+      <c r="B162" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="C162" s="39">
+      <c r="C162" s="26">
         <v>121.04</v>
       </c>
       <c r="D162" s="21">
         <f>SUM(C3:C162)</f>
         <v>-2472.07</v>
       </c>
-      <c r="E162" s="40"/>
-    </row>
-    <row r="163" ht="14.25" spans="1:5">
-      <c r="A163" s="41"/>
-      <c r="B163" s="42"/>
-      <c r="C163" s="43"/>
-      <c r="D163" s="43"/>
-      <c r="E163" s="44"/>
+      <c r="E162" s="34"/>
+    </row>
+    <row r="163" spans="1:5">
+      <c r="A163" s="24">
+        <v>46305</v>
+      </c>
+      <c r="B163" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="C163" s="26">
+        <v>12</v>
+      </c>
+      <c r="D163" s="21">
+        <f>SUM(C3:C163)</f>
+        <v>-2460.07</v>
+      </c>
+      <c r="E163" s="34"/>
     </row>
     <row r="164" spans="1:5">
-      <c r="A164" s="45" t="s">
-        <v>76</v>
-      </c>
-      <c r="B164" s="45"/>
-      <c r="C164" s="45"/>
-      <c r="D164" s="45"/>
-      <c r="E164" s="45"/>
+      <c r="A164" s="37"/>
+      <c r="B164" s="38"/>
+      <c r="C164" s="39"/>
+      <c r="D164" s="39"/>
+      <c r="E164" s="40"/>
+    </row>
+    <row r="165" spans="1:5">
+      <c r="A165" s="41" t="s">
+        <v>77</v>
+      </c>
+      <c r="B165" s="41"/>
+      <c r="C165" s="41"/>
+      <c r="D165" s="41"/>
+      <c r="E165" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="42">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="G1:K1"/>
-    <mergeCell ref="A164:E164"/>
+    <mergeCell ref="A165:E165"/>
     <mergeCell ref="A3:A7"/>
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="A23:A24"/>
@@ -4812,8 +4929,8 @@
     <mergeCell ref="D92:D94"/>
     <mergeCell ref="D98:D102"/>
   </mergeCells>
-  <conditionalFormatting sqref="I25">
-    <cfRule type="dataBar" priority="19">
+  <conditionalFormatting sqref="I26">
+    <cfRule type="dataBar" priority="20">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4821,12 +4938,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0516d668-bde6-4820-9c21-bd9bfe863a0b}</x14:id>
+          <x14:id>{1e706b11-9071-4342-b703-3936458eca29}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I$1:I$1048576">
+  <conditionalFormatting sqref="I3:I52">
     <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="min"/>
@@ -4835,13 +4952,13 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f9af9851-3b3f-4134-b8de-49494a92d3d3}</x14:id>
+          <x14:id>{702023a5-6b76-4725-ab5a-e73a1a96687b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D1:D18 D20:D23 D25:D26 D28:D42 D44:D45 D47:D48 D50:D51 D53 D55 D57:D60 D62:D64 D66:D73 D75:D92 D95:D98 D103:D163 D165:D1048576">
-    <cfRule type="colorScale" priority="81">
+  <conditionalFormatting sqref="D1:D18 D20:D23 D25:D26 D28:D42 D44:D45 D47:D48 D50:D51 D53 D55 D57:D60 D62:D64 D66:D73 D75:D92 D95:D98 D103:D164 D166:D1048576">
+    <cfRule type="colorScale" priority="82">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4853,7 +4970,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G1 G2:I2">
-    <cfRule type="dataBar" priority="92">
+    <cfRule type="dataBar" priority="93">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4861,12 +4978,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d8c93784-4d59-402c-bd64-0ae50c373c64}</x14:id>
+          <x14:id>{f2859ee8-d1f3-48c2-94dc-cdab6bbd66ea}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I26 I28:I1048576">
+  <conditionalFormatting sqref="I1:I17 I19:I1048576">
     <cfRule type="dataBar" priority="2">
       <dataBar>
         <cfvo type="min"/>
@@ -4875,13 +4992,13 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c6782148-85aa-4485-ac94-2bb6567ca129}</x14:id>
+          <x14:id>{c2fdf4eb-9309-4790-9577-64d0375898cf}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I24 I26 I28:I1048576">
-    <cfRule type="dataBar" priority="20">
+  <conditionalFormatting sqref="I1:I17 I29:I1048576 I19:I27">
+    <cfRule type="dataBar" priority="3">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4889,13 +5006,13 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1f04ca4b-f0e5-4ce8-82e6-d45a7293206e}</x14:id>
+          <x14:id>{32a56779-809f-48ef-abe5-6499028ee3b1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I18 I28:I1048576 I20:I24 I26">
-    <cfRule type="dataBar" priority="22">
+  <conditionalFormatting sqref="I1:I17 I29:I1048576 I27 I19:I25">
+    <cfRule type="dataBar" priority="21">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4903,12 +5020,40 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{580211c7-d112-48e0-b9ff-a7e120b3cd1e}</x14:id>
+          <x14:id>{4e5517ac-ac71-4595-b8ea-b3ebf3c4f558}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I9 I20:I24 I11:I18 I28:I1048576 I26">
+  <conditionalFormatting sqref="I1:I9 I29:I1048576 I11:I17 I27 I19 I21:I25">
+    <cfRule type="dataBar" priority="24">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{d437ab4f-284f-4dce-87a8-883f66c3d40c}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I1:I9 I29:I1048576 I11:I17 I27 I19 I21:I24">
+    <cfRule type="dataBar" priority="25">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{7bd851aa-fab6-46d2-9e8f-f30f01213615}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I1:I17 I29:I1048576 I21:I25 I19 I27">
     <cfRule type="dataBar" priority="23">
       <dataBar>
         <cfvo type="min"/>
@@ -4917,13 +5062,13 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5a4de853-09f0-4ccd-ab01-c5117ab4fa1e}</x14:id>
+          <x14:id>{8b33c886-3e56-416e-aac3-18e5b9e69aab}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I9 I20:I23 I11:I18 I28:I1048576 I26">
-    <cfRule type="dataBar" priority="24">
+  <conditionalFormatting sqref="I2 I53:I1048576 I32">
+    <cfRule type="dataBar" priority="51">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4931,13 +5076,13 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a7117f6a-d99b-4cb0-9716-f960ad6ce4cc}</x14:id>
+          <x14:id>{a37213c5-d8c2-4d8a-b9b3-8854c5fda7e3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2 I52:I1048576 I31">
-    <cfRule type="dataBar" priority="50">
+  <conditionalFormatting sqref="I2:I4 I29:I39 I6:I7 I41:I1048576 I9 I11:I17 I21:I24 I19 I27">
+    <cfRule type="dataBar" priority="28">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4945,13 +5090,13 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{47aea96c-dd5e-4001-99bd-35c4d627f457}</x14:id>
+          <x14:id>{5350f9cd-155e-472b-b411-a99f85295a24}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I4 I20:I23 I28:I38 I26 I11:I18 I9 I6:I7 I40:I1048576">
-    <cfRule type="dataBar" priority="27">
+  <conditionalFormatting sqref="I2:I4 I29:I39 I41:I1048576 I11:I16 I9 I6:I7 I21:I24 I27 I19">
+    <cfRule type="dataBar" priority="32">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4959,27 +5104,13 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cf5ce95e-bb0a-4cbd-9e21-64ebd53e1e9c}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I4 I20:I23 I28:I38 I9 I26 I6:I7 I11:I16 I40:I1048576 I18">
-    <cfRule type="dataBar" priority="31">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{379edc11-7862-47d4-9e53-f459d953d005}</x14:id>
+          <x14:id>{8341e6f2-1230-4f64-84bf-d7d05e301a02}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D3 D10:D18 D20:D23 D25:D26 D28:D33">
-    <cfRule type="colorScale" priority="104">
+    <cfRule type="colorScale" priority="105">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4989,7 +5120,7 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="116">
+    <cfRule type="colorScale" priority="117">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4999,7 +5130,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D3:D18 D20:D23 D25:D26 D28:D34">
-    <cfRule type="colorScale" priority="82">
+    <cfRule type="colorScale" priority="83">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5010,21 +5141,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I12:I14 I3:I4 I43:I48 I50:I51 I6:I7 I18 I9 I20:I23 I26 I37:I38 I29 I32:I34 I40:I41">
-    <cfRule type="dataBar" priority="37">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b940c2a0-92a9-4e3b-a50c-1071151a728e}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I18 I3:I4 I43:I48 I50:I51 I6:I7 I12:I14 I9 I20:I23 I37:I38 I29 I32:I34 I40:I41">
+  <conditionalFormatting sqref="I12:I14 I3:I4 I33:I35 I44:I49 I6:I7 I51:I52 I9 I38:I39 I41:I42 I30 I21:I24 I19 I27">
     <cfRule type="dataBar" priority="38">
       <dataBar>
         <cfvo type="min"/>
@@ -5033,12 +5150,54 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{401edcdf-43ae-4b44-99c5-0e95810b949c}</x14:id>
+          <x14:id>{16165f7b-7c0f-49c9-a2bf-e789513a0274}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I16 I3:I4 I40:I41 I43:I48 I6:I7 I12:I14 I9 I20:I23 I26 I18 I50:I51 I29 I32:I34 I37:I38">
+  <conditionalFormatting sqref="I33:I35 I3:I4 I44:I49 I51:I52 I6:I7 I12:I14 I9 I41:I42 I38:I39 I19 I21:I24 I30">
+    <cfRule type="dataBar" priority="39">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{1930dc6f-ae55-44b4-bc75-eacc4e163e32}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I16 I3:I4 I33:I35 I41:I42 I6:I7 I12:I14 I9 I44:I49 I51:I52 I38:I39 I30 I27 I21:I24 I19">
+    <cfRule type="dataBar" priority="36">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{3a06ec88-65f8-458a-a2ae-d66c87115e22}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I11:I14 I3:I4 I33:I36 I38:I39 I6:I7 I41:I42 I9 I16 I44:I52 I19 I27 I21:I24 I30:I31">
+    <cfRule type="dataBar" priority="34">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{612fc072-dda3-4faa-8079-9b7afcbb38a0}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I38:I39 I3:I4 I44:I49 I51:I52 I6:I7 I16 I9 I11:I14 I33:I35 I41:I42 I21:I24 I27 I30:I31 I19">
     <cfRule type="dataBar" priority="35">
       <dataBar>
         <cfvo type="min"/>
@@ -5047,12 +5206,26 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{523fecbb-3adb-4d79-a75b-8b4a50bc759a}</x14:id>
+          <x14:id>{2af321a6-43d8-439d-bf9e-502a21c6653b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I11:I14 I3:I4 I32:I35 I37:I38 I6:I7 I20:I23 I9 I16 I26 I18 I40:I41 I29:I30 I43:I51">
+  <conditionalFormatting sqref="I41:I52 I33:I39 I3:I4 I9 I11:I16 I6:I7 I19 I27 I29:I31 I21:I24">
+    <cfRule type="dataBar" priority="30">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{1e9ad7a3-a880-46af-b64c-6384d0bb9a85}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I11:I16 I3:I4 I33:I39 I41:I52 I6:I7 I9 I19 I21:I24 I27 I30:I31">
     <cfRule type="dataBar" priority="33">
       <dataBar>
         <cfvo type="min"/>
@@ -5061,26 +5234,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{32087ca6-3254-40a7-8cc5-b988d1d7a0c2}</x14:id>
+          <x14:id>{1ede0976-3f5d-4548-a608-b5da5ee0adb8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I20:I23 I3:I4 I43:I48 I29:I30 I6:I7 I16 I9 I11:I14 I26 I18 I50:I51 I32:I34 I37:I38 I40:I41">
-    <cfRule type="dataBar" priority="34">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{dc69e5a5-d61c-4a5e-82bd-46b575a4d8cb}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I18 I20:I23 I3:I4 I32:I38 I40:I51 I6:I7 I26 I9 I11:I16 I28:I30">
+  <conditionalFormatting sqref="I11:I17 I41:I52 I3:I4 I33:I39 I9 I6:I7 I19 I21:I24 I27 I29:I31">
     <cfRule type="dataBar" priority="29">
       <dataBar>
         <cfvo type="min"/>
@@ -5089,54 +5248,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{42579923-6e79-4eea-92bf-7b4dfaf2fb1c}</x14:id>
+          <x14:id>{e4db04cc-6be5-4ecd-b3e9-b1e5cf7d1031}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I11:I16 I3:I4 I29:I30 I32:I38 I6:I7 I20:I23 I9 I18 I26 I40:I51">
-    <cfRule type="dataBar" priority="32">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7052e990-7149-4d2c-bc26-fe0346d51423}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I11:I18 I3:I4 I28:I30 I40:I51 I6:I7 I20:I23 I9 I26 I32:I38">
-    <cfRule type="dataBar" priority="28">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6b05bec6-0fe7-4451-8778-669f759a2cba}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I11:I18 I20:I23 I3:I7 I9 I28:I30 I32:I51 I26">
-    <cfRule type="dataBar" priority="25">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a3ec90ee-0edb-4044-a3ca-e7b0fbb2eb3f}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I26 I20:I23 I9 I3:I7 I28:I30 I32:I38 I40:I51 I11:I18">
+  <conditionalFormatting sqref="I11:I17 I33:I52 I9 I3:I7 I27 I29:I31 I21:I24 I19">
     <cfRule type="dataBar" priority="26">
       <dataBar>
         <cfvo type="min"/>
@@ -5145,13 +5262,13 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8e0cbaf6-6166-4117-96ff-bf728ed8445d}</x14:id>
+          <x14:id>{6c63add2-3203-45b5-89a2-4a12d8afc0b1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I26 I32:I51 I3:I24 I28:I30">
-    <cfRule type="dataBar" priority="21">
+  <conditionalFormatting sqref="I41:I52 I33:I39 I9 I3:I7 I11:I17 I19 I29:I31 I21:I24 I27">
+    <cfRule type="dataBar" priority="27">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -5159,7 +5276,21 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2b82bf50-89c6-4846-b5dd-7ef49ea29902}</x14:id>
+          <x14:id>{300abaa2-c1d9-48b9-ae8e-05015977ad1a}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I33:I52 I3:I17 I19:I25 I29:I31 I27">
+    <cfRule type="dataBar" priority="22">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{ee1fe562-cfba-4b9c-8a63-a97f8821f0c2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5173,7 +5304,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0516d668-bde6-4820-9c21-bd9bfe863a0b}">
+          <x14:cfRule type="dataBar" id="{1e706b11-9071-4342-b703-3936458eca29}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5181,10 +5312,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I25</xm:sqref>
+          <xm:sqref>I26</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f9af9851-3b3f-4134-b8de-49494a92d3d3}">
+          <x14:cfRule type="dataBar" id="{702023a5-6b76-4725-ab5a-e73a1a96687b}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5192,10 +5323,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I$1:I$1048576</xm:sqref>
+          <xm:sqref>I3:I52</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d8c93784-4d59-402c-bd64-0ae50c373c64}">
+          <x14:cfRule type="dataBar" id="{f2859ee8-d1f3-48c2-94dc-cdab6bbd66ea}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5208,7 +5339,7 @@
           <xm:sqref>G1 G2:I2</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c6782148-85aa-4485-ac94-2bb6567ca129}">
+          <x14:cfRule type="dataBar" id="{c2fdf4eb-9309-4790-9577-64d0375898cf}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5216,10 +5347,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I1:I26 I28:I1048576</xm:sqref>
+          <xm:sqref>I1:I17 I19:I1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1f04ca4b-f0e5-4ce8-82e6-d45a7293206e}">
+          <x14:cfRule type="dataBar" id="{32a56779-809f-48ef-abe5-6499028ee3b1}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5227,10 +5358,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I1:I24 I26 I28:I1048576</xm:sqref>
+          <xm:sqref>I1:I17 I29:I1048576 I19:I27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{580211c7-d112-48e0-b9ff-a7e120b3cd1e}">
+          <x14:cfRule type="dataBar" id="{4e5517ac-ac71-4595-b8ea-b3ebf3c4f558}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5238,10 +5369,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I1:I18 I28:I1048576 I20:I24 I26</xm:sqref>
+          <xm:sqref>I1:I17 I29:I1048576 I27 I19:I25</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5a4de853-09f0-4ccd-ab01-c5117ab4fa1e}">
+          <x14:cfRule type="dataBar" id="{d437ab4f-284f-4dce-87a8-883f66c3d40c}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5249,10 +5380,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I1:I9 I20:I24 I11:I18 I28:I1048576 I26</xm:sqref>
+          <xm:sqref>I1:I9 I29:I1048576 I11:I17 I27 I19 I21:I25</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a7117f6a-d99b-4cb0-9716-f960ad6ce4cc}">
+          <x14:cfRule type="dataBar" id="{7bd851aa-fab6-46d2-9e8f-f30f01213615}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5260,10 +5391,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I1:I9 I20:I23 I11:I18 I28:I1048576 I26</xm:sqref>
+          <xm:sqref>I1:I9 I29:I1048576 I11:I17 I27 I19 I21:I24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{47aea96c-dd5e-4001-99bd-35c4d627f457}">
+          <x14:cfRule type="dataBar" id="{8b33c886-3e56-416e-aac3-18e5b9e69aab}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5271,10 +5402,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I2 I52:I1048576 I31</xm:sqref>
+          <xm:sqref>I1:I17 I29:I1048576 I21:I25 I19 I27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{cf5ce95e-bb0a-4cbd-9e21-64ebd53e1e9c}">
+          <x14:cfRule type="dataBar" id="{a37213c5-d8c2-4d8a-b9b3-8854c5fda7e3}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5282,10 +5413,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I2:I4 I20:I23 I28:I38 I26 I11:I18 I9 I6:I7 I40:I1048576</xm:sqref>
+          <xm:sqref>I2 I53:I1048576 I32</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{379edc11-7862-47d4-9e53-f459d953d005}">
+          <x14:cfRule type="dataBar" id="{5350f9cd-155e-472b-b411-a99f85295a24}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5293,10 +5424,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I2:I4 I20:I23 I28:I38 I9 I26 I6:I7 I11:I16 I40:I1048576 I18</xm:sqref>
+          <xm:sqref>I2:I4 I29:I39 I6:I7 I41:I1048576 I9 I11:I17 I21:I24 I19 I27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b940c2a0-92a9-4e3b-a50c-1071151a728e}">
+          <x14:cfRule type="dataBar" id="{8341e6f2-1230-4f64-84bf-d7d05e301a02}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5304,10 +5435,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I12:I14 I3:I4 I43:I48 I50:I51 I6:I7 I18 I9 I20:I23 I26 I37:I38 I29 I32:I34 I40:I41</xm:sqref>
+          <xm:sqref>I2:I4 I29:I39 I41:I1048576 I11:I16 I9 I6:I7 I21:I24 I27 I19</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{401edcdf-43ae-4b44-99c5-0e95810b949c}">
+          <x14:cfRule type="dataBar" id="{16165f7b-7c0f-49c9-a2bf-e789513a0274}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5315,10 +5446,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I18 I3:I4 I43:I48 I50:I51 I6:I7 I12:I14 I9 I20:I23 I37:I38 I29 I32:I34 I40:I41</xm:sqref>
+          <xm:sqref>I12:I14 I3:I4 I33:I35 I44:I49 I6:I7 I51:I52 I9 I38:I39 I41:I42 I30 I21:I24 I19 I27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{523fecbb-3adb-4d79-a75b-8b4a50bc759a}">
+          <x14:cfRule type="dataBar" id="{1930dc6f-ae55-44b4-bc75-eacc4e163e32}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5326,10 +5457,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I16 I3:I4 I40:I41 I43:I48 I6:I7 I12:I14 I9 I20:I23 I26 I18 I50:I51 I29 I32:I34 I37:I38</xm:sqref>
+          <xm:sqref>I33:I35 I3:I4 I44:I49 I51:I52 I6:I7 I12:I14 I9 I41:I42 I38:I39 I19 I21:I24 I30</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{32087ca6-3254-40a7-8cc5-b988d1d7a0c2}">
+          <x14:cfRule type="dataBar" id="{3a06ec88-65f8-458a-a2ae-d66c87115e22}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5337,10 +5468,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I11:I14 I3:I4 I32:I35 I37:I38 I6:I7 I20:I23 I9 I16 I26 I18 I40:I41 I29:I30 I43:I51</xm:sqref>
+          <xm:sqref>I16 I3:I4 I33:I35 I41:I42 I6:I7 I12:I14 I9 I44:I49 I51:I52 I38:I39 I30 I27 I21:I24 I19</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{dc69e5a5-d61c-4a5e-82bd-46b575a4d8cb}">
+          <x14:cfRule type="dataBar" id="{612fc072-dda3-4faa-8079-9b7afcbb38a0}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5348,10 +5479,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I20:I23 I3:I4 I43:I48 I29:I30 I6:I7 I16 I9 I11:I14 I26 I18 I50:I51 I32:I34 I37:I38 I40:I41</xm:sqref>
+          <xm:sqref>I11:I14 I3:I4 I33:I36 I38:I39 I6:I7 I41:I42 I9 I16 I44:I52 I19 I27 I21:I24 I30:I31</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{42579923-6e79-4eea-92bf-7b4dfaf2fb1c}">
+          <x14:cfRule type="dataBar" id="{2af321a6-43d8-439d-bf9e-502a21c6653b}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5359,10 +5490,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I18 I20:I23 I3:I4 I32:I38 I40:I51 I6:I7 I26 I9 I11:I16 I28:I30</xm:sqref>
+          <xm:sqref>I38:I39 I3:I4 I44:I49 I51:I52 I6:I7 I16 I9 I11:I14 I33:I35 I41:I42 I21:I24 I27 I30:I31 I19</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7052e990-7149-4d2c-bc26-fe0346d51423}">
+          <x14:cfRule type="dataBar" id="{1e9ad7a3-a880-46af-b64c-6384d0bb9a85}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5370,10 +5501,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I11:I16 I3:I4 I29:I30 I32:I38 I6:I7 I20:I23 I9 I18 I26 I40:I51</xm:sqref>
+          <xm:sqref>I41:I52 I33:I39 I3:I4 I9 I11:I16 I6:I7 I19 I27 I29:I31 I21:I24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6b05bec6-0fe7-4451-8778-669f759a2cba}">
+          <x14:cfRule type="dataBar" id="{1ede0976-3f5d-4548-a608-b5da5ee0adb8}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5381,10 +5512,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I11:I18 I3:I4 I28:I30 I40:I51 I6:I7 I20:I23 I9 I26 I32:I38</xm:sqref>
+          <xm:sqref>I11:I16 I3:I4 I33:I39 I41:I52 I6:I7 I9 I19 I21:I24 I27 I30:I31</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a3ec90ee-0edb-4044-a3ca-e7b0fbb2eb3f}">
+          <x14:cfRule type="dataBar" id="{e4db04cc-6be5-4ecd-b3e9-b1e5cf7d1031}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5392,10 +5523,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I11:I18 I20:I23 I3:I7 I9 I28:I30 I32:I51 I26</xm:sqref>
+          <xm:sqref>I11:I17 I41:I52 I3:I4 I33:I39 I9 I6:I7 I19 I21:I24 I27 I29:I31</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8e0cbaf6-6166-4117-96ff-bf728ed8445d}">
+          <x14:cfRule type="dataBar" id="{6c63add2-3203-45b5-89a2-4a12d8afc0b1}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5403,10 +5534,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I26 I20:I23 I9 I3:I7 I28:I30 I32:I38 I40:I51 I11:I18</xm:sqref>
+          <xm:sqref>I11:I17 I33:I52 I9 I3:I7 I27 I29:I31 I21:I24 I19</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2b82bf50-89c6-4846-b5dd-7ef49ea29902}">
+          <x14:cfRule type="dataBar" id="{300abaa2-c1d9-48b9-ae8e-05015977ad1a}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5414,26 +5545,21 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I26 I32:I51 I3:I24 I28:I30</xm:sqref>
+          <xm:sqref>I41:I52 I33:I39 I9 I3:I7 I11:I17 I19 I29:I31 I21:I24 I27</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{ee1fe562-cfba-4b9c-8a63-a97f8821f0c2}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>I33:I52 I3:I17 I19:I25 I29:I31 I27</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
   </extLst>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <cols>
-    <col min="1" max="1" width="11.5" customWidth="1"/>
-    <col min="2" max="2" width="8.125" customWidth="1"/>
-    <col min="3" max="3" width="8.875" customWidth="1"/>
-  </cols>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
 </file>
--- a/CrCraft收支与赞助鸣谢单.xlsx
+++ b/CrCraft收支与赞助鸣谢单.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="81">
   <si>
     <t>服务器收入与支出</t>
   </si>
@@ -149,7 +149,7 @@
     <t>luolizuiniubi</t>
   </si>
   <si>
-    <t>↑34</t>
+    <t>↑35</t>
   </si>
   <si>
     <t>匿名玩家</t>
@@ -227,10 +227,19 @@
     <t>Mo_Xuan_Yu</t>
   </si>
   <si>
+    <t>Damon</t>
+  </si>
+  <si>
+    <t>↑13</t>
+  </si>
+  <si>
+    <t>主板、CPU、电源、机械硬盘</t>
+  </si>
+  <si>
     <t>xiaomin</t>
   </si>
   <si>
-    <t>主板、CPU、电源、机械硬盘</t>
+    <t>↓2</t>
   </si>
   <si>
     <t>A1TanJZ</t>
@@ -1107,7 +1116,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1180,6 +1189,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="31" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1218,6 +1230,21 @@
     </xf>
     <xf numFmtId="31" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="31" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="31" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="7" xfId="22" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="31" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -1555,7 +1582,7 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:K165"/>
+  <dimension ref="A1:K167"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="15.625" customWidth="1"/>
@@ -2741,17 +2768,17 @@
       <c r="G40" s="15">
         <v>38</v>
       </c>
-      <c r="H40" s="10" t="s">
+      <c r="H40" s="24" t="s">
         <v>66</v>
       </c>
       <c r="I40" s="2">
-        <v>2.5</v>
+        <v>2.741</v>
       </c>
       <c r="J40" s="3">
-        <v>45976</v>
+        <v>46305</v>
       </c>
       <c r="K40" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -2768,23 +2795,22 @@
         <v>-1999.72</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G41">
         <v>39</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="I41" s="16">
-        <f>SUM(C35,C33:C33)</f>
-        <v>2.18</v>
+        <v>69</v>
+      </c>
+      <c r="I41" s="2">
+        <v>2.5</v>
       </c>
       <c r="J41" s="3">
-        <v>45396</v>
+        <v>45976</v>
       </c>
       <c r="K41" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -2808,16 +2834,17 @@
         <v>40</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="I42" s="16">
-        <v>2</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>11</v>
+        <f>SUM(C35,C33:C33)</f>
+        <v>2.18</v>
+      </c>
+      <c r="J42" s="3">
+        <v>45396</v>
       </c>
       <c r="K42" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -2833,371 +2860,386 @@
       <c r="G43">
         <v>41</v>
       </c>
-      <c r="H43" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="I43" s="2">
+      <c r="H43" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="I43" s="16">
         <v>2</v>
       </c>
-      <c r="J43" s="3">
-        <v>45907</v>
+      <c r="J43" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="K43" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
     </row>
     <row r="44" spans="1:11">
-      <c r="A44" s="24">
+      <c r="A44" s="25">
         <v>45495</v>
       </c>
-      <c r="B44" s="25" t="s">
+      <c r="B44" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="C44" s="26">
+      <c r="C44" s="27">
         <v>8</v>
       </c>
       <c r="D44" s="21">
         <f>SUM(C3:C44)</f>
         <v>-1907.27</v>
       </c>
-      <c r="E44" s="27"/>
+      <c r="E44" s="28"/>
       <c r="G44">
         <v>42</v>
       </c>
-      <c r="H44" s="28" t="s">
-        <v>41</v>
-      </c>
-      <c r="I44" s="16">
-        <v>1.32</v>
+      <c r="H44" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="I44" s="2">
+        <v>2</v>
       </c>
       <c r="J44" s="3">
-        <v>44958</v>
+        <v>45907</v>
       </c>
       <c r="K44" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
     </row>
     <row r="45" spans="1:11">
-      <c r="A45" s="24">
+      <c r="A45" s="25">
         <v>45496</v>
       </c>
-      <c r="B45" s="25" t="s">
+      <c r="B45" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="C45" s="26">
+      <c r="C45" s="27">
         <v>5</v>
       </c>
       <c r="D45" s="21">
         <f>SUM(C3:C46)</f>
         <v>-1899.27</v>
       </c>
-      <c r="E45" s="27"/>
+      <c r="E45" s="28"/>
       <c r="G45">
         <v>43</v>
       </c>
-      <c r="H45" s="10" t="s">
-        <v>20</v>
+      <c r="H45" s="29" t="s">
+        <v>41</v>
       </c>
       <c r="I45" s="16">
-        <v>1.28</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>11</v>
+        <v>1.32</v>
+      </c>
+      <c r="J45" s="3">
+        <v>44958</v>
       </c>
       <c r="K45" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
     </row>
     <row r="46" spans="1:11">
-      <c r="A46" s="29"/>
-      <c r="B46" s="25" t="s">
+      <c r="A46" s="30"/>
+      <c r="B46" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C46" s="26">
+      <c r="C46" s="27">
         <v>3</v>
       </c>
-      <c r="D46" s="30"/>
-      <c r="E46" s="27"/>
+      <c r="D46" s="31"/>
+      <c r="E46" s="28"/>
       <c r="G46">
         <v>44</v>
       </c>
       <c r="H46" s="10" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="I46" s="16">
-        <v>1.01</v>
-      </c>
-      <c r="J46" s="3">
-        <v>45141</v>
+        <v>1.28</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="K46" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
     </row>
     <row r="47" spans="1:11">
       <c r="A47" s="17">
         <v>45497</v>
       </c>
-      <c r="B47" s="25" t="s">
+      <c r="B47" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="C47" s="26">
+      <c r="C47" s="27">
         <v>25</v>
       </c>
       <c r="D47" s="21">
         <f>SUM(C3:C47)</f>
         <v>-1874.27</v>
       </c>
-      <c r="E47" s="27"/>
+      <c r="E47" s="28"/>
       <c r="G47">
         <v>45</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="I47" s="16">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="J47" s="3">
-        <v>45794</v>
+        <v>45141</v>
       </c>
       <c r="K47" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
     </row>
     <row r="48" spans="1:11">
-      <c r="A48" s="24">
+      <c r="A48" s="25">
         <v>45500</v>
       </c>
-      <c r="B48" s="25" t="s">
+      <c r="B48" s="26" t="s">
         <v>65</v>
       </c>
-      <c r="C48" s="26">
+      <c r="C48" s="27">
         <v>3</v>
       </c>
       <c r="D48" s="21">
         <f>SUM(C3:C49)</f>
         <v>-1866.27</v>
       </c>
-      <c r="E48" s="27"/>
+      <c r="E48" s="28"/>
       <c r="G48" s="15">
         <v>46</v>
       </c>
       <c r="H48" s="10" t="s">
-        <v>14</v>
+        <v>72</v>
       </c>
       <c r="I48" s="16">
-        <v>0.55</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>11</v>
+        <v>1</v>
+      </c>
+      <c r="J48" s="3">
+        <v>45794</v>
       </c>
       <c r="K48" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
     </row>
     <row r="49" spans="1:11">
-      <c r="A49" s="31"/>
-      <c r="B49" s="25" t="s">
+      <c r="A49" s="32"/>
+      <c r="B49" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="C49" s="26">
+      <c r="C49" s="27">
         <v>5</v>
       </c>
-      <c r="D49" s="30"/>
-      <c r="E49" s="27" t="s">
+      <c r="D49" s="31"/>
+      <c r="E49" s="28" t="s">
         <v>33</v>
       </c>
       <c r="G49">
         <v>47</v>
       </c>
       <c r="H49" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I49" s="16">
+        <v>0.55</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K49" t="s">
         <v>70</v>
       </c>
-      <c r="I49" s="16">
-        <v>0.5</v>
-      </c>
-      <c r="J49" s="3">
-        <v>45697</v>
-      </c>
-      <c r="K49" t="s">
-        <v>43</v>
-      </c>
     </row>
     <row r="50" spans="1:11">
-      <c r="A50" s="24">
+      <c r="A50" s="25">
         <v>45505</v>
       </c>
-      <c r="B50" s="25" t="s">
+      <c r="B50" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="C50" s="26">
+      <c r="C50" s="27">
         <v>10</v>
       </c>
       <c r="D50" s="21">
         <f>SUM(C3:C50)</f>
         <v>-1856.27</v>
       </c>
-      <c r="E50" s="27" t="s">
+      <c r="E50" s="28" t="s">
         <v>33</v>
       </c>
       <c r="G50">
         <v>48</v>
       </c>
       <c r="H50" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="I50" s="2">
+        <v>73</v>
+      </c>
+      <c r="I50" s="16">
         <v>0.5</v>
       </c>
       <c r="J50" s="3">
-        <v>45885</v>
+        <v>45697</v>
       </c>
       <c r="K50" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
     </row>
     <row r="51" spans="1:11">
-      <c r="A51" s="24">
+      <c r="A51" s="25">
         <v>45507</v>
       </c>
-      <c r="B51" s="25" t="s">
+      <c r="B51" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="C51" s="26">
+      <c r="C51" s="27">
         <v>14</v>
       </c>
       <c r="D51" s="21">
         <f>SUM(C3:C52)</f>
         <v>-1756.27</v>
       </c>
-      <c r="E51" s="27" t="s">
+      <c r="E51" s="28" t="s">
         <v>33</v>
       </c>
       <c r="G51">
         <v>49</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="I51" s="16">
-        <v>0.11</v>
+        <v>74</v>
+      </c>
+      <c r="I51" s="2">
+        <v>0.5</v>
       </c>
       <c r="J51" s="3">
-        <v>45140</v>
+        <v>45885</v>
       </c>
       <c r="K51" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
     </row>
     <row r="52" spans="1:11">
-      <c r="A52" s="31"/>
-      <c r="B52" s="25" t="s">
+      <c r="A52" s="32"/>
+      <c r="B52" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="C52" s="26">
+      <c r="C52" s="27">
         <v>86</v>
       </c>
-      <c r="D52" s="30"/>
-      <c r="E52" s="27" t="s">
-        <v>72</v>
+      <c r="D52" s="31"/>
+      <c r="E52" s="28" t="s">
+        <v>75</v>
       </c>
       <c r="G52">
         <v>50</v>
       </c>
       <c r="H52" s="10" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="I52" s="16">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="J52" s="3">
-        <v>44213</v>
+        <v>45140</v>
       </c>
       <c r="K52" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
     </row>
     <row r="53" spans="1:11">
-      <c r="A53" s="24">
+      <c r="A53" s="25">
         <v>45508</v>
       </c>
-      <c r="B53" s="25" t="s">
+      <c r="B53" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="C53" s="26">
+      <c r="C53" s="27">
         <v>9</v>
       </c>
       <c r="D53" s="21">
         <f>SUM(C3:C54)</f>
         <v>-1737.27</v>
       </c>
-      <c r="E53" s="27" t="s">
+      <c r="E53" s="28" t="s">
         <v>33</v>
       </c>
+      <c r="G53">
+        <v>51</v>
+      </c>
+      <c r="H53" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="I53" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="J53" s="3">
+        <v>44213</v>
+      </c>
+      <c r="K53" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="54" spans="1:11">
-      <c r="A54" s="31"/>
-      <c r="B54" s="25" t="s">
+      <c r="A54" s="32"/>
+      <c r="B54" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="C54" s="26">
+      <c r="C54" s="27">
         <v>10</v>
       </c>
-      <c r="D54" s="30"/>
-      <c r="E54" s="27"/>
+      <c r="D54" s="31"/>
+      <c r="E54" s="28"/>
     </row>
     <row r="55" spans="1:11">
-      <c r="A55" s="24">
+      <c r="A55" s="25">
         <v>45509</v>
       </c>
-      <c r="B55" s="25"/>
-      <c r="C55" s="32">
+      <c r="B55" s="26"/>
+      <c r="C55" s="33">
         <v>-10</v>
       </c>
       <c r="D55" s="21">
         <f>SUM(C3:C56)</f>
         <v>-1737.27</v>
       </c>
-      <c r="E55" s="27" t="s">
-        <v>73</v>
+      <c r="E55" s="28" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="56" spans="1:11">
-      <c r="A56" s="31"/>
-      <c r="B56" s="25" t="s">
+      <c r="A56" s="32"/>
+      <c r="B56" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C56" s="26">
+      <c r="C56" s="27">
         <v>10</v>
       </c>
-      <c r="D56" s="30"/>
-      <c r="E56" s="27"/>
+      <c r="D56" s="31"/>
+      <c r="E56" s="28"/>
     </row>
     <row r="57" spans="1:11">
-      <c r="A57" s="24">
+      <c r="A57" s="25">
         <v>45510</v>
       </c>
-      <c r="B57" s="25" t="s">
+      <c r="B57" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="C57" s="26">
+      <c r="C57" s="27">
         <v>40</v>
       </c>
       <c r="D57" s="20">
         <f>SUM(C3:C57)</f>
         <v>-1697.27</v>
       </c>
-      <c r="E57" s="27"/>
+      <c r="E57" s="28"/>
     </row>
     <row r="58" spans="1:11">
-      <c r="A58" s="24">
+      <c r="A58" s="25">
         <v>45525</v>
       </c>
-      <c r="B58" s="33" t="s">
+      <c r="B58" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="C58" s="26">
+      <c r="C58" s="27">
         <f>6+5+5+5+6+5+5+5+30</f>
         <v>72</v>
       </c>
@@ -3205,233 +3247,233 @@
         <f>SUM(C3:C58)</f>
         <v>-1625.27</v>
       </c>
-      <c r="E58" s="27" t="s">
+      <c r="E58" s="28" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="59" spans="1:11">
-      <c r="A59" s="24">
+      <c r="A59" s="25">
         <v>45525</v>
       </c>
-      <c r="B59" s="33" t="s">
+      <c r="B59" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="C59" s="26">
+      <c r="C59" s="27">
         <v>6</v>
       </c>
       <c r="D59" s="21">
         <f>SUM(C3:C59)</f>
         <v>-1619.27</v>
       </c>
-      <c r="E59" s="27"/>
+      <c r="E59" s="28"/>
     </row>
     <row r="60" spans="1:11">
-      <c r="A60" s="24">
+      <c r="A60" s="25">
         <v>45549</v>
       </c>
-      <c r="B60" s="33" t="s">
+      <c r="B60" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="C60" s="26">
+      <c r="C60" s="27">
         <v>30</v>
       </c>
       <c r="D60" s="21">
         <f>SUM(C3:C61)</f>
         <v>-1569.27</v>
       </c>
-      <c r="E60" s="27" t="s">
+      <c r="E60" s="28" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="61" spans="1:11">
-      <c r="A61" s="29"/>
-      <c r="B61" s="33" t="s">
+      <c r="A61" s="30"/>
+      <c r="B61" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="C61" s="26">
+      <c r="C61" s="27">
         <v>20</v>
       </c>
-      <c r="D61" s="30"/>
-      <c r="E61" s="27"/>
+      <c r="D61" s="31"/>
+      <c r="E61" s="28"/>
     </row>
     <row r="62" spans="1:11">
-      <c r="A62" s="31">
+      <c r="A62" s="32">
         <v>45551</v>
       </c>
-      <c r="B62" s="33" t="s">
+      <c r="B62" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="C62" s="26">
+      <c r="C62" s="27">
         <v>17</v>
       </c>
       <c r="D62" s="21">
         <f>SUM(C3:C62)</f>
         <v>-1552.27</v>
       </c>
-      <c r="E62" s="27"/>
+      <c r="E62" s="28"/>
     </row>
     <row r="63" spans="1:11">
-      <c r="A63" s="24">
+      <c r="A63" s="25">
         <v>45552</v>
       </c>
-      <c r="B63" s="33" t="s">
+      <c r="B63" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="C63" s="26">
+      <c r="C63" s="27">
         <v>40</v>
       </c>
       <c r="D63" s="21">
         <f>SUM(C3:C63)</f>
         <v>-1512.27</v>
       </c>
-      <c r="E63" s="27"/>
+      <c r="E63" s="28"/>
     </row>
     <row r="64" spans="1:11">
-      <c r="A64" s="24">
+      <c r="A64" s="25">
         <v>45555</v>
       </c>
-      <c r="B64" s="33" t="s">
+      <c r="B64" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="C64" s="26">
+      <c r="C64" s="27">
         <v>6</v>
       </c>
       <c r="D64" s="21">
         <f>SUM(C3:C65)</f>
         <v>-1486.27</v>
       </c>
-      <c r="E64" s="27"/>
+      <c r="E64" s="28"/>
     </row>
     <row r="65" spans="1:5">
-      <c r="A65" s="31"/>
-      <c r="B65" s="33" t="s">
+      <c r="A65" s="32"/>
+      <c r="B65" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="C65" s="26">
+      <c r="C65" s="27">
         <v>20</v>
       </c>
-      <c r="D65" s="30"/>
-      <c r="E65" s="27"/>
+      <c r="D65" s="31"/>
+      <c r="E65" s="28"/>
     </row>
     <row r="66" spans="1:5">
-      <c r="A66" s="24">
+      <c r="A66" s="25">
         <v>45584</v>
       </c>
-      <c r="B66" s="33" t="s">
+      <c r="B66" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="C66" s="26">
+      <c r="C66" s="27">
         <v>30</v>
       </c>
       <c r="D66" s="21">
         <f>SUM(C3:C66)</f>
         <v>-1456.27</v>
       </c>
-      <c r="E66" s="27" t="s">
+      <c r="E66" s="28" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="67" spans="1:5">
-      <c r="A67" s="24">
+      <c r="A67" s="25">
         <v>45584</v>
       </c>
-      <c r="B67" s="33" t="s">
+      <c r="B67" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="C67" s="26">
+      <c r="C67" s="27">
         <v>7</v>
       </c>
       <c r="D67" s="21">
         <f>SUM(C3:C67)</f>
         <v>-1449.27</v>
       </c>
-      <c r="E67" s="27"/>
+      <c r="E67" s="28"/>
     </row>
     <row r="68" spans="1:5">
-      <c r="A68" s="24">
+      <c r="A68" s="25">
         <v>45592</v>
       </c>
-      <c r="B68" s="33" t="s">
+      <c r="B68" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="C68" s="26">
+      <c r="C68" s="27">
         <v>60</v>
       </c>
       <c r="D68" s="21">
         <f>SUM(C3:C68)</f>
         <v>-1389.27</v>
       </c>
-      <c r="E68" s="27" t="s">
-        <v>74</v>
+      <c r="E68" s="28" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="69" spans="1:5">
-      <c r="A69" s="24">
+      <c r="A69" s="25">
         <v>45597</v>
       </c>
-      <c r="B69" s="33" t="s">
+      <c r="B69" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="C69" s="26">
+      <c r="C69" s="27">
         <v>5</v>
       </c>
       <c r="D69" s="21">
         <f>SUM(C3:C69)</f>
         <v>-1384.27</v>
       </c>
-      <c r="E69" s="27" t="s">
+      <c r="E69" s="28" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="70" spans="1:5">
-      <c r="A70" s="24">
+      <c r="A70" s="25">
         <v>45598</v>
       </c>
-      <c r="B70" s="33" t="s">
+      <c r="B70" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="C70" s="26">
+      <c r="C70" s="27">
         <v>5</v>
       </c>
       <c r="D70" s="21">
         <f>SUM(C3:C70)</f>
         <v>-1379.27</v>
       </c>
-      <c r="E70" s="27" t="s">
+      <c r="E70" s="28" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="71" spans="1:5">
-      <c r="A71" s="24">
+      <c r="A71" s="25">
         <v>45612</v>
       </c>
-      <c r="B71" s="33" t="s">
+      <c r="B71" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="C71" s="26">
+      <c r="C71" s="27">
         <v>5</v>
       </c>
       <c r="D71" s="21">
         <f>SUM(C3:C71)</f>
         <v>-1374.27</v>
       </c>
-      <c r="E71" s="27"/>
+      <c r="E71" s="28"/>
     </row>
     <row r="72" spans="1:5">
-      <c r="A72" s="24">
+      <c r="A72" s="25">
         <v>45619</v>
       </c>
-      <c r="B72" s="33" t="s">
+      <c r="B72" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="C72" s="26">
+      <c r="C72" s="27">
         <v>15</v>
       </c>
       <c r="D72" s="21">
         <f>SUM(C3:C72)</f>
         <v>-1359.27</v>
       </c>
-      <c r="E72" s="27" t="s">
+      <c r="E72" s="28" t="s">
         <v>33</v>
       </c>
     </row>
@@ -3439,306 +3481,306 @@
       <c r="A73" s="17">
         <v>45634</v>
       </c>
-      <c r="B73" s="33" t="s">
+      <c r="B73" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="C73" s="26">
+      <c r="C73" s="27">
         <v>5</v>
       </c>
       <c r="D73" s="21">
         <f>SUM(C3:C74)</f>
         <v>-1344.27</v>
       </c>
-      <c r="E73" s="27" t="s">
+      <c r="E73" s="28" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="17"/>
-      <c r="B74" s="33" t="s">
+      <c r="B74" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="C74" s="26">
+      <c r="C74" s="27">
         <v>10</v>
       </c>
-      <c r="D74" s="30"/>
-      <c r="E74" s="27"/>
+      <c r="D74" s="31"/>
+      <c r="E74" s="28"/>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="17">
         <v>45649</v>
       </c>
-      <c r="B75" s="33" t="s">
+      <c r="B75" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="C75" s="26">
+      <c r="C75" s="27">
         <v>10</v>
       </c>
       <c r="D75" s="21">
         <f>SUM(C3:C75)</f>
         <v>-1334.27</v>
       </c>
-      <c r="E75" s="27"/>
+      <c r="E75" s="28"/>
     </row>
     <row r="76" spans="1:5">
-      <c r="A76" s="24">
+      <c r="A76" s="25">
         <v>45654</v>
       </c>
-      <c r="B76" s="33" t="s">
+      <c r="B76" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="C76" s="26">
+      <c r="C76" s="27">
         <v>30</v>
       </c>
       <c r="D76" s="21">
         <f>SUM(C3:C76)</f>
         <v>-1304.27</v>
       </c>
-      <c r="E76" s="27"/>
+      <c r="E76" s="28"/>
     </row>
     <row r="77" spans="1:5">
-      <c r="A77" s="24">
+      <c r="A77" s="25">
         <v>45686</v>
       </c>
-      <c r="B77" s="33" t="s">
+      <c r="B77" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="C77" s="26">
+      <c r="C77" s="27">
         <v>9</v>
       </c>
       <c r="D77" s="21">
         <f>SUM(C3:C77)</f>
         <v>-1295.27</v>
       </c>
-      <c r="E77" s="27" t="s">
+      <c r="E77" s="28" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="78" spans="1:5">
-      <c r="A78" s="24">
+      <c r="A78" s="25">
         <v>45697</v>
       </c>
-      <c r="B78" s="33" t="s">
-        <v>70</v>
-      </c>
-      <c r="C78" s="26">
+      <c r="B78" s="34" t="s">
+        <v>73</v>
+      </c>
+      <c r="C78" s="27">
         <v>0.5</v>
       </c>
       <c r="D78" s="21">
         <f>SUM(C3:C78)</f>
         <v>-1294.77</v>
       </c>
-      <c r="E78" s="27"/>
+      <c r="E78" s="28"/>
     </row>
     <row r="79" spans="1:5">
-      <c r="A79" s="24">
+      <c r="A79" s="25">
         <v>45707</v>
       </c>
-      <c r="B79" s="33" t="s">
+      <c r="B79" s="34" t="s">
         <v>62</v>
       </c>
-      <c r="C79" s="26">
+      <c r="C79" s="27">
         <v>4.15</v>
       </c>
       <c r="D79" s="21">
         <f>SUM(C3:C79)</f>
         <v>-1290.62</v>
       </c>
-      <c r="E79" s="27"/>
+      <c r="E79" s="28"/>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="17">
         <v>45794</v>
       </c>
-      <c r="B80" s="33" t="s">
-        <v>69</v>
-      </c>
-      <c r="C80" s="26">
+      <c r="B80" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="C80" s="27">
         <v>1</v>
       </c>
       <c r="D80" s="20">
         <f>SUM(C3:C80)</f>
         <v>-1289.62</v>
       </c>
-      <c r="E80" s="27"/>
+      <c r="E80" s="28"/>
     </row>
     <row r="81" spans="1:5">
-      <c r="A81" s="24">
+      <c r="A81" s="25">
         <v>45829</v>
       </c>
-      <c r="B81" s="33" t="s">
+      <c r="B81" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="C81" s="26">
+      <c r="C81" s="27">
         <v>26.66</v>
       </c>
       <c r="D81" s="21">
         <f>SUM(C3:C81)</f>
         <v>-1262.96</v>
       </c>
-      <c r="E81" s="27"/>
+      <c r="E81" s="28"/>
     </row>
     <row r="82" spans="1:5">
-      <c r="A82" s="24">
+      <c r="A82" s="25">
         <v>45844</v>
       </c>
-      <c r="B82" s="33" t="s">
+      <c r="B82" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="C82" s="26">
+      <c r="C82" s="27">
         <v>2.48</v>
       </c>
       <c r="D82" s="21">
         <f>SUM(C3:C82)</f>
         <v>-1260.48</v>
       </c>
-      <c r="E82" s="27"/>
+      <c r="E82" s="28"/>
     </row>
     <row r="83" spans="1:5">
-      <c r="A83" s="24">
+      <c r="A83" s="25">
         <v>45860</v>
       </c>
-      <c r="B83" s="33" t="s">
+      <c r="B83" s="34" t="s">
         <v>54</v>
       </c>
-      <c r="C83" s="26">
+      <c r="C83" s="27">
         <v>8</v>
       </c>
       <c r="D83" s="21">
         <f>SUM(C3:C83)</f>
         <v>-1252.48</v>
       </c>
-      <c r="E83" s="27"/>
+      <c r="E83" s="28"/>
     </row>
     <row r="84" spans="1:5">
-      <c r="A84" s="24">
+      <c r="A84" s="25">
         <v>45861</v>
       </c>
-      <c r="B84" s="33" t="s">
+      <c r="B84" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="C84" s="26">
+      <c r="C84" s="27">
         <v>0.5</v>
       </c>
       <c r="D84" s="21">
         <f>SUM(C3:C84)</f>
         <v>-1251.98</v>
       </c>
-      <c r="E84" s="27"/>
+      <c r="E84" s="28"/>
     </row>
     <row r="85" spans="1:5">
-      <c r="A85" s="24">
+      <c r="A85" s="25">
         <v>45865</v>
       </c>
-      <c r="B85" s="33" t="s">
+      <c r="B85" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="C85" s="26">
+      <c r="C85" s="27">
         <v>3</v>
       </c>
       <c r="D85" s="21">
         <f>SUM(C3:C85)</f>
         <v>-1248.98</v>
       </c>
-      <c r="E85" s="27"/>
+      <c r="E85" s="28"/>
     </row>
     <row r="86" spans="1:5">
-      <c r="A86" s="24">
+      <c r="A86" s="25">
         <v>45868</v>
       </c>
-      <c r="B86" s="33" t="s">
+      <c r="B86" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="C86" s="26">
+      <c r="C86" s="27">
         <v>5.01</v>
       </c>
       <c r="D86" s="21">
         <f>SUM(C3:C86)</f>
         <v>-1243.97</v>
       </c>
-      <c r="E86" s="27"/>
+      <c r="E86" s="28"/>
     </row>
     <row r="87" spans="1:5">
-      <c r="A87" s="24">
+      <c r="A87" s="25">
         <v>45868</v>
       </c>
-      <c r="B87" s="33" t="s">
+      <c r="B87" s="34" t="s">
         <v>58</v>
       </c>
-      <c r="C87" s="26">
+      <c r="C87" s="27">
         <v>6</v>
       </c>
       <c r="D87" s="21">
         <f>SUM(C3:C87)</f>
         <v>-1237.97</v>
       </c>
-      <c r="E87" s="27"/>
+      <c r="E87" s="28"/>
     </row>
     <row r="88" spans="1:5">
-      <c r="A88" s="24">
+      <c r="A88" s="25">
         <v>45877</v>
       </c>
-      <c r="B88" s="33" t="s">
+      <c r="B88" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="C88" s="26">
+      <c r="C88" s="27">
         <v>5</v>
       </c>
       <c r="D88" s="21">
         <f>SUM(C3:C88)</f>
         <v>-1232.97</v>
       </c>
-      <c r="E88" s="27" t="s">
+      <c r="E88" s="28" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="89" spans="1:5">
-      <c r="A89" s="24">
+      <c r="A89" s="25">
         <v>45878</v>
       </c>
-      <c r="B89" s="33" t="s">
+      <c r="B89" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="C89" s="26">
+      <c r="C89" s="27">
         <v>0.01</v>
       </c>
       <c r="D89" s="21">
         <f>SUM(C3:C89)</f>
         <v>-1232.96</v>
       </c>
-      <c r="E89" s="27"/>
+      <c r="E89" s="28"/>
     </row>
     <row r="90" spans="1:5">
-      <c r="A90" s="24">
+      <c r="A90" s="25">
         <v>45879</v>
       </c>
-      <c r="B90" s="33" t="s">
+      <c r="B90" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="C90" s="26">
+      <c r="C90" s="27">
         <v>26</v>
       </c>
       <c r="D90" s="21">
         <f>SUM(C3:C90)</f>
         <v>-1206.96</v>
       </c>
-      <c r="E90" s="34"/>
+      <c r="E90" s="35"/>
     </row>
     <row r="91" spans="1:5">
-      <c r="A91" s="24">
+      <c r="A91" s="25">
         <v>45881</v>
       </c>
-      <c r="B91" s="33" t="s">
+      <c r="B91" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="C91" s="26">
+      <c r="C91" s="27">
         <v>5</v>
       </c>
       <c r="D91" s="21">
         <f>SUM(C3:C91)</f>
         <v>-1201.96</v>
       </c>
-      <c r="E91" s="34" t="s">
+      <c r="E91" s="35" t="s">
         <v>33</v>
       </c>
     </row>
@@ -3746,1149 +3788,1172 @@
       <c r="A92" s="17">
         <v>45885</v>
       </c>
-      <c r="B92" s="33" t="s">
-        <v>71</v>
-      </c>
-      <c r="C92" s="26">
+      <c r="B92" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="C92" s="27">
         <v>0.5</v>
       </c>
       <c r="D92" s="21">
         <f>SUM(C3:C94)</f>
         <v>-1191.46</v>
       </c>
-      <c r="E92" s="34"/>
+      <c r="E92" s="35"/>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="17"/>
-      <c r="B93" s="33" t="s">
+      <c r="B93" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="C93" s="26">
+      <c r="C93" s="27">
         <v>6</v>
       </c>
-      <c r="D93" s="30"/>
-      <c r="E93" s="34"/>
+      <c r="D93" s="31"/>
+      <c r="E93" s="35"/>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="17"/>
-      <c r="B94" s="33" t="s">
+      <c r="B94" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="C94" s="26">
+      <c r="C94" s="27">
         <v>4</v>
       </c>
-      <c r="D94" s="30"/>
-      <c r="E94" s="34"/>
+      <c r="D94" s="31"/>
+      <c r="E94" s="35"/>
     </row>
     <row r="95" spans="1:5">
-      <c r="A95" s="24">
+      <c r="A95" s="25">
         <v>45886</v>
       </c>
-      <c r="B95" s="33" t="s">
+      <c r="B95" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="C95" s="26">
+      <c r="C95" s="27">
         <v>5</v>
       </c>
       <c r="D95" s="21">
         <f>SUM(C3:C95)</f>
         <v>-1186.46</v>
       </c>
-      <c r="E95" s="34" t="s">
+      <c r="E95" s="35" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="96" spans="1:5">
-      <c r="A96" s="24">
+      <c r="A96" s="25">
         <v>45894</v>
       </c>
-      <c r="B96" s="33" t="s">
+      <c r="B96" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="C96" s="26">
+      <c r="C96" s="27">
         <v>1</v>
       </c>
       <c r="D96" s="21">
         <f>SUM(C3:C96)</f>
         <v>-1185.46</v>
       </c>
-      <c r="E96" s="34"/>
+      <c r="E96" s="35"/>
     </row>
     <row r="97" spans="1:5">
-      <c r="A97" s="24">
+      <c r="A97" s="25">
         <v>45905</v>
       </c>
-      <c r="B97" s="33" t="s">
+      <c r="B97" s="34" t="s">
         <v>56</v>
       </c>
-      <c r="C97" s="26">
+      <c r="C97" s="27">
         <v>7.33</v>
       </c>
       <c r="D97" s="21">
         <f>SUM(C3:C97)</f>
         <v>-1178.13</v>
       </c>
-      <c r="E97" s="34"/>
+      <c r="E97" s="35"/>
     </row>
     <row r="98" spans="1:5">
-      <c r="A98" s="24">
+      <c r="A98" s="25">
         <v>45907</v>
       </c>
-      <c r="B98" s="33" t="s">
+      <c r="B98" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="C98" s="26">
+      <c r="C98" s="27">
         <v>2</v>
       </c>
       <c r="D98" s="21">
         <f>SUM(C3:C102)</f>
         <v>-1168.13</v>
       </c>
-      <c r="E98" s="34"/>
+      <c r="E98" s="35"/>
     </row>
     <row r="99" spans="1:5">
-      <c r="A99" s="31"/>
-      <c r="B99" s="33" t="s">
+      <c r="A99" s="32"/>
+      <c r="B99" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="C99" s="26">
+      <c r="C99" s="27">
         <v>2</v>
       </c>
-      <c r="D99" s="30"/>
-      <c r="E99" s="34"/>
+      <c r="D99" s="31"/>
+      <c r="E99" s="35"/>
     </row>
     <row r="100" spans="1:5">
-      <c r="A100" s="31"/>
-      <c r="B100" s="33" t="s">
+      <c r="A100" s="32"/>
+      <c r="B100" s="34" t="s">
         <v>64</v>
       </c>
-      <c r="C100" s="26">
+      <c r="C100" s="27">
         <v>2</v>
       </c>
-      <c r="D100" s="30"/>
-      <c r="E100" s="34"/>
+      <c r="D100" s="31"/>
+      <c r="E100" s="35"/>
     </row>
     <row r="101" spans="1:5">
-      <c r="A101" s="31"/>
-      <c r="B101" s="33" t="s">
+      <c r="A101" s="32"/>
+      <c r="B101" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="C101" s="26">
+      <c r="C101" s="27">
         <v>2</v>
       </c>
-      <c r="D101" s="30"/>
-      <c r="E101" s="34"/>
+      <c r="D101" s="31"/>
+      <c r="E101" s="35"/>
     </row>
     <row r="102" spans="1:5">
-      <c r="A102" s="31"/>
-      <c r="B102" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="C102" s="26">
+      <c r="A102" s="32"/>
+      <c r="B102" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="C102" s="27">
         <v>2</v>
       </c>
-      <c r="D102" s="30"/>
-      <c r="E102" s="34"/>
+      <c r="D102" s="31"/>
+      <c r="E102" s="35"/>
     </row>
     <row r="103" spans="1:5">
-      <c r="A103" s="24">
+      <c r="A103" s="25">
         <v>45915</v>
       </c>
-      <c r="B103" s="33"/>
-      <c r="C103" s="32">
+      <c r="B103" s="34"/>
+      <c r="C103" s="33">
         <v>-130</v>
       </c>
       <c r="D103" s="21">
         <f>SUM(C3:C103)</f>
         <v>-1298.13</v>
       </c>
-      <c r="E103" s="34" t="s">
-        <v>75</v>
+      <c r="E103" s="35" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="104" spans="1:5">
-      <c r="A104" s="24">
+      <c r="A104" s="25">
         <v>45916</v>
       </c>
-      <c r="B104" s="33" t="s">
+      <c r="B104" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="C104" s="26">
+      <c r="C104" s="27">
         <v>6</v>
       </c>
       <c r="D104" s="21">
         <f>SUM(C3:C104)</f>
         <v>-1292.13</v>
       </c>
-      <c r="E104" s="34" t="s">
+      <c r="E104" s="35" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="105" spans="1:5">
-      <c r="A105" s="24">
+      <c r="A105" s="25">
         <v>45925</v>
       </c>
-      <c r="B105" s="33" t="s">
+      <c r="B105" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="C105" s="26">
+      <c r="C105" s="27">
         <v>10</v>
       </c>
       <c r="D105" s="21">
         <f>SUM(C3:C105)</f>
         <v>-1282.13</v>
       </c>
-      <c r="E105" s="34"/>
+      <c r="E105" s="35"/>
     </row>
     <row r="106" spans="1:5">
-      <c r="A106" s="24">
+      <c r="A106" s="25">
         <v>45930</v>
       </c>
-      <c r="B106" s="33" t="s">
+      <c r="B106" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="C106" s="26">
+      <c r="C106" s="27">
         <v>15</v>
       </c>
       <c r="D106" s="21">
         <f>SUM(C3:C106)</f>
         <v>-1267.13</v>
       </c>
-      <c r="E106" s="34"/>
+      <c r="E106" s="35"/>
     </row>
     <row r="107" spans="1:5">
-      <c r="A107" s="24">
+      <c r="A107" s="25">
         <v>45934</v>
       </c>
-      <c r="B107" s="33" t="s">
+      <c r="B107" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="C107" s="26">
+      <c r="C107" s="27">
         <v>2</v>
       </c>
       <c r="D107" s="21">
         <f>SUM(C3:C107)</f>
         <v>-1265.13</v>
       </c>
-      <c r="E107" s="34"/>
+      <c r="E107" s="35"/>
     </row>
     <row r="108" spans="1:5">
-      <c r="A108" s="31"/>
-      <c r="B108" s="33" t="s">
+      <c r="A108" s="32"/>
+      <c r="B108" s="34" t="s">
         <v>64</v>
       </c>
-      <c r="C108" s="26">
+      <c r="C108" s="27">
         <v>2</v>
       </c>
       <c r="D108" s="21">
         <f>SUM(C3:C108)</f>
         <v>-1263.13</v>
       </c>
-      <c r="E108" s="34"/>
+      <c r="E108" s="35"/>
     </row>
     <row r="109" spans="1:5">
-      <c r="A109" s="31"/>
-      <c r="B109" s="33" t="s">
+      <c r="A109" s="32"/>
+      <c r="B109" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="C109" s="26">
+      <c r="C109" s="27">
         <v>0.45</v>
       </c>
       <c r="D109" s="21">
         <f>SUM(C3:C109)</f>
         <v>-1262.68</v>
       </c>
-      <c r="E109" s="34"/>
+      <c r="E109" s="35"/>
     </row>
     <row r="110" spans="1:5">
-      <c r="A110" s="24">
+      <c r="A110" s="25">
         <v>45965</v>
       </c>
-      <c r="B110" s="33" t="s">
+      <c r="B110" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="C110" s="26">
+      <c r="C110" s="27">
         <v>60</v>
       </c>
       <c r="D110" s="21">
         <f>SUM(C3:C110)</f>
         <v>-1202.68</v>
       </c>
-      <c r="E110" s="34"/>
+      <c r="E110" s="35"/>
     </row>
     <row r="111" spans="1:5">
-      <c r="A111" s="24">
+      <c r="A111" s="25">
         <v>45968</v>
       </c>
-      <c r="B111" s="33" t="s">
+      <c r="B111" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="C111" s="26">
+      <c r="C111" s="27">
         <v>5</v>
       </c>
       <c r="D111" s="21">
         <f>SUM(C3:C111)</f>
         <v>-1197.68</v>
       </c>
-      <c r="E111" s="34"/>
+      <c r="E111" s="35"/>
     </row>
     <row r="112" spans="1:5">
-      <c r="A112" s="24">
+      <c r="A112" s="25">
         <v>45969</v>
       </c>
-      <c r="B112" s="33" t="s">
+      <c r="B112" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="C112" s="26">
+      <c r="C112" s="27">
         <v>6</v>
       </c>
       <c r="D112" s="21">
         <f>SUM(C3:C112)</f>
         <v>-1191.68</v>
       </c>
-      <c r="E112" s="34"/>
+      <c r="E112" s="35"/>
     </row>
     <row r="113" spans="1:5">
-      <c r="A113" s="24">
+      <c r="A113" s="25">
         <v>45972</v>
       </c>
-      <c r="B113" s="33" t="s">
+      <c r="B113" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="C113" s="26">
+      <c r="C113" s="27">
         <v>60</v>
       </c>
       <c r="D113" s="21">
         <f>SUM(C3:C113)</f>
         <v>-1131.68</v>
       </c>
-      <c r="E113" s="34"/>
+      <c r="E113" s="35"/>
     </row>
     <row r="114" spans="1:5">
-      <c r="A114" s="24">
+      <c r="A114" s="25">
         <v>45975</v>
       </c>
-      <c r="B114" s="33" t="s">
+      <c r="B114" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="C114" s="26">
+      <c r="C114" s="27">
         <v>37</v>
       </c>
       <c r="D114" s="21">
         <f>SUM(C3:C114)</f>
         <v>-1094.68</v>
       </c>
-      <c r="E114" s="34"/>
+      <c r="E114" s="35"/>
     </row>
     <row r="115" spans="1:5">
-      <c r="A115" s="24">
+      <c r="A115" s="25">
         <v>45976</v>
       </c>
-      <c r="B115" s="33" t="s">
-        <v>66</v>
-      </c>
-      <c r="C115" s="26">
+      <c r="B115" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="C115" s="27">
         <v>2.5</v>
       </c>
       <c r="D115" s="21">
         <f>SUM(C3:C115)</f>
         <v>-1092.18</v>
       </c>
-      <c r="E115" s="34"/>
+      <c r="E115" s="35"/>
     </row>
     <row r="116" spans="1:5">
-      <c r="A116" s="24">
+      <c r="A116" s="25">
         <v>45980</v>
       </c>
-      <c r="B116" s="33" t="s">
+      <c r="B116" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="C116" s="26">
+      <c r="C116" s="27">
         <v>20</v>
       </c>
       <c r="D116" s="21">
         <f>SUM(C3:C116)</f>
         <v>-1072.18</v>
       </c>
-      <c r="E116" s="34"/>
+      <c r="E116" s="35"/>
     </row>
     <row r="117" spans="1:5">
-      <c r="A117" s="24">
+      <c r="A117" s="25">
         <v>45990</v>
       </c>
-      <c r="B117" s="33" t="s">
+      <c r="B117" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="C117" s="26">
+      <c r="C117" s="27">
         <v>1</v>
       </c>
       <c r="D117" s="21">
         <f>SUM(C3:C117)</f>
         <v>-1071.18</v>
       </c>
-      <c r="E117" s="34"/>
+      <c r="E117" s="35"/>
     </row>
     <row r="118" spans="1:5">
-      <c r="A118" s="24">
+      <c r="A118" s="25">
         <v>46012</v>
       </c>
-      <c r="B118" s="33" t="s">
+      <c r="B118" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="C118" s="26">
+      <c r="C118" s="27">
         <v>10</v>
       </c>
       <c r="D118" s="21">
         <f>SUM(C3:C118)</f>
         <v>-1061.18</v>
       </c>
-      <c r="E118" s="34"/>
+      <c r="E118" s="35"/>
     </row>
     <row r="119" spans="1:5">
-      <c r="A119" s="24">
+      <c r="A119" s="25">
         <v>46029</v>
       </c>
-      <c r="B119" s="33" t="s">
+      <c r="B119" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="C119" s="26">
+      <c r="C119" s="27">
         <v>16</v>
       </c>
       <c r="D119" s="21">
         <f>SUM(C3:C119)</f>
         <v>-1045.18</v>
       </c>
-      <c r="E119" s="34"/>
+      <c r="E119" s="35"/>
     </row>
     <row r="120" spans="1:5">
-      <c r="A120" s="24">
+      <c r="A120" s="25">
         <v>46031</v>
       </c>
-      <c r="B120" s="33" t="s">
+      <c r="B120" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="C120" s="26">
+      <c r="C120" s="27">
         <v>2</v>
       </c>
       <c r="D120" s="21">
         <f>SUM(C3:C120)</f>
         <v>-1043.18</v>
       </c>
-      <c r="E120" s="34"/>
+      <c r="E120" s="35"/>
     </row>
     <row r="121" spans="1:5">
-      <c r="A121" s="24">
+      <c r="A121" s="25">
         <v>46038</v>
       </c>
-      <c r="B121" s="33" t="s">
+      <c r="B121" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="C121" s="26">
+      <c r="C121" s="27">
         <v>66</v>
       </c>
       <c r="D121" s="21">
         <f>SUM(C3:C121)</f>
         <v>-977.18</v>
       </c>
-      <c r="E121" s="34"/>
+      <c r="E121" s="35"/>
     </row>
     <row r="122" spans="1:5">
-      <c r="A122" s="24">
+      <c r="A122" s="25">
         <v>46039</v>
       </c>
-      <c r="B122" s="33" t="s">
+      <c r="B122" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="C122" s="26">
+      <c r="C122" s="27">
         <v>1</v>
       </c>
       <c r="D122" s="21">
         <f>SUM(C3:C122)</f>
         <v>-976.18</v>
       </c>
-      <c r="E122" s="34"/>
+      <c r="E122" s="35"/>
     </row>
     <row r="123" spans="1:5">
-      <c r="A123" s="24">
+      <c r="A123" s="25">
         <v>46047</v>
       </c>
-      <c r="B123" s="33" t="s">
+      <c r="B123" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="C123" s="26">
+      <c r="C123" s="27">
         <v>7</v>
       </c>
       <c r="D123" s="21">
         <f>SUM(C3:C123)</f>
         <v>-969.18</v>
       </c>
-      <c r="E123" s="34"/>
+      <c r="E123" s="35"/>
     </row>
     <row r="124" spans="1:5">
-      <c r="A124" s="31"/>
-      <c r="B124" s="33" t="s">
+      <c r="A124" s="32"/>
+      <c r="B124" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="C124" s="26">
+      <c r="C124" s="27">
         <v>11</v>
       </c>
       <c r="D124" s="21">
         <f>SUM(C3:C124)</f>
         <v>-958.18</v>
       </c>
-      <c r="E124" s="34"/>
+      <c r="E124" s="35"/>
     </row>
     <row r="125" spans="1:5">
-      <c r="A125" s="24">
+      <c r="A125" s="25">
         <v>46054</v>
       </c>
-      <c r="B125" s="33" t="s">
+      <c r="B125" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="C125" s="26">
+      <c r="C125" s="27">
         <v>5</v>
       </c>
       <c r="D125" s="21">
         <f>SUM(C3:C125)</f>
         <v>-953.18</v>
       </c>
-      <c r="E125" s="34" t="s">
+      <c r="E125" s="35" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="126" spans="1:5">
-      <c r="A126" s="24">
+      <c r="A126" s="25">
         <v>46055</v>
       </c>
-      <c r="B126" s="33" t="s">
+      <c r="B126" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="C126" s="26">
+      <c r="C126" s="27">
         <v>36</v>
       </c>
       <c r="D126" s="21">
         <f>SUM(C3:C126)</f>
         <v>-917.18</v>
       </c>
-      <c r="E126" s="34"/>
+      <c r="E126" s="35"/>
     </row>
     <row r="127" spans="1:5">
-      <c r="A127" s="24">
+      <c r="A127" s="25">
         <v>46057</v>
       </c>
-      <c r="B127" s="33" t="s">
+      <c r="B127" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="C127" s="26">
+      <c r="C127" s="27">
         <v>5</v>
       </c>
       <c r="D127" s="21">
         <f>SUM(C3:C127)</f>
         <v>-912.18</v>
       </c>
-      <c r="E127" s="34" t="s">
+      <c r="E127" s="35" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="128" spans="1:5">
-      <c r="A128" s="35">
+      <c r="A128" s="36">
         <v>46068</v>
       </c>
-      <c r="B128" s="33" t="s">
+      <c r="B128" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="C128" s="26">
+      <c r="C128" s="27">
         <v>78</v>
       </c>
       <c r="D128" s="21">
         <f>SUM(C3:C128)</f>
         <v>-834.18</v>
       </c>
-      <c r="E128" s="34"/>
+      <c r="E128" s="35"/>
     </row>
     <row r="129" spans="1:5">
-      <c r="A129" s="36"/>
-      <c r="B129" s="33" t="s">
+      <c r="A129" s="37"/>
+      <c r="B129" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="C129" s="26">
+      <c r="C129" s="27">
         <v>30</v>
       </c>
       <c r="D129" s="21">
         <f>SUM(C3:C129)</f>
         <v>-804.18</v>
       </c>
-      <c r="E129" s="34"/>
+      <c r="E129" s="35"/>
     </row>
     <row r="130" spans="1:5">
-      <c r="A130" s="24">
+      <c r="A130" s="25">
         <v>46069</v>
       </c>
-      <c r="B130" s="33" t="s">
+      <c r="B130" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="C130" s="26">
+      <c r="C130" s="27">
         <v>5</v>
       </c>
       <c r="D130" s="21">
         <f>SUM(C3:C130)</f>
         <v>-799.18</v>
       </c>
-      <c r="E130" s="34"/>
+      <c r="E130" s="35"/>
     </row>
     <row r="131" spans="1:5">
-      <c r="A131" s="31"/>
-      <c r="B131" s="33" t="s">
+      <c r="A131" s="32"/>
+      <c r="B131" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="C131" s="26">
+      <c r="C131" s="27">
         <v>8</v>
       </c>
       <c r="D131" s="21">
         <f>SUM(C3:C131)</f>
         <v>-791.18</v>
       </c>
-      <c r="E131" s="34"/>
+      <c r="E131" s="35"/>
     </row>
     <row r="132" spans="1:5">
-      <c r="A132" s="31"/>
-      <c r="B132" s="33" t="s">
+      <c r="A132" s="32"/>
+      <c r="B132" s="34" t="s">
         <v>50</v>
       </c>
-      <c r="C132" s="26">
+      <c r="C132" s="27">
         <v>10</v>
       </c>
       <c r="D132" s="21">
         <f>SUM(C3:C132)</f>
         <v>-781.18</v>
       </c>
-      <c r="E132" s="34"/>
+      <c r="E132" s="35"/>
     </row>
     <row r="133" spans="1:5">
-      <c r="A133" s="24">
+      <c r="A133" s="25">
         <v>46070</v>
       </c>
-      <c r="B133" s="33" t="s">
+      <c r="B133" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="C133" s="26">
+      <c r="C133" s="27">
         <v>8.32</v>
       </c>
       <c r="D133" s="21">
         <f>SUM(C3:C133)</f>
         <v>-772.86</v>
       </c>
-      <c r="E133" s="34"/>
+      <c r="E133" s="35"/>
     </row>
     <row r="134" spans="1:5">
-      <c r="A134" s="31"/>
-      <c r="B134" s="33" t="s">
+      <c r="A134" s="32"/>
+      <c r="B134" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="C134" s="26">
+      <c r="C134" s="27">
         <v>10</v>
       </c>
       <c r="D134" s="21">
         <f>SUM(C3:C134)</f>
         <v>-762.86</v>
       </c>
-      <c r="E134" s="34"/>
+      <c r="E134" s="35"/>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="17">
         <v>46074</v>
       </c>
-      <c r="B135" s="33" t="s">
+      <c r="B135" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="C135" s="26">
+      <c r="C135" s="27">
         <v>1.5</v>
       </c>
       <c r="D135" s="21">
         <f>SUM(C3:C135)</f>
         <v>-761.36</v>
       </c>
-      <c r="E135" s="34"/>
+      <c r="E135" s="35"/>
     </row>
     <row r="136" spans="1:5">
-      <c r="A136" s="24">
+      <c r="A136" s="25">
         <v>46079</v>
       </c>
-      <c r="B136" s="33" t="s">
+      <c r="B136" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="C136" s="26">
+      <c r="C136" s="27">
         <v>25</v>
       </c>
       <c r="D136" s="21">
         <f>SUM(C3:C136)</f>
         <v>-736.36</v>
       </c>
-      <c r="E136" s="34" t="s">
+      <c r="E136" s="35" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="137" spans="1:5">
-      <c r="A137" s="24">
+      <c r="A137" s="25">
         <v>46085</v>
       </c>
-      <c r="B137" s="33" t="s">
+      <c r="B137" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="C137" s="26">
+      <c r="C137" s="27">
         <v>10</v>
       </c>
       <c r="D137" s="21">
         <f>SUM(C3:C137)</f>
         <v>-726.36</v>
       </c>
-      <c r="E137" s="34"/>
+      <c r="E137" s="35"/>
     </row>
     <row r="138" spans="1:5">
-      <c r="A138" s="24">
+      <c r="A138" s="25">
         <v>46123</v>
       </c>
-      <c r="B138" s="33" t="s">
+      <c r="B138" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="C138" s="26">
+      <c r="C138" s="27">
         <v>70</v>
       </c>
       <c r="D138" s="21">
         <f>SUM(C3:C138)</f>
         <v>-656.36</v>
       </c>
-      <c r="E138" s="34" t="s">
+      <c r="E138" s="35" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="139" spans="1:5">
-      <c r="A139" s="24">
+      <c r="A139" s="25">
         <v>46130</v>
       </c>
-      <c r="B139" s="33" t="s">
+      <c r="B139" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="C139" s="26">
+      <c r="C139" s="27">
         <v>3</v>
       </c>
       <c r="D139" s="21">
         <f>SUM(C3:C139)</f>
         <v>-653.36</v>
       </c>
-      <c r="E139" s="34"/>
+      <c r="E139" s="35"/>
     </row>
     <row r="140" spans="1:5">
-      <c r="A140" s="24">
+      <c r="A140" s="25">
         <v>46135</v>
       </c>
-      <c r="B140" s="33"/>
-      <c r="C140" s="32">
+      <c r="B140" s="34"/>
+      <c r="C140" s="33">
         <v>-2497.79</v>
       </c>
       <c r="D140" s="21">
         <f>SUM(C3:C140)</f>
         <v>-3151.15</v>
       </c>
-      <c r="E140" s="34" t="s">
-        <v>76</v>
+      <c r="E140" s="35" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="141" spans="1:5">
-      <c r="A141" s="24">
+      <c r="A141" s="25">
         <v>46136</v>
       </c>
-      <c r="B141" s="33" t="s">
+      <c r="B141" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="C141" s="26">
+      <c r="C141" s="27">
         <v>15</v>
       </c>
       <c r="D141" s="21">
         <f>SUM(C3:C141)</f>
         <v>-3136.15</v>
       </c>
-      <c r="E141" s="34" t="s">
+      <c r="E141" s="35" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="142" spans="1:5">
-      <c r="A142" s="24">
+      <c r="A142" s="25">
         <v>46141</v>
       </c>
-      <c r="B142" s="33" t="s">
+      <c r="B142" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="C142" s="26">
+      <c r="C142" s="27">
         <v>10</v>
       </c>
       <c r="D142" s="21">
         <f>SUM(C3:C142)</f>
         <v>-3126.15</v>
       </c>
-      <c r="E142" s="34"/>
+      <c r="E142" s="35"/>
     </row>
     <row r="143" spans="1:5">
-      <c r="A143" s="31"/>
-      <c r="B143" s="33" t="s">
+      <c r="A143" s="32"/>
+      <c r="B143" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="C143" s="26">
+      <c r="C143" s="27">
         <v>10</v>
       </c>
       <c r="D143" s="21">
         <f>SUM(C3:C143)</f>
         <v>-3116.15</v>
       </c>
-      <c r="E143" s="34"/>
+      <c r="E143" s="35"/>
     </row>
     <row r="144" spans="1:5">
-      <c r="A144" s="24">
+      <c r="A144" s="25">
         <v>46144</v>
       </c>
-      <c r="B144" s="33" t="s">
+      <c r="B144" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="C144" s="26">
+      <c r="C144" s="27">
         <v>1</v>
       </c>
       <c r="D144" s="21">
         <f>SUM(C3:C144)</f>
         <v>-3115.15</v>
       </c>
-      <c r="E144" s="34"/>
+      <c r="E144" s="35"/>
     </row>
     <row r="145" spans="1:5">
-      <c r="A145" s="24">
+      <c r="A145" s="25">
         <v>46145</v>
       </c>
-      <c r="B145" s="33" t="s">
+      <c r="B145" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="C145" s="26">
+      <c r="C145" s="27">
         <v>10</v>
       </c>
       <c r="D145" s="21">
         <f>SUM(C3:C145)</f>
         <v>-3105.15</v>
       </c>
-      <c r="E145" s="34"/>
+      <c r="E145" s="35"/>
     </row>
     <row r="146" spans="1:5">
-      <c r="A146" s="31"/>
-      <c r="B146" s="33" t="s">
+      <c r="A146" s="32"/>
+      <c r="B146" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="C146" s="26">
+      <c r="C146" s="27">
         <v>6</v>
       </c>
       <c r="D146" s="21">
         <f>SUM(C3:C146)</f>
         <v>-3099.15</v>
       </c>
-      <c r="E146" s="34"/>
+      <c r="E146" s="35"/>
     </row>
     <row r="147" spans="1:5">
-      <c r="A147" s="24">
+      <c r="A147" s="25">
         <v>46146</v>
       </c>
-      <c r="B147" s="33" t="s">
+      <c r="B147" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="C147" s="26">
+      <c r="C147" s="27">
         <v>20</v>
       </c>
       <c r="D147" s="21">
         <f>SUM(C3:C147)</f>
         <v>-3079.15</v>
       </c>
-      <c r="E147" s="34"/>
+      <c r="E147" s="35"/>
     </row>
     <row r="148" spans="1:5">
-      <c r="A148" s="24">
+      <c r="A148" s="25">
         <v>46158</v>
       </c>
-      <c r="B148" s="33" t="s">
+      <c r="B148" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="C148" s="26">
+      <c r="C148" s="27">
         <v>20</v>
       </c>
       <c r="D148" s="21">
         <f>SUM(C3:C148)</f>
         <v>-3059.15</v>
       </c>
-      <c r="E148" s="34" t="s">
+      <c r="E148" s="35" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="149" spans="1:5">
-      <c r="A149" s="24">
+      <c r="A149" s="25">
         <v>46160</v>
       </c>
-      <c r="B149" s="33" t="s">
+      <c r="B149" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="C149" s="26">
+      <c r="C149" s="27">
         <v>5.04</v>
       </c>
       <c r="D149" s="21">
         <f>SUM(C3:C149)</f>
         <v>-3054.11</v>
       </c>
-      <c r="E149" s="34"/>
+      <c r="E149" s="35"/>
     </row>
     <row r="150" spans="1:5">
-      <c r="A150" s="24">
+      <c r="A150" s="25">
         <v>46179</v>
       </c>
-      <c r="B150" s="33" t="s">
+      <c r="B150" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="C150" s="26">
+      <c r="C150" s="27">
         <v>30</v>
       </c>
       <c r="D150" s="21">
         <f>SUM(C3:C150)</f>
         <v>-3024.11</v>
       </c>
-      <c r="E150" s="34" t="s">
+      <c r="E150" s="35" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="151" spans="1:5">
-      <c r="A151" s="24">
+      <c r="A151" s="25">
         <v>46184</v>
       </c>
-      <c r="B151" s="33" t="s">
+      <c r="B151" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="C151" s="26">
+      <c r="C151" s="27">
         <v>10</v>
       </c>
       <c r="D151" s="21">
         <f>SUM(C3:C151)</f>
         <v>-3014.11</v>
       </c>
-      <c r="E151" s="34"/>
+      <c r="E151" s="35"/>
     </row>
     <row r="152" spans="1:5">
-      <c r="A152" s="24">
+      <c r="A152" s="25">
         <v>46192</v>
       </c>
-      <c r="B152" s="33" t="s">
+      <c r="B152" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="C152" s="26">
+      <c r="C152" s="27">
         <v>20</v>
       </c>
       <c r="D152" s="21">
         <f>SUM(C3:C152)</f>
         <v>-2994.11</v>
       </c>
-      <c r="E152" s="34" t="s">
+      <c r="E152" s="35" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="153" spans="1:5">
-      <c r="A153" s="24">
+      <c r="A153" s="25">
         <v>46193</v>
       </c>
-      <c r="B153" s="33" t="s">
+      <c r="B153" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="C153" s="26">
+      <c r="C153" s="27">
         <v>50</v>
       </c>
       <c r="D153" s="21">
         <f>SUM(C3:C153)</f>
         <v>-2944.11</v>
       </c>
-      <c r="E153" s="34"/>
+      <c r="E153" s="35"/>
     </row>
     <row r="154" spans="1:5">
-      <c r="A154" s="31"/>
-      <c r="B154" s="33" t="s">
+      <c r="A154" s="32"/>
+      <c r="B154" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="C154" s="26">
+      <c r="C154" s="27">
         <v>10</v>
       </c>
       <c r="D154" s="21">
         <f>SUM(C3:C154)</f>
         <v>-2934.11</v>
       </c>
-      <c r="E154" s="34" t="s">
+      <c r="E154" s="35" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="155" spans="1:5">
-      <c r="A155" s="24">
+      <c r="A155" s="25">
         <v>46196</v>
       </c>
-      <c r="B155" s="33" t="s">
+      <c r="B155" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="C155" s="26">
+      <c r="C155" s="27">
         <v>25</v>
       </c>
       <c r="D155" s="21">
         <f>SUM(C3:C155)</f>
         <v>-2909.11</v>
       </c>
-      <c r="E155" s="34"/>
+      <c r="E155" s="35"/>
     </row>
     <row r="156" spans="1:5">
-      <c r="A156" s="24">
+      <c r="A156" s="25">
         <v>46204</v>
       </c>
-      <c r="B156" s="33" t="s">
+      <c r="B156" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="C156" s="26">
+      <c r="C156" s="27">
         <v>20</v>
       </c>
       <c r="D156" s="21">
         <f>SUM(C3:C156)</f>
         <v>-2889.11</v>
       </c>
-      <c r="E156" s="34" t="s">
+      <c r="E156" s="35" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="157" spans="1:5">
-      <c r="A157" s="24">
+      <c r="A157" s="25">
         <v>46205</v>
       </c>
-      <c r="B157" s="33" t="s">
+      <c r="B157" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="C157" s="26">
+      <c r="C157" s="27">
         <v>8</v>
       </c>
       <c r="D157" s="21">
         <f>SUM(C3:C157)</f>
         <v>-2881.11</v>
       </c>
-      <c r="E157" s="34"/>
+      <c r="E157" s="35"/>
     </row>
     <row r="158" spans="1:5">
-      <c r="A158" s="31"/>
-      <c r="B158" s="33" t="s">
+      <c r="A158" s="32"/>
+      <c r="B158" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="C158" s="26">
+      <c r="C158" s="27">
         <v>240</v>
       </c>
       <c r="D158" s="21">
         <f>SUM(C3:C158)</f>
         <v>-2641.11</v>
       </c>
-      <c r="E158" s="34"/>
+      <c r="E158" s="35"/>
     </row>
     <row r="159" spans="1:5">
-      <c r="A159" s="31"/>
-      <c r="B159" s="33" t="s">
+      <c r="A159" s="32"/>
+      <c r="B159" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="C159" s="26">
+      <c r="C159" s="27">
         <v>10</v>
       </c>
       <c r="D159" s="21">
         <f>SUM(C3:C159)</f>
         <v>-2631.11</v>
       </c>
-      <c r="E159" s="34" t="s">
+      <c r="E159" s="35" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="160" spans="1:5">
-      <c r="A160" s="24">
+      <c r="A160" s="25">
         <v>46206</v>
       </c>
-      <c r="B160" s="33" t="s">
+      <c r="B160" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="C160" s="26">
+      <c r="C160" s="27">
         <v>5</v>
       </c>
       <c r="D160" s="21">
         <f>SUM(C3:C160)</f>
         <v>-2626.11</v>
       </c>
-      <c r="E160" s="34" t="s">
+      <c r="E160" s="35" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="161" spans="1:5">
-      <c r="A161" s="24">
+      <c r="A161" s="25">
         <v>46210</v>
       </c>
-      <c r="B161" s="33" t="s">
+      <c r="B161" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="C161" s="26">
+      <c r="C161" s="27">
         <v>33</v>
       </c>
       <c r="D161" s="21">
         <f>SUM(C3:C161)</f>
         <v>-2593.11</v>
       </c>
-      <c r="E161" s="34"/>
+      <c r="E161" s="35"/>
     </row>
     <row r="162" spans="1:5">
-      <c r="A162" s="24">
+      <c r="A162" s="25">
         <v>46219</v>
       </c>
-      <c r="B162" s="33" t="s">
+      <c r="B162" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="C162" s="26">
+      <c r="C162" s="27">
         <v>121.04</v>
       </c>
       <c r="D162" s="21">
         <f>SUM(C3:C162)</f>
         <v>-2472.07</v>
       </c>
-      <c r="E162" s="34"/>
+      <c r="E162" s="35"/>
     </row>
     <row r="163" spans="1:5">
-      <c r="A163" s="24">
+      <c r="A163" s="25">
         <v>46305</v>
       </c>
-      <c r="B163" s="33" t="s">
+      <c r="B163" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="C163" s="26">
+      <c r="C163" s="27">
         <v>12</v>
       </c>
       <c r="D163" s="21">
         <f>SUM(C3:C163)</f>
         <v>-2460.07</v>
       </c>
-      <c r="E163" s="34"/>
+      <c r="E163" s="35"/>
     </row>
     <row r="164" spans="1:5">
-      <c r="A164" s="37"/>
-      <c r="B164" s="38"/>
-      <c r="C164" s="39"/>
-      <c r="D164" s="39"/>
-      <c r="E164" s="40"/>
+      <c r="A164" s="38">
+        <v>46305</v>
+      </c>
+      <c r="B164" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="C164" s="40">
+        <v>2.74</v>
+      </c>
+      <c r="D164" s="21">
+        <f>SUM(C3:C164)</f>
+        <v>-2457.33</v>
+      </c>
+      <c r="E164" s="41"/>
     </row>
     <row r="165" spans="1:5">
-      <c r="A165" s="41" t="s">
-        <v>77</v>
-      </c>
-      <c r="B165" s="41"/>
-      <c r="C165" s="41"/>
-      <c r="D165" s="41"/>
+      <c r="A165" s="38"/>
+      <c r="B165" s="39"/>
+      <c r="C165" s="40"/>
+      <c r="D165" s="42"/>
       <c r="E165" s="41"/>
+    </row>
+    <row r="166" spans="1:5">
+      <c r="A166" s="43"/>
+      <c r="B166" s="44"/>
+      <c r="C166" s="45"/>
+      <c r="D166" s="45"/>
+      <c r="E166" s="46"/>
+    </row>
+    <row r="167" spans="1:5">
+      <c r="A167" s="47" t="s">
+        <v>80</v>
+      </c>
+      <c r="B167" s="47"/>
+      <c r="C167" s="47"/>
+      <c r="D167" s="47"/>
+      <c r="E167" s="47"/>
     </row>
   </sheetData>
   <mergeCells count="42">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="G1:K1"/>
-    <mergeCell ref="A165:E165"/>
+    <mergeCell ref="A167:E167"/>
     <mergeCell ref="A3:A7"/>
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="A23:A24"/>
@@ -4938,26 +5003,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1e706b11-9071-4342-b703-3936458eca29}</x14:id>
+          <x14:id>{fe93615c-9386-4e68-a3d8-dcd399127919}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I52">
-    <cfRule type="dataBar" priority="1">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{702023a5-6b76-4725-ab5a-e73a1a96687b}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D1:D18 D20:D23 D25:D26 D28:D42 D44:D45 D47:D48 D50:D51 D53 D55 D57:D60 D62:D64 D66:D73 D75:D92 D95:D98 D103:D164 D166:D1048576">
+  <conditionalFormatting sqref="D1:D18 D20:D23 D25:D26 D28:D42 D44:D45 D47:D48 D50:D51 D53 D55 D57:D60 D62:D64 D66:D73 D75:D92 D95:D98 D103:D166 D168:D1048576">
     <cfRule type="colorScale" priority="82">
       <colorScale>
         <cfvo type="min"/>
@@ -4978,12 +5029,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f2859ee8-d1f3-48c2-94dc-cdab6bbd66ea}</x14:id>
+          <x14:id>{6e1f2766-40dd-4fd6-ae6e-bc7674e878db}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I17 I19:I1048576">
+  <conditionalFormatting sqref="I1:I17 I19:I39 I41:I1048576">
     <cfRule type="dataBar" priority="2">
       <dataBar>
         <cfvo type="min"/>
@@ -4992,12 +5043,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c2fdf4eb-9309-4790-9577-64d0375898cf}</x14:id>
+          <x14:id>{8cec9d82-964e-46ef-9772-89fbb2530727}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I17 I29:I1048576 I19:I27">
+  <conditionalFormatting sqref="I1:I17 I29:I39 I41:I1048576 I19:I27">
     <cfRule type="dataBar" priority="3">
       <dataBar>
         <cfvo type="min"/>
@@ -5006,12 +5057,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{32a56779-809f-48ef-abe5-6499028ee3b1}</x14:id>
+          <x14:id>{0f6a72ee-a057-428c-8ed3-9638476122dd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I17 I29:I1048576 I27 I19:I25">
+  <conditionalFormatting sqref="I1:I17 I29:I39 I41:I1048576 I19:I25 I27">
     <cfRule type="dataBar" priority="21">
       <dataBar>
         <cfvo type="min"/>
@@ -5020,12 +5071,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4e5517ac-ac71-4595-b8ea-b3ebf3c4f558}</x14:id>
+          <x14:id>{6eab6aa1-105e-4d74-8ae0-c75db30c2d26}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I9 I29:I1048576 I11:I17 I27 I19 I21:I25">
+  <conditionalFormatting sqref="I1:I9 I29:I39 I41:I1048576 I11:I17 I27 I21:I25 I19">
     <cfRule type="dataBar" priority="24">
       <dataBar>
         <cfvo type="min"/>
@@ -5034,12 +5085,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d437ab4f-284f-4dce-87a8-883f66c3d40c}</x14:id>
+          <x14:id>{ba32311f-c293-45a0-ab90-991923d7d44e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I9 I29:I1048576 I11:I17 I27 I19 I21:I24">
+  <conditionalFormatting sqref="I1:I9 I29:I39 I41:I1048576 I11:I17 I27 I21:I24 I19">
     <cfRule type="dataBar" priority="25">
       <dataBar>
         <cfvo type="min"/>
@@ -5048,12 +5099,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7bd851aa-fab6-46d2-9e8f-f30f01213615}</x14:id>
+          <x14:id>{56d90323-347a-4c29-8ad9-80803c2b332e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I17 I29:I1048576 I21:I25 I19 I27">
+  <conditionalFormatting sqref="I1:I17 I29:I39 I41:I1048576 I19 I21:I25 I27">
     <cfRule type="dataBar" priority="23">
       <dataBar>
         <cfvo type="min"/>
@@ -5062,12 +5113,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8b33c886-3e56-416e-aac3-18e5b9e69aab}</x14:id>
+          <x14:id>{78e0a573-3615-47e7-9886-e8fb7ea90448}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2 I53:I1048576 I32">
+  <conditionalFormatting sqref="I2 I54:I1048576 I32">
     <cfRule type="dataBar" priority="51">
       <dataBar>
         <cfvo type="min"/>
@@ -5076,12 +5127,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a37213c5-d8c2-4d8a-b9b3-8854c5fda7e3}</x14:id>
+          <x14:id>{52e2b908-04b9-452d-be88-73c6181bddbb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I4 I29:I39 I6:I7 I41:I1048576 I9 I11:I17 I21:I24 I19 I27">
+  <conditionalFormatting sqref="I2:I4 I29:I39 I6:I7 I42:I1048576 I11:I17 I21:I24 I27 I19 I9">
     <cfRule type="dataBar" priority="28">
       <dataBar>
         <cfvo type="min"/>
@@ -5090,12 +5141,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5350f9cd-155e-472b-b411-a99f85295a24}</x14:id>
+          <x14:id>{d39af3c7-3fcf-48d3-bcb8-514f85206965}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I4 I29:I39 I41:I1048576 I11:I16 I9 I6:I7 I21:I24 I27 I19">
+  <conditionalFormatting sqref="I2:I4 I29:I39 I42:I1048576 I6:I7 I21:I24 I19 I27 I11:I16 I9">
     <cfRule type="dataBar" priority="32">
       <dataBar>
         <cfvo type="min"/>
@@ -5104,7 +5155,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8341e6f2-1230-4f64-84bf-d7d05e301a02}</x14:id>
+          <x14:id>{ce3da0d1-7d02-41b1-bdf0-f79a2bab99f3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5141,7 +5192,21 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I12:I14 I3:I4 I33:I35 I44:I49 I6:I7 I51:I52 I9 I38:I39 I41:I42 I30 I21:I24 I19 I27">
+  <conditionalFormatting sqref="I3:I39 I41:I53">
+    <cfRule type="dataBar" priority="1">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{3c5da360-cb42-4ee1-9004-9fc9ef0109e2}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I12:I14 I3:I4 I33:I35 I27 I6:I7 I19 I9 I38:I39 I21:I24 I30 I45:I50 I42:I43 I52:I53">
     <cfRule type="dataBar" priority="38">
       <dataBar>
         <cfvo type="min"/>
@@ -5150,12 +5215,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{16165f7b-7c0f-49c9-a2bf-e789513a0274}</x14:id>
+          <x14:id>{8c7a61aa-2fd6-4ed0-86e4-d93205ed0969}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I33:I35 I3:I4 I44:I49 I51:I52 I6:I7 I12:I14 I9 I41:I42 I38:I39 I19 I21:I24 I30">
+  <conditionalFormatting sqref="I33:I35 I3:I4 I30 I21:I24 I6:I7 I12:I14 I9 I19 I38:I39 I45:I50 I42:I43 I52:I53">
     <cfRule type="dataBar" priority="39">
       <dataBar>
         <cfvo type="min"/>
@@ -5164,12 +5229,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1930dc6f-ae55-44b4-bc75-eacc4e163e32}</x14:id>
+          <x14:id>{11cd33f6-fffc-4851-9dcb-540df78c69ae}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I16 I3:I4 I33:I35 I41:I42 I6:I7 I12:I14 I9 I44:I49 I51:I52 I38:I39 I30 I27 I21:I24 I19">
+  <conditionalFormatting sqref="I16 I3:I4 I33:I35 I19 I6:I7 I12:I14 I9 I21:I24 I27 I38:I39 I30 I42:I43 I52:I53 I45:I50">
     <cfRule type="dataBar" priority="36">
       <dataBar>
         <cfvo type="min"/>
@@ -5178,12 +5243,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3a06ec88-65f8-458a-a2ae-d66c87115e22}</x14:id>
+          <x14:id>{3b7df007-1318-46f6-b584-4fa2b37a3df5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I11:I14 I3:I4 I33:I36 I38:I39 I6:I7 I41:I42 I9 I16 I44:I52 I19 I27 I21:I24 I30:I31">
+  <conditionalFormatting sqref="I11:I14 I3:I4 I33:I36 I38:I39 I6:I7 I30:I31 I9 I16 I21:I24 I19 I27 I42:I43 I45:I53">
     <cfRule type="dataBar" priority="34">
       <dataBar>
         <cfvo type="min"/>
@@ -5192,12 +5257,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{612fc072-dda3-4faa-8079-9b7afcbb38a0}</x14:id>
+          <x14:id>{bcf3a045-e169-4344-8a46-bbea048fcff5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I38:I39 I3:I4 I44:I49 I51:I52 I6:I7 I16 I9 I11:I14 I33:I35 I41:I42 I21:I24 I27 I30:I31 I19">
+  <conditionalFormatting sqref="I38:I39 I3:I4 I19 I30:I31 I6:I7 I16 I9 I11:I14 I33:I35 I27 I21:I24 I45:I50 I42:I43 I52:I53">
     <cfRule type="dataBar" priority="35">
       <dataBar>
         <cfvo type="min"/>
@@ -5206,12 +5271,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2af321a6-43d8-439d-bf9e-502a21c6653b}</x14:id>
+          <x14:id>{85996752-cc3d-4c7a-91ec-59a2a0082fe4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I41:I52 I33:I39 I3:I4 I9 I11:I16 I6:I7 I19 I27 I29:I31 I21:I24">
+  <conditionalFormatting sqref="I21:I24 I33:I39 I3:I4 I9 I11:I16 I6:I7 I19 I27 I29:I31 I42:I53">
     <cfRule type="dataBar" priority="30">
       <dataBar>
         <cfvo type="min"/>
@@ -5220,12 +5285,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1e9ad7a3-a880-46af-b64c-6384d0bb9a85}</x14:id>
+          <x14:id>{8f03883d-6bc2-4348-a39d-6e9be7965527}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I11:I16 I3:I4 I33:I39 I41:I52 I6:I7 I9 I19 I21:I24 I27 I30:I31">
+  <conditionalFormatting sqref="I11:I16 I3:I4 I33:I39 I30:I31 I6:I7 I9 I19 I21:I24 I27 I42:I53">
     <cfRule type="dataBar" priority="33">
       <dataBar>
         <cfvo type="min"/>
@@ -5234,12 +5299,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1ede0976-3f5d-4548-a608-b5da5ee0adb8}</x14:id>
+          <x14:id>{840df7f5-c2a1-4cee-b2c8-314e2d820a35}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I11:I17 I41:I52 I3:I4 I33:I39 I9 I6:I7 I19 I21:I24 I27 I29:I31">
+  <conditionalFormatting sqref="I11:I17 I29:I31 I3:I4 I33:I39 I9 I6:I7 I19 I21:I24 I27 I42:I53">
     <cfRule type="dataBar" priority="29">
       <dataBar>
         <cfvo type="min"/>
@@ -5248,12 +5313,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e4db04cc-6be5-4ecd-b3e9-b1e5cf7d1031}</x14:id>
+          <x14:id>{835c0286-e79b-4e31-a6e5-89b49d1d58b5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I11:I17 I33:I52 I9 I3:I7 I27 I29:I31 I21:I24 I19">
+  <conditionalFormatting sqref="I11:I17 I33:I39 I19 I9 I3:I7 I27 I29:I31 I21:I24 I41:I53">
     <cfRule type="dataBar" priority="26">
       <dataBar>
         <cfvo type="min"/>
@@ -5262,12 +5327,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6c63add2-3203-45b5-89a2-4a12d8afc0b1}</x14:id>
+          <x14:id>{ae9fac30-fc82-47f3-9a5c-a3185969e7d9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I41:I52 I33:I39 I9 I3:I7 I11:I17 I19 I29:I31 I21:I24 I27">
+  <conditionalFormatting sqref="I27 I33:I39 I9 I3:I7 I11:I17 I19 I29:I31 I21:I24 I42:I53">
     <cfRule type="dataBar" priority="27">
       <dataBar>
         <cfvo type="min"/>
@@ -5276,12 +5341,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{300abaa2-c1d9-48b9-ae8e-05015977ad1a}</x14:id>
+          <x14:id>{9b00a8aa-386e-4c4e-b561-2763c24c7b76}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I33:I52 I3:I17 I19:I25 I29:I31 I27">
+  <conditionalFormatting sqref="I33:I39 I27 I3:I17 I19:I25 I29:I31 I41:I53">
     <cfRule type="dataBar" priority="22">
       <dataBar>
         <cfvo type="min"/>
@@ -5290,7 +5355,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ee1fe562-cfba-4b9c-8a63-a97f8821f0c2}</x14:id>
+          <x14:id>{09ae2eac-49db-43b7-a6d9-14db4c2446d5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5298,13 +5363,13 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="E40:E41 E45 E48:E49 E34 E36:E37 D3 D8:D108 E8:E14 E16:E17 E19:E20 E22:E23 E25:E27 E29" formulaRange="1"/>
+    <ignoredError sqref="E29 E25:E27 E22:E23 E19:E20 E16:E17 E8:E14 D8:D108 D3 E36:E37 E34 E48:E49 E45 E40:E41" formulaRange="1"/>
   </ignoredErrors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1e706b11-9071-4342-b703-3936458eca29}">
+          <x14:cfRule type="dataBar" id="{fe93615c-9386-4e68-a3d8-dcd399127919}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5315,18 +5380,7 @@
           <xm:sqref>I26</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{702023a5-6b76-4725-ab5a-e73a1a96687b}">
-            <x14:dataBar minLength="0" maxLength="100" gradient="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>I3:I52</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f2859ee8-d1f3-48c2-94dc-cdab6bbd66ea}">
+          <x14:cfRule type="dataBar" id="{6e1f2766-40dd-4fd6-ae6e-bc7674e878db}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5339,7 +5393,7 @@
           <xm:sqref>G1 G2:I2</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c2fdf4eb-9309-4790-9577-64d0375898cf}">
+          <x14:cfRule type="dataBar" id="{8cec9d82-964e-46ef-9772-89fbb2530727}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5347,10 +5401,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I1:I17 I19:I1048576</xm:sqref>
+          <xm:sqref>I1:I17 I19:I39 I41:I1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{32a56779-809f-48ef-abe5-6499028ee3b1}">
+          <x14:cfRule type="dataBar" id="{0f6a72ee-a057-428c-8ed3-9638476122dd}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5358,10 +5412,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I1:I17 I29:I1048576 I19:I27</xm:sqref>
+          <xm:sqref>I1:I17 I29:I39 I41:I1048576 I19:I27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4e5517ac-ac71-4595-b8ea-b3ebf3c4f558}">
+          <x14:cfRule type="dataBar" id="{6eab6aa1-105e-4d74-8ae0-c75db30c2d26}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5369,10 +5423,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I1:I17 I29:I1048576 I27 I19:I25</xm:sqref>
+          <xm:sqref>I1:I17 I29:I39 I41:I1048576 I19:I25 I27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d437ab4f-284f-4dce-87a8-883f66c3d40c}">
+          <x14:cfRule type="dataBar" id="{ba32311f-c293-45a0-ab90-991923d7d44e}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5380,10 +5434,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I1:I9 I29:I1048576 I11:I17 I27 I19 I21:I25</xm:sqref>
+          <xm:sqref>I1:I9 I29:I39 I41:I1048576 I11:I17 I27 I21:I25 I19</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7bd851aa-fab6-46d2-9e8f-f30f01213615}">
+          <x14:cfRule type="dataBar" id="{56d90323-347a-4c29-8ad9-80803c2b332e}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5391,10 +5445,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I1:I9 I29:I1048576 I11:I17 I27 I19 I21:I24</xm:sqref>
+          <xm:sqref>I1:I9 I29:I39 I41:I1048576 I11:I17 I27 I21:I24 I19</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8b33c886-3e56-416e-aac3-18e5b9e69aab}">
+          <x14:cfRule type="dataBar" id="{78e0a573-3615-47e7-9886-e8fb7ea90448}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5402,10 +5456,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I1:I17 I29:I1048576 I21:I25 I19 I27</xm:sqref>
+          <xm:sqref>I1:I17 I29:I39 I41:I1048576 I19 I21:I25 I27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a37213c5-d8c2-4d8a-b9b3-8854c5fda7e3}">
+          <x14:cfRule type="dataBar" id="{52e2b908-04b9-452d-be88-73c6181bddbb}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5413,10 +5467,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I2 I53:I1048576 I32</xm:sqref>
+          <xm:sqref>I2 I54:I1048576 I32</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5350f9cd-155e-472b-b411-a99f85295a24}">
+          <x14:cfRule type="dataBar" id="{d39af3c7-3fcf-48d3-bcb8-514f85206965}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5424,10 +5478,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I2:I4 I29:I39 I6:I7 I41:I1048576 I9 I11:I17 I21:I24 I19 I27</xm:sqref>
+          <xm:sqref>I2:I4 I29:I39 I6:I7 I42:I1048576 I11:I17 I21:I24 I27 I19 I9</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8341e6f2-1230-4f64-84bf-d7d05e301a02}">
+          <x14:cfRule type="dataBar" id="{ce3da0d1-7d02-41b1-bdf0-f79a2bab99f3}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5435,10 +5489,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I2:I4 I29:I39 I41:I1048576 I11:I16 I9 I6:I7 I21:I24 I27 I19</xm:sqref>
+          <xm:sqref>I2:I4 I29:I39 I42:I1048576 I6:I7 I21:I24 I19 I27 I11:I16 I9</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{16165f7b-7c0f-49c9-a2bf-e789513a0274}">
+          <x14:cfRule type="dataBar" id="{3c5da360-cb42-4ee1-9004-9fc9ef0109e2}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5446,10 +5500,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I12:I14 I3:I4 I33:I35 I44:I49 I6:I7 I51:I52 I9 I38:I39 I41:I42 I30 I21:I24 I19 I27</xm:sqref>
+          <xm:sqref>I3:I39 I41:I53</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1930dc6f-ae55-44b4-bc75-eacc4e163e32}">
+          <x14:cfRule type="dataBar" id="{8c7a61aa-2fd6-4ed0-86e4-d93205ed0969}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5457,10 +5511,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I33:I35 I3:I4 I44:I49 I51:I52 I6:I7 I12:I14 I9 I41:I42 I38:I39 I19 I21:I24 I30</xm:sqref>
+          <xm:sqref>I12:I14 I3:I4 I33:I35 I27 I6:I7 I19 I9 I38:I39 I21:I24 I30 I45:I50 I42:I43 I52:I53</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3a06ec88-65f8-458a-a2ae-d66c87115e22}">
+          <x14:cfRule type="dataBar" id="{11cd33f6-fffc-4851-9dcb-540df78c69ae}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5468,10 +5522,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I16 I3:I4 I33:I35 I41:I42 I6:I7 I12:I14 I9 I44:I49 I51:I52 I38:I39 I30 I27 I21:I24 I19</xm:sqref>
+          <xm:sqref>I33:I35 I3:I4 I30 I21:I24 I6:I7 I12:I14 I9 I19 I38:I39 I45:I50 I42:I43 I52:I53</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{612fc072-dda3-4faa-8079-9b7afcbb38a0}">
+          <x14:cfRule type="dataBar" id="{3b7df007-1318-46f6-b584-4fa2b37a3df5}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5479,10 +5533,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I11:I14 I3:I4 I33:I36 I38:I39 I6:I7 I41:I42 I9 I16 I44:I52 I19 I27 I21:I24 I30:I31</xm:sqref>
+          <xm:sqref>I16 I3:I4 I33:I35 I19 I6:I7 I12:I14 I9 I21:I24 I27 I38:I39 I30 I42:I43 I52:I53 I45:I50</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2af321a6-43d8-439d-bf9e-502a21c6653b}">
+          <x14:cfRule type="dataBar" id="{bcf3a045-e169-4344-8a46-bbea048fcff5}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5490,10 +5544,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I38:I39 I3:I4 I44:I49 I51:I52 I6:I7 I16 I9 I11:I14 I33:I35 I41:I42 I21:I24 I27 I30:I31 I19</xm:sqref>
+          <xm:sqref>I11:I14 I3:I4 I33:I36 I38:I39 I6:I7 I30:I31 I9 I16 I21:I24 I19 I27 I42:I43 I45:I53</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1e9ad7a3-a880-46af-b64c-6384d0bb9a85}">
+          <x14:cfRule type="dataBar" id="{85996752-cc3d-4c7a-91ec-59a2a0082fe4}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5501,10 +5555,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I41:I52 I33:I39 I3:I4 I9 I11:I16 I6:I7 I19 I27 I29:I31 I21:I24</xm:sqref>
+          <xm:sqref>I38:I39 I3:I4 I19 I30:I31 I6:I7 I16 I9 I11:I14 I33:I35 I27 I21:I24 I45:I50 I42:I43 I52:I53</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1ede0976-3f5d-4548-a608-b5da5ee0adb8}">
+          <x14:cfRule type="dataBar" id="{8f03883d-6bc2-4348-a39d-6e9be7965527}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5512,10 +5566,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I11:I16 I3:I4 I33:I39 I41:I52 I6:I7 I9 I19 I21:I24 I27 I30:I31</xm:sqref>
+          <xm:sqref>I21:I24 I33:I39 I3:I4 I9 I11:I16 I6:I7 I19 I27 I29:I31 I42:I53</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e4db04cc-6be5-4ecd-b3e9-b1e5cf7d1031}">
+          <x14:cfRule type="dataBar" id="{840df7f5-c2a1-4cee-b2c8-314e2d820a35}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5523,10 +5577,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I11:I17 I41:I52 I3:I4 I33:I39 I9 I6:I7 I19 I21:I24 I27 I29:I31</xm:sqref>
+          <xm:sqref>I11:I16 I3:I4 I33:I39 I30:I31 I6:I7 I9 I19 I21:I24 I27 I42:I53</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6c63add2-3203-45b5-89a2-4a12d8afc0b1}">
+          <x14:cfRule type="dataBar" id="{835c0286-e79b-4e31-a6e5-89b49d1d58b5}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5534,10 +5588,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I11:I17 I33:I52 I9 I3:I7 I27 I29:I31 I21:I24 I19</xm:sqref>
+          <xm:sqref>I11:I17 I29:I31 I3:I4 I33:I39 I9 I6:I7 I19 I21:I24 I27 I42:I53</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{300abaa2-c1d9-48b9-ae8e-05015977ad1a}">
+          <x14:cfRule type="dataBar" id="{ae9fac30-fc82-47f3-9a5c-a3185969e7d9}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5545,10 +5599,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I41:I52 I33:I39 I9 I3:I7 I11:I17 I19 I29:I31 I21:I24 I27</xm:sqref>
+          <xm:sqref>I11:I17 I33:I39 I19 I9 I3:I7 I27 I29:I31 I21:I24 I41:I53</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ee1fe562-cfba-4b9c-8a63-a97f8821f0c2}">
+          <x14:cfRule type="dataBar" id="{9b00a8aa-386e-4c4e-b561-2763c24c7b76}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5556,7 +5610,18 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I33:I52 I3:I17 I19:I25 I29:I31 I27</xm:sqref>
+          <xm:sqref>I27 I33:I39 I9 I3:I7 I11:I17 I19 I29:I31 I21:I24 I42:I53</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{09ae2eac-49db-43b7-a6d9-14db4c2446d5}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>I33:I39 I27 I3:I17 I19:I25 I29:I31 I41:I53</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>

--- a/CrCraft收支与赞助鸣谢单.xlsx
+++ b/CrCraft收支与赞助鸣谢单.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="84">
   <si>
     <t>服务器收入与支出</t>
   </si>
@@ -149,7 +149,7 @@
     <t>luolizuiniubi</t>
   </si>
   <si>
-    <t>↑35</t>
+    <t>↑36</t>
   </si>
   <si>
     <t>匿名玩家</t>
@@ -191,9 +191,18 @@
     <t>樱花映射VIP</t>
   </si>
   <si>
+    <t>AhLangGe</t>
+  </si>
+  <si>
+    <t>↑27</t>
+  </si>
+  <si>
     <t>wybhh51811</t>
   </si>
   <si>
+    <t>↓2</t>
+  </si>
+  <si>
     <t>red_chipi</t>
   </si>
   <si>
@@ -206,12 +215,12 @@
     <t>XL12</t>
   </si>
   <si>
+    <t>hanfengzunzhe</t>
+  </si>
+  <si>
     <t>Xiaoyingawa</t>
   </si>
   <si>
-    <t>hanfengzunzhe</t>
-  </si>
-  <si>
     <t>Onion520</t>
   </si>
   <si>
@@ -227,19 +236,19 @@
     <t>Mo_Xuan_Yu</t>
   </si>
   <si>
+    <t>主板、CPU、电源、机械硬盘</t>
+  </si>
+  <si>
     <t>Damon</t>
   </si>
   <si>
     <t>↑13</t>
   </si>
   <si>
-    <t>主板、CPU、电源、机械硬盘</t>
-  </si>
-  <si>
     <t>xiaomin</t>
   </si>
   <si>
-    <t>↓2</t>
+    <t>↓3</t>
   </si>
   <si>
     <t>A1TanJZ</t>
@@ -251,10 +260,10 @@
     <t>QSWY_MC</t>
   </si>
   <si>
+    <t>遗物</t>
+  </si>
+  <si>
     <t>CHYunyou</t>
-  </si>
-  <si>
-    <t>遗物</t>
   </si>
   <si>
     <t>映射VIP</t>
@@ -1116,7 +1125,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1204,15 +1213,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="31" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="31" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="31" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1234,17 +1243,23 @@
     <xf numFmtId="31" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="31" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="31" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="31" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="2" borderId="7" xfId="22" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="31" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -1582,7 +1597,7 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:K167"/>
+  <dimension ref="A1:K168"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="15.625" customWidth="1"/>
@@ -2355,17 +2370,17 @@
       <c r="G27">
         <v>25</v>
       </c>
-      <c r="H27" s="10" t="s">
+      <c r="H27" s="24" t="s">
         <v>54</v>
       </c>
       <c r="I27" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J27" s="3">
-        <v>45860</v>
+        <v>46306</v>
       </c>
       <c r="K27" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -2387,16 +2402,16 @@
         <v>26</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I28" s="2">
         <v>8</v>
       </c>
       <c r="J28" s="3">
-        <v>46205</v>
+        <v>45860</v>
       </c>
       <c r="K28" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -2418,16 +2433,16 @@
         <v>27</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I29" s="2">
-        <v>7.33</v>
+        <v>8</v>
       </c>
       <c r="J29" s="3">
-        <v>45907</v>
+        <v>46205</v>
       </c>
       <c r="K29" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -2449,17 +2464,16 @@
         <v>28</v>
       </c>
       <c r="H30" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="I30" s="2">
+        <v>7.33</v>
+      </c>
+      <c r="J30" s="3">
+        <v>45907</v>
+      </c>
+      <c r="K30" t="s">
         <v>57</v>
-      </c>
-      <c r="I30" s="16">
-        <f>SUM(C82,C84,C94)</f>
-        <v>6.98</v>
-      </c>
-      <c r="J30" s="3">
-        <v>45861</v>
-      </c>
-      <c r="K30" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -2481,16 +2495,17 @@
         <v>29</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="I31" s="2">
-        <v>6</v>
+        <v>60</v>
+      </c>
+      <c r="I31" s="16">
+        <f>SUM(C82,C84,C94)</f>
+        <v>6.98</v>
       </c>
       <c r="J31" s="3">
-        <v>45868</v>
+        <v>45861</v>
       </c>
       <c r="K31" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -2514,16 +2529,16 @@
         <v>30</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="I32" s="2">
-        <v>5.04</v>
+        <v>6</v>
       </c>
       <c r="J32" s="3">
-        <v>46160</v>
+        <v>45868</v>
       </c>
       <c r="K32" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -2531,7 +2546,7 @@
         <v>45387</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C33" s="13">
         <v>1.38</v>
@@ -2545,16 +2560,16 @@
         <v>31</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="I33" s="16">
-        <v>5.02</v>
+        <v>63</v>
+      </c>
+      <c r="I33" s="2">
+        <v>5.04</v>
       </c>
       <c r="J33" s="3">
-        <v>44787</v>
+        <v>46160</v>
       </c>
       <c r="K33" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -2578,16 +2593,16 @@
         <v>32</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="I34" s="16">
-        <v>5</v>
+        <v>5.02</v>
       </c>
       <c r="J34" s="3">
-        <v>45634</v>
+        <v>44787</v>
       </c>
       <c r="K34" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -2595,7 +2610,7 @@
         <v>45396</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C35" s="13">
         <v>0.8</v>
@@ -2609,16 +2624,16 @@
         <v>33</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I35" s="16">
-        <v>4.15</v>
+        <v>5</v>
       </c>
       <c r="J35" s="3">
-        <v>45707</v>
+        <v>45634</v>
       </c>
       <c r="K35" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -2640,16 +2655,16 @@
         <v>34</v>
       </c>
       <c r="H36" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="I36" s="2">
-        <v>4</v>
+        <v>65</v>
+      </c>
+      <c r="I36" s="16">
+        <v>4.15</v>
       </c>
       <c r="J36" s="3">
-        <v>45885</v>
+        <v>45707</v>
       </c>
       <c r="K36" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -2672,18 +2687,17 @@
       <c r="G37">
         <v>35</v>
       </c>
-      <c r="H37" s="1" t="s">
-        <v>64</v>
+      <c r="H37" s="10" t="s">
+        <v>66</v>
       </c>
       <c r="I37" s="2">
-        <f>SUM(C100,C108)</f>
         <v>4</v>
       </c>
       <c r="J37" s="3">
-        <v>45934</v>
+        <v>45885</v>
       </c>
       <c r="K37" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -2704,17 +2718,18 @@
       <c r="G38" s="15">
         <v>36</v>
       </c>
-      <c r="H38" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="I38" s="16">
-        <v>3</v>
-      </c>
-      <c r="J38" s="3" t="s">
-        <v>11</v>
+      <c r="H38" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="I38" s="2">
+        <f>SUM(C100,C108)</f>
+        <v>4</v>
+      </c>
+      <c r="J38" s="3">
+        <v>45934</v>
       </c>
       <c r="K38" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -2736,16 +2751,16 @@
         <v>37</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>65</v>
+        <v>18</v>
       </c>
       <c r="I39" s="16">
         <v>3</v>
       </c>
-      <c r="J39" s="3">
-        <v>45500</v>
+      <c r="J39" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="K39" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -2768,17 +2783,17 @@
       <c r="G40" s="15">
         <v>38</v>
       </c>
-      <c r="H40" s="24" t="s">
-        <v>66</v>
-      </c>
-      <c r="I40" s="2">
-        <v>2.741</v>
+      <c r="H40" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="I40" s="16">
+        <v>3</v>
       </c>
       <c r="J40" s="3">
-        <v>46305</v>
+        <v>45500</v>
       </c>
       <c r="K40" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -2795,22 +2810,22 @@
         <v>-1999.72</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G41">
         <v>39</v>
       </c>
-      <c r="H41" s="10" t="s">
-        <v>69</v>
+      <c r="H41" s="1" t="s">
+        <v>70</v>
       </c>
       <c r="I41" s="2">
-        <v>2.5</v>
+        <v>2.741</v>
       </c>
       <c r="J41" s="3">
-        <v>45976</v>
+        <v>46305</v>
       </c>
       <c r="K41" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -2834,17 +2849,16 @@
         <v>40</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="I42" s="16">
-        <f>SUM(C35,C33:C33)</f>
-        <v>2.18</v>
+        <v>72</v>
+      </c>
+      <c r="I42" s="2">
+        <v>2.5</v>
       </c>
       <c r="J42" s="3">
-        <v>45396</v>
+        <v>45976</v>
       </c>
       <c r="K42" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -2861,16 +2875,17 @@
         <v>41</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>16</v>
+        <v>62</v>
       </c>
       <c r="I43" s="16">
-        <v>2</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>11</v>
+        <f>SUM(C35,C33:C33)</f>
+        <v>2.18</v>
+      </c>
+      <c r="J43" s="3">
+        <v>45396</v>
       </c>
       <c r="K43" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="44" spans="1:11">
@@ -2891,17 +2906,17 @@
       <c r="G44">
         <v>42</v>
       </c>
-      <c r="H44" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="I44" s="2">
+      <c r="H44" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="I44" s="16">
         <v>2</v>
       </c>
-      <c r="J44" s="3">
-        <v>45907</v>
+      <c r="J44" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="K44" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -2922,43 +2937,43 @@
       <c r="G45">
         <v>43</v>
       </c>
-      <c r="H45" s="29" t="s">
-        <v>41</v>
-      </c>
-      <c r="I45" s="16">
-        <v>1.32</v>
+      <c r="H45" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="I45" s="2">
+        <v>2</v>
       </c>
       <c r="J45" s="3">
-        <v>44958</v>
+        <v>45907</v>
       </c>
       <c r="K45" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="46" spans="1:11">
-      <c r="A46" s="30"/>
+      <c r="A46" s="29"/>
       <c r="B46" s="26" t="s">
         <v>32</v>
       </c>
       <c r="C46" s="27">
         <v>3</v>
       </c>
-      <c r="D46" s="31"/>
+      <c r="D46" s="30"/>
       <c r="E46" s="28"/>
       <c r="G46">
         <v>44</v>
       </c>
-      <c r="H46" s="10" t="s">
-        <v>20</v>
+      <c r="H46" s="31" t="s">
+        <v>41</v>
       </c>
       <c r="I46" s="16">
-        <v>1.28</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>11</v>
+        <v>1.32</v>
+      </c>
+      <c r="J46" s="3">
+        <v>44958</v>
       </c>
       <c r="K46" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="47" spans="1:11">
@@ -2980,16 +2995,16 @@
         <v>45</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="I47" s="16">
-        <v>1.01</v>
-      </c>
-      <c r="J47" s="3">
-        <v>45141</v>
+        <v>1.28</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="K47" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -2997,7 +3012,7 @@
         <v>45500</v>
       </c>
       <c r="B48" s="26" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C48" s="27">
         <v>3</v>
@@ -3011,16 +3026,16 @@
         <v>46</v>
       </c>
       <c r="H48" s="10" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="I48" s="16">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="J48" s="3">
-        <v>45794</v>
+        <v>45141</v>
       </c>
       <c r="K48" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="49" spans="1:11">
@@ -3031,7 +3046,7 @@
       <c r="C49" s="27">
         <v>5</v>
       </c>
-      <c r="D49" s="31"/>
+      <c r="D49" s="30"/>
       <c r="E49" s="28" t="s">
         <v>33</v>
       </c>
@@ -3039,16 +3054,16 @@
         <v>47</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="I49" s="16">
-        <v>0.55</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>11</v>
+        <v>1</v>
+      </c>
+      <c r="J49" s="3">
+        <v>45794</v>
       </c>
       <c r="K49" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -3072,16 +3087,16 @@
         <v>48</v>
       </c>
       <c r="H50" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I50" s="16">
+        <v>0.55</v>
+      </c>
+      <c r="J50" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K50" t="s">
         <v>73</v>
-      </c>
-      <c r="I50" s="16">
-        <v>0.5</v>
-      </c>
-      <c r="J50" s="3">
-        <v>45697</v>
-      </c>
-      <c r="K50" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -3105,16 +3120,16 @@
         <v>49</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="I51" s="2">
+        <v>76</v>
+      </c>
+      <c r="I51" s="16">
         <v>0.5</v>
       </c>
       <c r="J51" s="3">
-        <v>45885</v>
+        <v>45697</v>
       </c>
       <c r="K51" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -3125,24 +3140,24 @@
       <c r="C52" s="27">
         <v>86</v>
       </c>
-      <c r="D52" s="31"/>
+      <c r="D52" s="30"/>
       <c r="E52" s="28" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G52">
         <v>50</v>
       </c>
       <c r="H52" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="I52" s="16">
-        <v>0.11</v>
+        <v>78</v>
+      </c>
+      <c r="I52" s="2">
+        <v>0.5</v>
       </c>
       <c r="J52" s="3">
-        <v>45140</v>
+        <v>45885</v>
       </c>
       <c r="K52" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -3166,16 +3181,16 @@
         <v>51</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="I53" s="16">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="J53" s="3">
-        <v>44213</v>
+        <v>45140</v>
       </c>
       <c r="K53" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -3186,8 +3201,23 @@
       <c r="C54" s="27">
         <v>10</v>
       </c>
-      <c r="D54" s="31"/>
+      <c r="D54" s="30"/>
       <c r="E54" s="28"/>
+      <c r="G54">
+        <v>52</v>
+      </c>
+      <c r="H54" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="I54" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="J54" s="3">
+        <v>44213</v>
+      </c>
+      <c r="K54" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="55" spans="1:11">
       <c r="A55" s="25">
@@ -3202,7 +3232,7 @@
         <v>-1737.27</v>
       </c>
       <c r="E55" s="28" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="56" spans="1:11">
@@ -3213,7 +3243,7 @@
       <c r="C56" s="27">
         <v>10</v>
       </c>
-      <c r="D56" s="31"/>
+      <c r="D56" s="30"/>
       <c r="E56" s="28"/>
     </row>
     <row r="57" spans="1:11">
@@ -3286,14 +3316,14 @@
       </c>
     </row>
     <row r="61" spans="1:11">
-      <c r="A61" s="30"/>
+      <c r="A61" s="29"/>
       <c r="B61" s="34" t="s">
         <v>19</v>
       </c>
       <c r="C61" s="27">
         <v>20</v>
       </c>
-      <c r="D61" s="31"/>
+      <c r="D61" s="30"/>
       <c r="E61" s="28"/>
     </row>
     <row r="62" spans="1:11">
@@ -3352,7 +3382,7 @@
       <c r="C65" s="27">
         <v>20</v>
       </c>
-      <c r="D65" s="31"/>
+      <c r="D65" s="30"/>
       <c r="E65" s="28"/>
     </row>
     <row r="66" spans="1:5">
@@ -3404,7 +3434,7 @@
         <v>-1389.27</v>
       </c>
       <c r="E68" s="28" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -3482,7 +3512,7 @@
         <v>45634</v>
       </c>
       <c r="B73" s="34" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C73" s="27">
         <v>5</v>
@@ -3503,7 +3533,7 @@
       <c r="C74" s="27">
         <v>10</v>
       </c>
-      <c r="D74" s="31"/>
+      <c r="D74" s="30"/>
       <c r="E74" s="28"/>
     </row>
     <row r="75" spans="1:5">
@@ -3561,7 +3591,7 @@
         <v>45697</v>
       </c>
       <c r="B78" s="34" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C78" s="27">
         <v>0.5</v>
@@ -3577,7 +3607,7 @@
         <v>45707</v>
       </c>
       <c r="B79" s="34" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C79" s="27">
         <v>4.15</v>
@@ -3593,7 +3623,7 @@
         <v>45794</v>
       </c>
       <c r="B80" s="34" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C80" s="27">
         <v>1</v>
@@ -3625,7 +3655,7 @@
         <v>45844</v>
       </c>
       <c r="B82" s="34" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C82" s="27">
         <v>2.48</v>
@@ -3641,7 +3671,7 @@
         <v>45860</v>
       </c>
       <c r="B83" s="34" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C83" s="27">
         <v>8</v>
@@ -3657,7 +3687,7 @@
         <v>45861</v>
       </c>
       <c r="B84" s="34" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C84" s="27">
         <v>0.5</v>
@@ -3705,7 +3735,7 @@
         <v>45868</v>
       </c>
       <c r="B87" s="34" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C87" s="27">
         <v>6</v>
@@ -3789,7 +3819,7 @@
         <v>45885</v>
       </c>
       <c r="B92" s="34" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C92" s="27">
         <v>0.5</v>
@@ -3803,23 +3833,23 @@
     <row r="93" spans="1:5">
       <c r="A93" s="17"/>
       <c r="B93" s="34" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C93" s="27">
         <v>6</v>
       </c>
-      <c r="D93" s="31"/>
+      <c r="D93" s="30"/>
       <c r="E93" s="35"/>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="17"/>
       <c r="B94" s="34" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C94" s="27">
         <v>4</v>
       </c>
-      <c r="D94" s="31"/>
+      <c r="D94" s="30"/>
       <c r="E94" s="35"/>
     </row>
     <row r="95" spans="1:5">
@@ -3861,7 +3891,7 @@
         <v>45905</v>
       </c>
       <c r="B97" s="34" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C97" s="27">
         <v>7.33</v>
@@ -3896,18 +3926,18 @@
       <c r="C99" s="27">
         <v>2</v>
       </c>
-      <c r="D99" s="31"/>
+      <c r="D99" s="30"/>
       <c r="E99" s="35"/>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="32"/>
       <c r="B100" s="34" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C100" s="27">
         <v>2</v>
       </c>
-      <c r="D100" s="31"/>
+      <c r="D100" s="30"/>
       <c r="E100" s="35"/>
     </row>
     <row r="101" spans="1:5">
@@ -3918,18 +3948,18 @@
       <c r="C101" s="27">
         <v>2</v>
       </c>
-      <c r="D101" s="31"/>
+      <c r="D101" s="30"/>
       <c r="E101" s="35"/>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="32"/>
       <c r="B102" s="34" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C102" s="27">
         <v>2</v>
       </c>
-      <c r="D102" s="31"/>
+      <c r="D102" s="30"/>
       <c r="E102" s="35"/>
     </row>
     <row r="103" spans="1:5">
@@ -3945,7 +3975,7 @@
         <v>-1298.13</v>
       </c>
       <c r="E103" s="35" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -4017,7 +4047,7 @@
     <row r="108" spans="1:5">
       <c r="A108" s="32"/>
       <c r="B108" s="34" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C108" s="27">
         <v>2</v>
@@ -4127,7 +4157,7 @@
         <v>45976</v>
       </c>
       <c r="B115" s="34" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C115" s="27">
         <v>2.5</v>
@@ -4533,7 +4563,7 @@
         <v>-3151.15</v>
       </c>
       <c r="E140" s="35" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="141" spans="1:5">
@@ -4669,7 +4699,7 @@
         <v>46160</v>
       </c>
       <c r="B149" s="34" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C149" s="27">
         <v>5.04</v>
@@ -4803,7 +4833,7 @@
         <v>46205</v>
       </c>
       <c r="B157" s="34" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C157" s="27">
         <v>8</v>
@@ -4895,7 +4925,7 @@
       <c r="E162" s="35"/>
     </row>
     <row r="163" spans="1:5">
-      <c r="A163" s="25">
+      <c r="A163" s="38">
         <v>46305</v>
       </c>
       <c r="B163" s="34" t="s">
@@ -4911,49 +4941,61 @@
       <c r="E163" s="35"/>
     </row>
     <row r="164" spans="1:5">
-      <c r="A164" s="38">
-        <v>46305</v>
-      </c>
-      <c r="B164" s="39" t="s">
-        <v>66</v>
-      </c>
-      <c r="C164" s="40">
+      <c r="A164" s="39"/>
+      <c r="B164" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="C164" s="27">
         <v>2.74</v>
       </c>
       <c r="D164" s="21">
         <f>SUM(C3:C164)</f>
         <v>-2457.33</v>
       </c>
-      <c r="E164" s="41"/>
+      <c r="E164" s="35"/>
     </row>
     <row r="165" spans="1:5">
-      <c r="A165" s="38"/>
-      <c r="B165" s="39"/>
-      <c r="C165" s="40"/>
-      <c r="D165" s="42"/>
-      <c r="E165" s="41"/>
+      <c r="A165" s="39"/>
+      <c r="B165" s="34" t="s">
+        <v>54</v>
+      </c>
+      <c r="C165" s="27">
+        <v>10</v>
+      </c>
+      <c r="D165" s="21">
+        <f>SUM(C3:C165)</f>
+        <v>-2447.33</v>
+      </c>
+      <c r="E165" s="35"/>
     </row>
     <row r="166" spans="1:5">
-      <c r="A166" s="43"/>
-      <c r="B166" s="44"/>
-      <c r="C166" s="45"/>
-      <c r="D166" s="45"/>
-      <c r="E166" s="46"/>
+      <c r="A166" s="40"/>
+      <c r="B166" s="41"/>
+      <c r="C166" s="42"/>
+      <c r="D166" s="43"/>
+      <c r="E166" s="44"/>
     </row>
     <row r="167" spans="1:5">
-      <c r="A167" s="47" t="s">
-        <v>80</v>
-      </c>
-      <c r="B167" s="47"/>
+      <c r="A167" s="45"/>
+      <c r="B167" s="46"/>
       <c r="C167" s="47"/>
       <c r="D167" s="47"/>
-      <c r="E167" s="47"/>
+      <c r="E167" s="48"/>
+    </row>
+    <row r="168" spans="1:5">
+      <c r="A168" s="49" t="s">
+        <v>83</v>
+      </c>
+      <c r="B168" s="49"/>
+      <c r="C168" s="49"/>
+      <c r="D168" s="49"/>
+      <c r="E168" s="49"/>
     </row>
   </sheetData>
-  <mergeCells count="42">
+  <mergeCells count="43">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="G1:K1"/>
-    <mergeCell ref="A167:E167"/>
+    <mergeCell ref="A168:E168"/>
     <mergeCell ref="A3:A7"/>
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="A23:A24"/>
@@ -4978,6 +5020,7 @@
     <mergeCell ref="A145:A146"/>
     <mergeCell ref="A153:A154"/>
     <mergeCell ref="A157:A159"/>
+    <mergeCell ref="A163:A165"/>
     <mergeCell ref="D3:D7"/>
     <mergeCell ref="D18:D19"/>
     <mergeCell ref="D23:D24"/>
@@ -4995,7 +5038,7 @@
     <mergeCell ref="D98:D102"/>
   </mergeCells>
   <conditionalFormatting sqref="I26">
-    <cfRule type="dataBar" priority="20">
+    <cfRule type="dataBar" priority="21">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -5003,13 +5046,27 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fe93615c-9386-4e68-a3d8-dcd399127919}</x14:id>
+          <x14:id>{daf3b84c-7971-45d3-910d-4abd77f6c13b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D1:D18 D20:D23 D25:D26 D28:D42 D44:D45 D47:D48 D50:D51 D53 D55 D57:D60 D62:D64 D66:D73 D75:D92 D95:D98 D103:D166 D168:D1048576">
-    <cfRule type="colorScale" priority="82">
+  <conditionalFormatting sqref="I$1:I$1048576">
+    <cfRule type="dataBar" priority="1">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{964efb26-34c7-43c0-9616-0cb0a86ecb44}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D1:D18 D20:D23 D25:D26 D28:D42 D44:D45 D47:D48 D50:D51 D53 D55 D57:D60 D62:D64 D66:D73 D75:D92 D95:D98 D103:D167 D169:D1048576">
+    <cfRule type="colorScale" priority="83">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5021,7 +5078,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G1 G2:I2">
-    <cfRule type="dataBar" priority="93">
+    <cfRule type="dataBar" priority="94">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -5029,26 +5086,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6e1f2766-40dd-4fd6-ae6e-bc7674e878db}</x14:id>
+          <x14:id>{9025380e-b8c2-49f8-a21c-3e743cc95b32}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I17 I19:I39 I41:I1048576">
-    <cfRule type="dataBar" priority="2">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8cec9d82-964e-46ef-9772-89fbb2530727}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I17 I29:I39 I41:I1048576 I19:I27">
+  <conditionalFormatting sqref="I1:I17 I19:I26 I42:I1048576 I28:I40">
     <cfRule type="dataBar" priority="3">
       <dataBar>
         <cfvo type="min"/>
@@ -5057,13 +5100,13 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0f6a72ee-a057-428c-8ed3-9638476122dd}</x14:id>
+          <x14:id>{10de938c-8233-4d7c-96e6-bc0c91a6d123}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I17 I29:I39 I41:I1048576 I19:I25 I27">
-    <cfRule type="dataBar" priority="21">
+  <conditionalFormatting sqref="I1:I17 I19:I26 I42:I1048576 I28 I30:I40">
+    <cfRule type="dataBar" priority="4">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -5071,12 +5114,54 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6eab6aa1-105e-4d74-8ae0-c75db30c2d26}</x14:id>
+          <x14:id>{1b06e32f-e60b-4204-9f5c-a98063618033}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I9 I29:I39 I41:I1048576 I11:I17 I27 I21:I25 I19">
+  <conditionalFormatting sqref="I1:I17 I19:I25 I42:I1048576 I30:I40 I28">
+    <cfRule type="dataBar" priority="22">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{2ff10b1e-3672-4e95-ad46-0dc91fa08703}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I1:I9 I21:I25 I42:I1048576 I19 I11:I17 I28 I30:I40">
+    <cfRule type="dataBar" priority="25">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{e19930b4-8329-405b-90a6-ab502815cbc9}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I1:I9 I21:I24 I42:I1048576 I19 I11:I17 I28 I30:I40">
+    <cfRule type="dataBar" priority="26">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{45ae7e1c-763c-46ff-a2ee-69e1ad8f11ff}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I1:I17 I19 I42:I1048576 I21:I25 I28 I30:I40">
     <cfRule type="dataBar" priority="24">
       <dataBar>
         <cfvo type="min"/>
@@ -5085,13 +5170,13 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ba32311f-c293-45a0-ab90-991923d7d44e}</x14:id>
+          <x14:id>{87982b8a-67e0-4d3e-8484-167f6b5a7892}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I9 I29:I39 I41:I1048576 I11:I17 I27 I21:I24 I19">
-    <cfRule type="dataBar" priority="25">
+  <conditionalFormatting sqref="I2 I55:I1048576 I33">
+    <cfRule type="dataBar" priority="52">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -5099,13 +5184,13 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{56d90323-347a-4c29-8ad9-80803c2b332e}</x14:id>
+          <x14:id>{ffc17467-5da3-433c-8ac5-69faa3276a81}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I17 I29:I39 I41:I1048576 I19 I21:I25 I27">
-    <cfRule type="dataBar" priority="23">
+  <conditionalFormatting sqref="I2:I4 I11:I17 I6:I7 I43:I1048576 I19 I21:I24 I9 I28 I30:I40">
+    <cfRule type="dataBar" priority="29">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -5113,13 +5198,13 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{78e0a573-3615-47e7-9886-e8fb7ea90448}</x14:id>
+          <x14:id>{8230e915-ebf3-4217-855c-30a9aa15f80e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2 I54:I1048576 I32">
-    <cfRule type="dataBar" priority="51">
+  <conditionalFormatting sqref="I2:I4 I21:I24 I43:I1048576 I6:I7 I19 I9 I11:I16 I28 I30:I40">
+    <cfRule type="dataBar" priority="33">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -5127,41 +5212,13 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{52e2b908-04b9-452d-be88-73c6181bddbb}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I4 I29:I39 I6:I7 I42:I1048576 I11:I17 I21:I24 I27 I19 I9">
-    <cfRule type="dataBar" priority="28">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d39af3c7-3fcf-48d3-bcb8-514f85206965}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I4 I29:I39 I42:I1048576 I6:I7 I21:I24 I19 I27 I11:I16 I9">
-    <cfRule type="dataBar" priority="32">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ce3da0d1-7d02-41b1-bdf0-f79a2bab99f3}</x14:id>
+          <x14:id>{ae04e9da-8447-47fd-ac44-324123086088}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D3 D10:D18 D20:D23 D25:D26 D28:D33">
-    <cfRule type="colorScale" priority="105">
+    <cfRule type="colorScale" priority="106">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5171,7 +5228,7 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="117">
+    <cfRule type="colorScale" priority="118">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -5181,7 +5238,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D3:D18 D20:D23 D25:D26 D28:D34">
-    <cfRule type="colorScale" priority="83">
+    <cfRule type="colorScale" priority="84">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5192,8 +5249,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I39 I41:I53">
-    <cfRule type="dataBar" priority="1">
+  <conditionalFormatting sqref="I3:I26 I42:I54 I28:I40">
+    <cfRule type="dataBar" priority="2">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -5201,26 +5258,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3c5da360-cb42-4ee1-9004-9fc9ef0109e2}</x14:id>
+          <x14:id>{8a7eaec4-194d-415b-8731-814c9b2e8188}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I12:I14 I3:I4 I33:I35 I27 I6:I7 I19 I9 I38:I39 I21:I24 I30 I45:I50 I42:I43 I52:I53">
-    <cfRule type="dataBar" priority="38">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8c7a61aa-2fd6-4ed0-86e4-d93205ed0969}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I33:I35 I3:I4 I30 I21:I24 I6:I7 I12:I14 I9 I19 I38:I39 I45:I50 I42:I43 I52:I53">
+  <conditionalFormatting sqref="I12:I14 I3:I4 I21:I24 I9 I6:I7 I19 I53:I54 I31 I39:I40 I28 I34:I36 I43:I44 I46:I51">
     <cfRule type="dataBar" priority="39">
       <dataBar>
         <cfvo type="min"/>
@@ -5229,12 +5272,54 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{11cd33f6-fffc-4851-9dcb-540df78c69ae}</x14:id>
+          <x14:id>{3b0afb5e-93c1-4dd7-8c58-58f23e63f6ed}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I16 I3:I4 I33:I35 I19 I6:I7 I12:I14 I9 I21:I24 I27 I38:I39 I30 I42:I43 I52:I53 I45:I50">
+  <conditionalFormatting sqref="I19 I3:I4 I9 I21:I24 I6:I7 I12:I14 I53:I54 I39:I40 I31 I34:I36 I46:I51 I43:I44">
+    <cfRule type="dataBar" priority="40">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{a44628d5-73ef-40e6-8b78-140968182f77}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I16 I3:I4 I21:I24 I19 I6:I7 I12:I14 I9 I46:I51 I31 I39:I40 I28 I34:I36 I43:I44 I53:I54">
+    <cfRule type="dataBar" priority="37">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{5a58545d-be4e-44cf-b89e-e93d9a23cfed}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I11:I14 I3:I4 I19 I21:I24 I6:I7 I16 I9 I46:I54 I31:I32 I39:I40 I34:I37 I43:I44 I28">
+    <cfRule type="dataBar" priority="35">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{14eef661-d018-4326-8dee-a084a02b7240}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I21:I24 I3:I4 I19 I11:I14 I6:I7 I16 I9 I53:I54 I28 I34:I36 I31:I32 I39:I40 I43:I44 I46:I51">
     <cfRule type="dataBar" priority="36">
       <dataBar>
         <cfvo type="min"/>
@@ -5243,12 +5328,26 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3b7df007-1318-46f6-b584-4fa2b37a3df5}</x14:id>
+          <x14:id>{591ea288-a3f6-4809-ad3d-c960ce4c677b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I11:I14 I3:I4 I33:I36 I38:I39 I6:I7 I30:I31 I9 I16 I21:I24 I19 I27 I42:I43 I45:I53">
+  <conditionalFormatting sqref="I21:I24 I19 I3:I4 I9 I11:I16 I6:I7 I43:I54 I28 I34:I40 I30:I32">
+    <cfRule type="dataBar" priority="31">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{86bcd8a8-6e6a-4d47-ace4-812c1284383e}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I11:I16 I3:I4 I21:I24 I19 I6:I7 I9 I43:I54 I31:I32 I34:I40 I28">
     <cfRule type="dataBar" priority="34">
       <dataBar>
         <cfvo type="min"/>
@@ -5257,26 +5356,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{bcf3a045-e169-4344-8a46-bbea048fcff5}</x14:id>
+          <x14:id>{11adac6c-2f92-4f6c-82bb-56950e2d556e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I38:I39 I3:I4 I19 I30:I31 I6:I7 I16 I9 I11:I14 I33:I35 I27 I21:I24 I45:I50 I42:I43 I52:I53">
-    <cfRule type="dataBar" priority="35">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{85996752-cc3d-4c7a-91ec-59a2a0082fe4}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I21:I24 I33:I39 I3:I4 I9 I11:I16 I6:I7 I19 I27 I29:I31 I42:I53">
+  <conditionalFormatting sqref="I11:I17 I21:I24 I3:I4 I19 I9 I6:I7 I43:I54 I34:I40 I30:I32 I28">
     <cfRule type="dataBar" priority="30">
       <dataBar>
         <cfvo type="min"/>
@@ -5285,54 +5370,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8f03883d-6bc2-4348-a39d-6e9be7965527}</x14:id>
+          <x14:id>{25db3124-d27e-47b6-a736-15c2e55878a4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I11:I16 I3:I4 I33:I39 I30:I31 I6:I7 I9 I19 I21:I24 I27 I42:I53">
-    <cfRule type="dataBar" priority="33">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{840df7f5-c2a1-4cee-b2c8-314e2d820a35}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I11:I17 I29:I31 I3:I4 I33:I39 I9 I6:I7 I19 I21:I24 I27 I42:I53">
-    <cfRule type="dataBar" priority="29">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{835c0286-e79b-4e31-a6e5-89b49d1d58b5}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I11:I17 I33:I39 I19 I9 I3:I7 I27 I29:I31 I21:I24 I41:I53">
-    <cfRule type="dataBar" priority="26">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ae9fac30-fc82-47f3-9a5c-a3185969e7d9}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I27 I33:I39 I9 I3:I7 I11:I17 I19 I29:I31 I21:I24 I42:I53">
+  <conditionalFormatting sqref="I11:I17 I21:I24 I19 I9 I3:I7 I42:I54 I30:I32 I28 I34:I40">
     <cfRule type="dataBar" priority="27">
       <dataBar>
         <cfvo type="min"/>
@@ -5341,13 +5384,13 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9b00a8aa-386e-4c4e-b561-2763c24c7b76}</x14:id>
+          <x14:id>{e5d398f1-17c9-408d-8122-f7ca0250a9f6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I33:I39 I27 I3:I17 I19:I25 I29:I31 I41:I53">
-    <cfRule type="dataBar" priority="22">
+  <conditionalFormatting sqref="I19 I21:I24 I9 I3:I7 I11:I17 I43:I54 I30:I32 I34:I40 I28">
+    <cfRule type="dataBar" priority="28">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -5355,7 +5398,21 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{09ae2eac-49db-43b7-a6d9-14db4c2446d5}</x14:id>
+          <x14:id>{737fbe19-9679-40e7-86b3-4e00ddbafea9}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I19:I25 I3:I17 I42:I54 I28 I34:I40 I30:I32">
+    <cfRule type="dataBar" priority="23">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{e06a5fd6-2eac-46c7-a8d7-2e3ffe8f038d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5363,13 +5420,13 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="E29 E25:E27 E22:E23 E19:E20 E16:E17 E8:E14 D8:D108 D3 E36:E37 E34 E48:E49 E45 E40:E41" formulaRange="1"/>
+    <ignoredError sqref="E40:E41 E45 E48:E49 E34 E36:E37 D3 D8:D108 E8:E14 E16:E17 E19:E20 E22:E23 E25:E27 E29" formulaRange="1"/>
   </ignoredErrors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{fe93615c-9386-4e68-a3d8-dcd399127919}">
+          <x14:cfRule type="dataBar" id="{daf3b84c-7971-45d3-910d-4abd77f6c13b}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5380,7 +5437,18 @@
           <xm:sqref>I26</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6e1f2766-40dd-4fd6-ae6e-bc7674e878db}">
+          <x14:cfRule type="dataBar" id="{964efb26-34c7-43c0-9616-0cb0a86ecb44}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>I$1:I$1048576</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{9025380e-b8c2-49f8-a21c-3e743cc95b32}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5393,7 +5461,7 @@
           <xm:sqref>G1 G2:I2</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8cec9d82-964e-46ef-9772-89fbb2530727}">
+          <x14:cfRule type="dataBar" id="{10de938c-8233-4d7c-96e6-bc0c91a6d123}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5401,10 +5469,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I1:I17 I19:I39 I41:I1048576</xm:sqref>
+          <xm:sqref>I1:I17 I19:I26 I42:I1048576 I28:I40</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0f6a72ee-a057-428c-8ed3-9638476122dd}">
+          <x14:cfRule type="dataBar" id="{1b06e32f-e60b-4204-9f5c-a98063618033}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5412,10 +5480,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I1:I17 I29:I39 I41:I1048576 I19:I27</xm:sqref>
+          <xm:sqref>I1:I17 I19:I26 I42:I1048576 I28 I30:I40</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6eab6aa1-105e-4d74-8ae0-c75db30c2d26}">
+          <x14:cfRule type="dataBar" id="{2ff10b1e-3672-4e95-ad46-0dc91fa08703}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5423,10 +5491,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I1:I17 I29:I39 I41:I1048576 I19:I25 I27</xm:sqref>
+          <xm:sqref>I1:I17 I19:I25 I42:I1048576 I30:I40 I28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ba32311f-c293-45a0-ab90-991923d7d44e}">
+          <x14:cfRule type="dataBar" id="{e19930b4-8329-405b-90a6-ab502815cbc9}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5434,10 +5502,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I1:I9 I29:I39 I41:I1048576 I11:I17 I27 I21:I25 I19</xm:sqref>
+          <xm:sqref>I1:I9 I21:I25 I42:I1048576 I19 I11:I17 I28 I30:I40</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{56d90323-347a-4c29-8ad9-80803c2b332e}">
+          <x14:cfRule type="dataBar" id="{45ae7e1c-763c-46ff-a2ee-69e1ad8f11ff}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5445,10 +5513,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I1:I9 I29:I39 I41:I1048576 I11:I17 I27 I21:I24 I19</xm:sqref>
+          <xm:sqref>I1:I9 I21:I24 I42:I1048576 I19 I11:I17 I28 I30:I40</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{78e0a573-3615-47e7-9886-e8fb7ea90448}">
+          <x14:cfRule type="dataBar" id="{87982b8a-67e0-4d3e-8484-167f6b5a7892}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5456,10 +5524,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I1:I17 I29:I39 I41:I1048576 I19 I21:I25 I27</xm:sqref>
+          <xm:sqref>I1:I17 I19 I42:I1048576 I21:I25 I28 I30:I40</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{52e2b908-04b9-452d-be88-73c6181bddbb}">
+          <x14:cfRule type="dataBar" id="{ffc17467-5da3-433c-8ac5-69faa3276a81}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5467,10 +5535,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I2 I54:I1048576 I32</xm:sqref>
+          <xm:sqref>I2 I55:I1048576 I33</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d39af3c7-3fcf-48d3-bcb8-514f85206965}">
+          <x14:cfRule type="dataBar" id="{8230e915-ebf3-4217-855c-30a9aa15f80e}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5478,10 +5546,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I2:I4 I29:I39 I6:I7 I42:I1048576 I11:I17 I21:I24 I27 I19 I9</xm:sqref>
+          <xm:sqref>I2:I4 I11:I17 I6:I7 I43:I1048576 I19 I21:I24 I9 I28 I30:I40</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ce3da0d1-7d02-41b1-bdf0-f79a2bab99f3}">
+          <x14:cfRule type="dataBar" id="{ae04e9da-8447-47fd-ac44-324123086088}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5489,10 +5557,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I2:I4 I29:I39 I42:I1048576 I6:I7 I21:I24 I19 I27 I11:I16 I9</xm:sqref>
+          <xm:sqref>I2:I4 I21:I24 I43:I1048576 I6:I7 I19 I9 I11:I16 I28 I30:I40</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3c5da360-cb42-4ee1-9004-9fc9ef0109e2}">
+          <x14:cfRule type="dataBar" id="{8a7eaec4-194d-415b-8731-814c9b2e8188}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5500,10 +5568,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I3:I39 I41:I53</xm:sqref>
+          <xm:sqref>I3:I26 I42:I54 I28:I40</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8c7a61aa-2fd6-4ed0-86e4-d93205ed0969}">
+          <x14:cfRule type="dataBar" id="{3b0afb5e-93c1-4dd7-8c58-58f23e63f6ed}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5511,10 +5579,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I12:I14 I3:I4 I33:I35 I27 I6:I7 I19 I9 I38:I39 I21:I24 I30 I45:I50 I42:I43 I52:I53</xm:sqref>
+          <xm:sqref>I12:I14 I3:I4 I21:I24 I9 I6:I7 I19 I53:I54 I31 I39:I40 I28 I34:I36 I43:I44 I46:I51</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{11cd33f6-fffc-4851-9dcb-540df78c69ae}">
+          <x14:cfRule type="dataBar" id="{a44628d5-73ef-40e6-8b78-140968182f77}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5522,10 +5590,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I33:I35 I3:I4 I30 I21:I24 I6:I7 I12:I14 I9 I19 I38:I39 I45:I50 I42:I43 I52:I53</xm:sqref>
+          <xm:sqref>I19 I3:I4 I9 I21:I24 I6:I7 I12:I14 I53:I54 I39:I40 I31 I34:I36 I46:I51 I43:I44</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3b7df007-1318-46f6-b584-4fa2b37a3df5}">
+          <x14:cfRule type="dataBar" id="{5a58545d-be4e-44cf-b89e-e93d9a23cfed}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5533,10 +5601,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I16 I3:I4 I33:I35 I19 I6:I7 I12:I14 I9 I21:I24 I27 I38:I39 I30 I42:I43 I52:I53 I45:I50</xm:sqref>
+          <xm:sqref>I16 I3:I4 I21:I24 I19 I6:I7 I12:I14 I9 I46:I51 I31 I39:I40 I28 I34:I36 I43:I44 I53:I54</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{bcf3a045-e169-4344-8a46-bbea048fcff5}">
+          <x14:cfRule type="dataBar" id="{14eef661-d018-4326-8dee-a084a02b7240}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5544,10 +5612,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I11:I14 I3:I4 I33:I36 I38:I39 I6:I7 I30:I31 I9 I16 I21:I24 I19 I27 I42:I43 I45:I53</xm:sqref>
+          <xm:sqref>I11:I14 I3:I4 I19 I21:I24 I6:I7 I16 I9 I46:I54 I31:I32 I39:I40 I34:I37 I43:I44 I28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{85996752-cc3d-4c7a-91ec-59a2a0082fe4}">
+          <x14:cfRule type="dataBar" id="{591ea288-a3f6-4809-ad3d-c960ce4c677b}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5555,10 +5623,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I38:I39 I3:I4 I19 I30:I31 I6:I7 I16 I9 I11:I14 I33:I35 I27 I21:I24 I45:I50 I42:I43 I52:I53</xm:sqref>
+          <xm:sqref>I21:I24 I3:I4 I19 I11:I14 I6:I7 I16 I9 I53:I54 I28 I34:I36 I31:I32 I39:I40 I43:I44 I46:I51</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8f03883d-6bc2-4348-a39d-6e9be7965527}">
+          <x14:cfRule type="dataBar" id="{86bcd8a8-6e6a-4d47-ace4-812c1284383e}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5566,10 +5634,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I21:I24 I33:I39 I3:I4 I9 I11:I16 I6:I7 I19 I27 I29:I31 I42:I53</xm:sqref>
+          <xm:sqref>I21:I24 I19 I3:I4 I9 I11:I16 I6:I7 I43:I54 I28 I34:I40 I30:I32</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{840df7f5-c2a1-4cee-b2c8-314e2d820a35}">
+          <x14:cfRule type="dataBar" id="{11adac6c-2f92-4f6c-82bb-56950e2d556e}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5577,10 +5645,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I11:I16 I3:I4 I33:I39 I30:I31 I6:I7 I9 I19 I21:I24 I27 I42:I53</xm:sqref>
+          <xm:sqref>I11:I16 I3:I4 I21:I24 I19 I6:I7 I9 I43:I54 I31:I32 I34:I40 I28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{835c0286-e79b-4e31-a6e5-89b49d1d58b5}">
+          <x14:cfRule type="dataBar" id="{25db3124-d27e-47b6-a736-15c2e55878a4}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5588,10 +5656,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I11:I17 I29:I31 I3:I4 I33:I39 I9 I6:I7 I19 I21:I24 I27 I42:I53</xm:sqref>
+          <xm:sqref>I11:I17 I21:I24 I3:I4 I19 I9 I6:I7 I43:I54 I34:I40 I30:I32 I28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ae9fac30-fc82-47f3-9a5c-a3185969e7d9}">
+          <x14:cfRule type="dataBar" id="{e5d398f1-17c9-408d-8122-f7ca0250a9f6}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5599,10 +5667,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I11:I17 I33:I39 I19 I9 I3:I7 I27 I29:I31 I21:I24 I41:I53</xm:sqref>
+          <xm:sqref>I11:I17 I21:I24 I19 I9 I3:I7 I42:I54 I30:I32 I28 I34:I40</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9b00a8aa-386e-4c4e-b561-2763c24c7b76}">
+          <x14:cfRule type="dataBar" id="{737fbe19-9679-40e7-86b3-4e00ddbafea9}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5610,10 +5678,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I27 I33:I39 I9 I3:I7 I11:I17 I19 I29:I31 I21:I24 I42:I53</xm:sqref>
+          <xm:sqref>I19 I21:I24 I9 I3:I7 I11:I17 I43:I54 I30:I32 I34:I40 I28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{09ae2eac-49db-43b7-a6d9-14db4c2446d5}">
+          <x14:cfRule type="dataBar" id="{e06a5fd6-2eac-46c7-a8d7-2e3ffe8f038d}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5621,7 +5689,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I33:I39 I27 I3:I17 I19:I25 I29:I31 I41:I53</xm:sqref>
+          <xm:sqref>I19:I25 I3:I17 I42:I54 I28 I34:I40 I30:I32</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
